--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -769,7 +769,7 @@
         <v>3.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="K2" t="n">
         <v>4.7</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -1151,16 +1151,16 @@
         <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>2.68</v>
       </c>
       <c r="H12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
         <v>4.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H13" t="n">
         <v>2.36</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="J13" t="n">
         <v>3.2</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G18" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H18" t="n">
         <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
         <v>4.1</v>
@@ -3894,7 +3894,7 @@
         <v>3.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>710</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G22" t="n">
         <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
         <v>3.75</v>
@@ -4664,7 +4664,7 @@
         <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
         <v>1.81</v>
@@ -4679,10 +4679,10 @@
         <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4694,7 +4694,7 @@
         <v>13</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
         <v>32</v>
@@ -4709,16 +4709,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="n">
         <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH22" t="n">
         <v>21</v>
@@ -4727,28 +4727,28 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM22" t="n">
         <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR22" t="n">
         <v>26</v>
@@ -4757,19 +4757,19 @@
         <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY22" t="n">
         <v>9.6</v>
@@ -4778,10 +4778,10 @@
         <v>18.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
@@ -4793,14 +4793,14 @@
         <v>80</v>
       </c>
       <c r="BF22" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG22" t="n">
         <v>44</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>1.67</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H23" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I23" t="n">
         <v>6.2</v>
@@ -4855,7 +4855,7 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
         <v>1.32</v>
@@ -4873,10 +4873,10 @@
         <v>3.55</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="U23" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Z23" t="n">
         <v>60</v>
@@ -4900,10 +4900,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4915,64 +4915,64 @@
         <v>10</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
         <v>150</v>
       </c>
       <c r="AN23" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV23" t="n">
         <v>19.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AX23" t="n">
         <v>8.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BB23" t="n">
         <v>14</v>
@@ -4981,20 +4981,20 @@
         <v>16</v>
       </c>
       <c r="BD23" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BF23" t="n">
         <v>9.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -5097,13 +5097,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG24" t="n">
         <v>12.5</v>
@@ -5127,7 +5127,7 @@
         <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO24" t="n">
         <v>19.5</v>
@@ -5169,10 +5169,10 @@
         <v>26</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BC24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD24" t="n">
         <v>25</v>
@@ -5181,14 +5181,14 @@
         <v>28</v>
       </c>
       <c r="BF24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG24" t="n">
         <v>16.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="H29" t="n">
         <v>1.57</v>
@@ -6010,7 +6010,7 @@
         <v>4.5</v>
       </c>
       <c r="K29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6028,7 +6028,7 @@
         <v>2.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
         <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>410</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         <v>1.01</v>
       </c>
       <c r="K31" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I32" t="n">
         <v>1.46</v>
@@ -6592,7 +6592,7 @@
         <v>5.3</v>
       </c>
       <c r="K32" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>5.7</v>
       </c>
       <c r="O32" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P32" t="n">
         <v>2.62</v>
@@ -6643,7 +6643,7 @@
         <v>15</v>
       </c>
       <c r="AB32" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AC32" t="n">
         <v>14</v>
@@ -6691,13 +6691,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS32" t="n">
         <v>11.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AU32" t="n">
         <v>10.5</v>
@@ -6709,7 +6709,7 @@
         <v>13</v>
       </c>
       <c r="AX32" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AY32" t="n">
         <v>24</v>
@@ -6727,7 +6727,7 @@
         <v>36</v>
       </c>
       <c r="BD32" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE32" t="n">
         <v>38</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>4.2</v>
       </c>
       <c r="I33" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
         <v>2.78</v>
@@ -6804,7 +6804,7 @@
         <v>1.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.56</v>
       </c>
       <c r="G34" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H34" t="n">
         <v>3.4</v>
@@ -6977,7 +6977,7 @@
         <v>3.85</v>
       </c>
       <c r="J34" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K34" t="n">
         <v>2.98</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 00:35:27</t>
+          <t>2026-03-01 02:55:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
         <v>1.67</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
         <v>1.98</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -2703,10 +2703,10 @@
         <v>2.68</v>
       </c>
       <c r="H12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="G14" t="n">
         <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I14" t="n">
         <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K16" t="n">
         <v>3.35</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>2.88</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
         <v>3.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.9</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H21" t="n">
         <v>2.26</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G22" t="n">
         <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
@@ -4670,7 +4670,7 @@
         <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
@@ -4679,7 +4679,7 @@
         <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U22" t="n">
         <v>1.96</v>
@@ -4694,7 +4694,7 @@
         <v>13</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
         <v>32</v>
@@ -4703,7 +4703,7 @@
         <v>120</v>
       </c>
       <c r="AB22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC22" t="n">
         <v>8.199999999999999</v>
@@ -4712,7 +4712,7 @@
         <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF22" t="n">
         <v>12</v>
@@ -4748,16 +4748,16 @@
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
         <v>26</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU22" t="n">
         <v>7.4</v>
@@ -4766,19 +4766,19 @@
         <v>15.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AX22" t="n">
         <v>10</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
         <v>20</v>
@@ -4787,20 +4787,20 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE22" t="n">
         <v>80</v>
       </c>
       <c r="BF22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG22" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1.67</v>
       </c>
       <c r="G23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H23" t="n">
         <v>5.9</v>
@@ -4861,22 +4861,22 @@
         <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
         <v>1.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
         <v>3.55</v>
       </c>
       <c r="T23" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U23" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4888,16 +4888,16 @@
         <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>200</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC23" t="n">
         <v>9.199999999999999</v>
@@ -4948,7 +4948,7 @@
         <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AT23" t="n">
         <v>7.4</v>
@@ -4990,11 +4990,11 @@
         <v>9.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
         <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BB24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.14</v>
+        <v>1.27</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="I30" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H32" t="n">
         <v>1.44</v>
@@ -6643,7 +6643,7 @@
         <v>15</v>
       </c>
       <c r="AB32" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
         <v>14</v>
@@ -6664,7 +6664,7 @@
         <v>25</v>
       </c>
       <c r="AI32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ32" t="n">
         <v>400</v>
@@ -6688,7 +6688,7 @@
         <v>22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR32" t="n">
         <v>9.199999999999999</v>
@@ -6709,7 +6709,7 @@
         <v>13</v>
       </c>
       <c r="AX32" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AY32" t="n">
         <v>24</v>
@@ -6724,7 +6724,7 @@
         <v>48</v>
       </c>
       <c r="BC32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD32" t="n">
         <v>36</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 02:55:10</t>
+          <t>2026-03-01 05:15:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="n">
         <v>2.54</v>
@@ -963,7 +963,7 @@
         <v>3.05</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
         <v>2.08</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
@@ -2148,7 +2148,7 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H11" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
         <v>3.95</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H12" t="n">
         <v>2.68</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.66</v>
       </c>
       <c r="I12" t="n">
         <v>3.25</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
         <v>4.4</v>
@@ -2730,7 +2730,7 @@
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>3.05</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H16" t="n">
         <v>2.7</v>
@@ -3485,7 +3485,7 @@
         <v>3.25</v>
       </c>
       <c r="J16" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
         <v>3.35</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -3873,10 +3873,10 @@
         <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.9</v>
       </c>
       <c r="G21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H21" t="n">
         <v>2.26</v>
@@ -4476,7 +4476,7 @@
         <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
         <v>4.4</v>
@@ -4781,7 +4781,7 @@
         <v>50</v>
       </c>
       <c r="BB22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H23" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I23" t="n">
         <v>6.2</v>
@@ -4960,7 +4960,7 @@
         <v>19.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>8.6</v>
@@ -4984,7 +4984,7 @@
         <v>32</v>
       </c>
       <c r="BE23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF23" t="n">
         <v>9.4</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
         <v>2.5</v>
       </c>
       <c r="H24" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
         <v>3.75</v>
@@ -5070,7 +5070,7 @@
         <v>1.54</v>
       </c>
       <c r="U24" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL24" t="n">
         <v>50</v>
@@ -5127,10 +5127,10 @@
         <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
         <v>19</v>
@@ -5139,7 +5139,7 @@
         <v>15</v>
       </c>
       <c r="AR24" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
         <v>27</v>
@@ -5154,7 +5154,7 @@
         <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AX24" t="n">
         <v>16.5</v>
@@ -5166,7 +5166,7 @@
         <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BB24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G29" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I29" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="J29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -6189,19 +6189,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G30" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="H30" t="n">
         <v>1.63</v>
       </c>
       <c r="I30" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K30" t="n">
         <v>4.6</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
         <v>5.3</v>
       </c>
       <c r="K32" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
         <v>1.04</v>
       </c>
       <c r="N32" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O32" t="n">
         <v>1.2</v>
@@ -6610,13 +6610,13 @@
         <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R32" t="n">
         <v>1.64</v>
       </c>
       <c r="S32" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
         <v>1.83</v>
@@ -6634,16 +6634,16 @@
         <v>28</v>
       </c>
       <c r="Y32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA32" t="n">
         <v>15</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AC32" t="n">
         <v>14</v>
@@ -6661,7 +6661,7 @@
         <v>36</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI32" t="n">
         <v>34</v>
@@ -6682,22 +6682,22 @@
         <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AP32" t="n">
         <v>22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS32" t="n">
         <v>11.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AU32" t="n">
         <v>10.5</v>
@@ -6706,7 +6706,7 @@
         <v>9.4</v>
       </c>
       <c r="AW32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX32" t="n">
         <v>32</v>
@@ -6718,7 +6718,7 @@
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BB32" t="n">
         <v>48</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 05:15:02</t>
+          <t>2026-03-01 07:36:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H2" t="n">
         <v>2.38</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.74</v>
       </c>
       <c r="I2" t="n">
         <v>3.8</v>
@@ -772,19 +772,19 @@
         <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
         <v>1.57</v>
@@ -793,134 +793,134 @@
         <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.39</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H4" t="n">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
         <v>2.04</v>
@@ -2124,7 +2124,7 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
@@ -2148,7 +2148,7 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="G11" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
         <v>4.6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="H12" t="n">
         <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
         <v>4.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="I16" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="J16" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3506,7 +3506,7 @@
         <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.35</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>1.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>870</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="K18" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
-        <v>870</v>
+        <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,61 +4240,61 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,61 +4434,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rapid Vienna (Am)</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SV Austria Salzburg</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.9</v>
+        <v>1.68</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="H21" t="n">
-        <v>2.26</v>
+        <v>5.8</v>
       </c>
       <c r="I21" t="n">
-        <v>2.72</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,116 +4497,116 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -4628,61 +4628,61 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>1.64</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Y22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
         <v>16</v>
       </c>
-      <c r="Z22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AC22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW22" t="n">
         <v>23</v>
       </c>
-      <c r="AL22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="AX22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF22" t="n">
         <v>12</v>
       </c>
-      <c r="AR22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>15</v>
-      </c>
       <c r="BG22" t="n">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,61 +4822,61 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>SS Virtus Verona 1921</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,61 +5016,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Albinoleffe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,116 +5079,116 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SS Virtus Verona 1921</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Albinoleffe</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SSD Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -5598,12 +5598,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SSD Dolomiti Bellunesi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,31 +5792,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>2.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,37 +5981,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Connahs Quay</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G29" t="n">
         <v>6.4</v>
       </c>
-      <c r="G29" t="n">
-        <v>7.2</v>
-      </c>
       <c r="H29" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="I29" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.6</v>
       </c>
-      <c r="K29" t="n">
-        <v>5</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -6180,31 +6180,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Connahs Quay</t>
+          <t>Barry Town Utd</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Penybont FC</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="G30" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="K30" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>1.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Barry Town Utd</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Penybont FC</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="G31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1000</v>
       </c>
-      <c r="H31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I31" t="n">
+      <c r="AG31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>400</v>
+      </c>
+      <c r="AK31" t="n">
         <v>1000</v>
       </c>
-      <c r="J31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K31" t="n">
-        <v>950</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,66 +6563,66 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>7.8</v>
+        <v>2.18</v>
       </c>
       <c r="G32" t="n">
-        <v>8.4</v>
+        <v>2.38</v>
       </c>
       <c r="H32" t="n">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="I32" t="n">
-        <v>1.46</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>5.3</v>
+        <v>2.78</v>
       </c>
       <c r="K32" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6631,116 +6631,116 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>
@@ -6757,36 +6757,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="G33" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="J33" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="K33" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,201 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 07:36:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>19:15:00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CA Huracan</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Belgrano</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-03-01 07:36:17</t>
+          <t>2026-03-01 09:55:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -763,7 +763,7 @@
         <v>3.35</v>
       </c>
       <c r="H2" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
         <v>3.8</v>
@@ -772,7 +772,7 @@
         <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -808,7 +808,7 @@
         <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>2.3</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>1.39</v>
       </c>
       <c r="G4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
         <v>5.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
         <v>1.73</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="G11" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
         <v>1.59</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="H12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I12" t="n">
         <v>3.05</v>
@@ -2730,7 +2730,7 @@
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q14" t="n">
         <v>2.42</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
         <v>3.45</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I15" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="J15" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="J16" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="H17" t="n">
         <v>2.7</v>
@@ -3682,7 +3682,7 @@
         <v>2.7</v>
       </c>
       <c r="K17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>1.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Q18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.77</v>
       </c>
       <c r="G19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>3.7</v>
@@ -4088,7 +4088,7 @@
         <v>3.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G20" t="n">
         <v>2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.02</v>
       </c>
       <c r="H20" t="n">
         <v>4.3</v>
@@ -4264,7 +4264,7 @@
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4291,10 +4291,10 @@
         <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4306,7 +4306,7 @@
         <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z20" t="n">
         <v>32</v>
@@ -4315,19 +4315,19 @@
         <v>120</v>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE20" t="n">
         <v>65</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
@@ -4339,34 +4339,34 @@
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK20" t="n">
         <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM20" t="n">
         <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO20" t="n">
         <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -4378,13 +4378,13 @@
         <v>15.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4402,17 +4402,17 @@
         <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG20" t="n">
         <v>50</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.68</v>
       </c>
-      <c r="G21" t="n">
-        <v>1.7</v>
-      </c>
       <c r="H21" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
         <v>6.2</v>
@@ -4458,7 +4458,7 @@
         <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4467,7 +4467,7 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O21" t="n">
         <v>1.32</v>
@@ -4476,7 +4476,7 @@
         <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R21" t="n">
         <v>1.37</v>
@@ -4485,7 +4485,7 @@
         <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U21" t="n">
         <v>1.96</v>
@@ -4533,10 +4533,10 @@
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL21" t="n">
         <v>40</v>
@@ -4545,7 +4545,7 @@
         <v>150</v>
       </c>
       <c r="AN21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
@@ -4560,7 +4560,7 @@
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>16.5</v>
+        <v>44</v>
       </c>
       <c r="AT21" t="n">
         <v>7.4</v>
@@ -4572,7 +4572,7 @@
         <v>19.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
@@ -4581,7 +4581,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA21" t="n">
         <v>36</v>
@@ -4593,20 +4593,20 @@
         <v>16</v>
       </c>
       <c r="BD21" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE21" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG21" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>2.6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U22" t="n">
         <v>2.7</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK22" t="n">
         <v>30</v>
@@ -4778,7 +4778,7 @@
         <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BB22" t="n">
         <v>28</v>
@@ -4787,7 +4787,7 @@
         <v>19</v>
       </c>
       <c r="BD22" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BE22" t="n">
         <v>28</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -6189,19 +6189,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K30" t="n">
         <v>950</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>7.8</v>
       </c>
       <c r="G31" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
         <v>1.44</v>
@@ -6395,7 +6395,7 @@
         <v>1.46</v>
       </c>
       <c r="J31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K31" t="n">
         <v>5.6</v>
@@ -6425,10 +6425,10 @@
         <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6443,13 +6443,13 @@
         <v>12.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AC31" t="n">
         <v>14.5</v>
@@ -6458,7 +6458,7 @@
         <v>10</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF31" t="n">
         <v>1000</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="AI31" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ31" t="n">
         <v>400</v>
@@ -6488,13 +6488,13 @@
         <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR31" t="n">
         <v>8.800000000000001</v>
@@ -6503,7 +6503,7 @@
         <v>11.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>10.5</v>
@@ -6518,13 +6518,13 @@
         <v>32</v>
       </c>
       <c r="AY31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ31" t="n">
         <v>19.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BB31" t="n">
         <v>48</v>
@@ -6533,7 +6533,7 @@
         <v>38</v>
       </c>
       <c r="BD31" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE31" t="n">
         <v>38</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -6586,13 +6586,13 @@
         <v>4.2</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J32" t="n">
         <v>2.78</v>
       </c>
       <c r="K32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
         <v>3.45</v>
       </c>
       <c r="J33" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="K33" t="n">
         <v>2.96</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 09:55:59</t>
+          <t>2026-03-01 12:12:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G2" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,16 +781,16 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
         <v>1.2</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
         <v>2.72</v>
@@ -1005,37 +1005,37 @@
         <v>1.4</v>
       </c>
       <c r="X3" t="n">
-        <v>9.6</v>
+        <v>980</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.800000000000001</v>
+        <v>980</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="AA3" t="n">
         <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.6</v>
+        <v>980</v>
       </c>
       <c r="AC3" t="n">
         <v>6.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AF3" t="n">
-        <v>19.5</v>
+        <v>980</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AI3" t="n">
         <v>75</v>
@@ -1056,7 +1056,7 @@
         <v>65</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AP3" t="n">
         <v>4.6</v>
@@ -1065,10 +1065,10 @@
         <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.24</v>
+        <v>3.65</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AT3" t="n">
         <v>4.6</v>
@@ -1080,41 +1080,41 @@
         <v>5.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AY3" t="n">
         <v>5.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BA3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG3" t="n">
         <v>1.78</v>
       </c>
-      <c r="BB3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="G4" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
         <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T5" t="n">
         <v>1.01</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.01</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.01</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SSV Ulm</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -2882,49 +2882,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>SSV Ulm</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I13" t="n">
         <v>3.3</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.36</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G14" t="n">
         <v>3.4</v>
@@ -3100,7 +3100,7 @@
         <v>2.96</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>3.45</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="H15" t="n">
         <v>2.22</v>
@@ -3291,7 +3291,7 @@
         <v>2.42</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
         <v>3.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>3.75</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I16" t="n">
         <v>2.42</v>
@@ -3488,7 +3488,7 @@
         <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>3.35</v>
+        <v>1.55</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>870</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="G18" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>870</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.77</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="I19" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="J19" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.2</v>
+        <v>1.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.32</v>
+        <v>2.58</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.99</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
         <v>1.39</v>
       </c>
       <c r="P20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
         <v>2.16</v>
@@ -4291,7 +4291,7 @@
         <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>1.97</v>
@@ -4315,13 +4315,13 @@
         <v>120</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>65</v>
@@ -4333,7 +4333,7 @@
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4354,7 +4354,7 @@
         <v>16.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
         <v>11.5</v>
@@ -4363,22 +4363,22 @@
         <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS20" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
         <v>15.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
@@ -4402,17 +4402,17 @@
         <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF20" t="n">
         <v>15</v>
       </c>
       <c r="BG20" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.67</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.68</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
@@ -4458,7 +4458,7 @@
         <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>1.32</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R21" t="n">
         <v>1.37</v>
@@ -4485,7 +4485,7 @@
         <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>1.96</v>
@@ -4497,19 +4497,19 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z21" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AA21" t="n">
         <v>200</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>9.199999999999999</v>
@@ -4521,10 +4521,10 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH21" t="n">
         <v>23</v>
@@ -4542,7 +4542,7 @@
         <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN21" t="n">
         <v>10.5</v>
@@ -4551,13 +4551,13 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AS21" t="n">
         <v>44</v>
@@ -4566,34 +4566,34 @@
         <v>7.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BB21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
         <v>42</v>
@@ -4602,11 +4602,11 @@
         <v>9</v>
       </c>
       <c r="BG21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
         <v>19.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BF22" t="n">
         <v>12</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SS Virtus Verona 1921</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Albinoleffe</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SSD Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Albinoleffe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>SS Virtus Verona 1921</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SSD Dolomiti Bellunesi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,66 +5981,66 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Connahs Quay</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.28</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="J29" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="K29" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R29" t="n">
         <v>1.64</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6049,123 +6049,123 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,36 +6175,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Barry Town Utd</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Penybont FC</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.02</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H30" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J30" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,66 +6369,66 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>7.8</v>
+        <v>2.78</v>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="H31" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="I31" t="n">
-        <v>1.46</v>
+        <v>3.45</v>
       </c>
       <c r="J31" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="K31" t="n">
-        <v>5.6</v>
+        <v>2.96</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.62</v>
+        <v>1.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.59</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6437,504 +6437,116 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 12:12:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Sarmiento de Junin</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Estudiantes Rio Cuarto</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-03-01 12:12:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>19:15:00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CA Huracan</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Belgrano</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-03-01 12:12:42</t>
+          <t>2026-03-01 14:26:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
         <v>2.84</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -805,7 +805,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
         <v>1.47</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1187,7 +1187,7 @@
         <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
         <v>1.79</v>
@@ -1253,62 +1253,62 @@
         <v>260</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
         <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>2.62</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
         <v>1.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>3.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>46</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>3.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>40</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>30</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>50</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
@@ -1545,7 +1545,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
@@ -1566,13 +1566,13 @@
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.3</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>2.24</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1584,7 +1584,7 @@
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1641,52 +1641,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.24</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.08</v>
       </c>
       <c r="S7" t="n">
         <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>30</v>
+        <v>2.92</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="AW7" t="n">
-        <v>26</v>
+        <v>2.88</v>
       </c>
       <c r="AX7" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>4.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>40</v>
+        <v>2.92</v>
       </c>
       <c r="BB7" t="n">
-        <v>29</v>
+        <v>2.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>2.86</v>
       </c>
       <c r="BD7" t="n">
-        <v>38</v>
+        <v>2.92</v>
       </c>
       <c r="BE7" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>2.74</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>3.45</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.6</v>
+        <v>3.35</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>3.15</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.5</v>
+        <v>3.65</v>
       </c>
       <c r="AS8" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.6</v>
+        <v>3.25</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>2.96</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>3.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>3.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>29</v>
+        <v>4.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>50</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1860 Munich</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Erzgebirge</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>2.58</v>
       </c>
       <c r="G9" t="n">
-        <v>1.98</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>SSV Ulm</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Viktoria Koln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87</v>
+        <v>2.74</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>2.64</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.68</v>
+        <v>2.96</v>
       </c>
       <c r="G11" t="n">
-        <v>1.82</v>
+        <v>3.25</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>2.76</v>
       </c>
       <c r="I11" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
         <v>4.7</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>VfL Osnabruck</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Viktoria Koln</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="H12" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SSV Ulm</t>
+          <t>1860 Munich</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>1.98</v>
       </c>
       <c r="H13" t="n">
-        <v>2.66</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
         <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.96</v>
+        <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="H14" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AC Monza</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.45</v>
+        <v>1.77</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4</v>
+        <v>2.06</v>
       </c>
       <c r="H15" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2.42</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6</v>
+        <v>980</v>
       </c>
       <c r="H16" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>2.42</v>
+        <v>870</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.26</v>
+        <v>1.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I17" t="n">
-        <v>870</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.77</v>
+        <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="I18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA18" t="n">
         <v>4.7</v>
       </c>
-      <c r="J18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>AC Monza</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="I19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J19" t="n">
         <v>3.25</v>
       </c>
-      <c r="J19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="K19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.25</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,61 +4240,61 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,61 +4434,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>SSD Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,123 +4497,123 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,61 +4628,61 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Albinoleffe</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,116 +4691,116 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>SS Virtus Verona 1921</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SSD Dolomiti Bellunesi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -5058,7 +5058,7 @@
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Albinoleffe</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SS Virtus Verona 1921</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,977 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 14:26:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Italian Serie C</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>16:30:00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Lecco</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Renate</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-03-01 14:26:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Swiss Super League</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>16:30:00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Winterthur</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Servette</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-03-01 14:26:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>English Premier League</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>17:15:00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Wolves</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>400</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>38</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-03-01 14:26:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Sarmiento de Junin</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Estudiantes Rio Cuarto</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-03-01 14:26:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>19:15:00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CA Huracan</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Belgrano</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-03-01 14:26:36</t>
+          <t>2026-03-01 16:36:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -775,7 +775,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -784,10 +784,10 @@
         <v>1.69</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q2" t="n">
         <v>2.16</v>
@@ -805,10 +805,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="G3" t="n">
         <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J3" t="n">
         <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.45</v>
@@ -981,7 +981,7 @@
         <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
         <v>2.56</v>
@@ -999,10 +999,10 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X3" t="n">
         <v>980</v>
@@ -1065,7 +1065,7 @@
         <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AS3" t="n">
         <v>1.94</v>
@@ -1074,7 +1074,7 @@
         <v>4.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="AV3" t="n">
         <v>5.5</v>
@@ -1083,13 +1083,13 @@
         <v>1.92</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.7</v>
+        <v>2.22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BA3" t="n">
         <v>1.8</v>
@@ -1098,7 +1098,7 @@
         <v>1.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.79</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
         <v>1.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -1360,25 +1360,25 @@
         <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="T5" t="n">
         <v>1.79</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>1.98</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
@@ -1545,7 +1545,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.06</v>
+        <v>2.06</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1584,7 +1584,7 @@
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>3.65</v>
       </c>
       <c r="J7" t="n">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.74</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
         <v>2.96</v>
@@ -1936,7 +1936,7 @@
         <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
@@ -1966,16 +1966,16 @@
         <v>1.86</v>
       </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V8" t="n">
         <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
         <v>11.5</v>
@@ -1987,13 +1987,13 @@
         <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="AC8" t="n">
         <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>980</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
         <v>980</v>
@@ -2029,69 +2029,69 @@
         <v>980</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU8" t="n">
         <v>3.25</v>
       </c>
-      <c r="AU8" t="n">
-        <v>2.96</v>
-      </c>
       <c r="AV8" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Padova</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="G9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
         <v>2.96</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="O9" t="n">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>2.42</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP9" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>27</v>
+        <v>6.4</v>
       </c>
       <c r="AT9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY9" t="n">
         <v>11</v>
       </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -2312,40 +2312,40 @@
         <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
         <v>2.64</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
         <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S10" t="n">
         <v>2.46</v>
@@ -2357,10 +2357,10 @@
         <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
         <v>27</v>
@@ -2399,7 +2399,7 @@
         <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2417,69 +2417,69 @@
         <v>21</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>17.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA10" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.5</v>
       </c>
       <c r="BB10" t="n">
         <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="H11" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>1.63</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.42</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H12" t="n">
         <v>4.8</v>
@@ -2715,13 +2715,13 @@
         <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
         <v>1.28</v>
@@ -2730,25 +2730,25 @@
         <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R12" t="n">
         <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X12" t="n">
         <v>980</v>
@@ -2814,7 +2814,7 @@
         <v>4.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2829,7 +2829,7 @@
         <v>4.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.4</v>
+        <v>3.65</v>
       </c>
       <c r="AY12" t="n">
         <v>7.8</v>
@@ -2847,7 +2847,7 @@
         <v>4.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
         <v>4.8</v>
@@ -2856,11 +2856,11 @@
         <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G13" t="n">
         <v>1.98</v>
@@ -2927,10 +2927,10 @@
         <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.77</v>
       </c>
       <c r="G15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H15" t="n">
         <v>3.7</v>
@@ -3291,158 +3291,158 @@
         <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
         <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
         <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="S15" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="V15" t="n">
         <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP15" t="n">
-        <v>29</v>
+        <v>4.7</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>30</v>
+        <v>4.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>60</v>
+        <v>4.9</v>
       </c>
       <c r="AT15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV15" t="n">
         <v>15</v>
       </c>
-      <c r="AU15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>4.6</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="H16" t="n">
         <v>1.04</v>
@@ -3485,7 +3485,7 @@
         <v>870</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3497,13 +3497,13 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="Q16" t="n">
         <v>1.2</v>
@@ -3581,52 +3581,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>2.74</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3706,7 +3706,7 @@
         <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T17" t="n">
         <v>2.06</v>
@@ -3724,7 +3724,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z17" t="n">
         <v>19.5</v>
@@ -3781,7 +3781,7 @@
         <v>7.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS17" t="n">
         <v>34</v>
@@ -3796,7 +3796,7 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX17" t="n">
         <v>15.5</v>
@@ -3805,32 +3805,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG17" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H18" t="n">
         <v>2.18</v>
@@ -3903,13 +3903,13 @@
         <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W18" t="n">
         <v>1.28</v>
@@ -3972,7 +3972,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR18" t="n">
         <v>11.5</v>
@@ -3981,7 +3981,7 @@
         <v>4.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AU18" t="n">
         <v>6.6</v>
@@ -4002,7 +4002,7 @@
         <v>4.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB18" t="n">
         <v>4.9</v>
@@ -4011,20 +4011,20 @@
         <v>4.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE18" t="n">
         <v>5</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG18" t="n">
         <v>18.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H19" t="n">
         <v>2.24</v>
@@ -4073,10 +4073,10 @@
         <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
         <v>3.25</v>
@@ -4091,28 +4091,28 @@
         <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T19" t="n">
         <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
         <v>1.69</v>
       </c>
       <c r="W19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
         <v>17.5</v>
@@ -4121,10 +4121,10 @@
         <v>40</v>
       </c>
       <c r="AB19" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
         <v>14</v>
@@ -4172,7 +4172,7 @@
         <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -4184,41 +4184,41 @@
         <v>9.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="AY19" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BG19" t="n">
         <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Albinoleffe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSD Dolomiti Bellunesi</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>2.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Albinoleffe</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
         <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>SSD Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,378 +5205,4258 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>1.35</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 16:36:43</t>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X26" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>85</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rapid Vienna (Am)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SV Austria Salzburg</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X29" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Welsh Premiership</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Barry Town Utd</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Penybont FC</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K30" t="n">
+        <v>950</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Welsh Premiership</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Connahs Quay</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>The New Saints</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Scottish League Two</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Spartans</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Stirling</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X32" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Scottish League One</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Montrose</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Kelty Hearts</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>85</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Dunfermline</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ross Co</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Scottish Championship</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Arbroath</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ayr</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Hartlepool</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sutton Utd</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>York City</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X37" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Boston Utd</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Wealdstone</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Morecambe</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Yeovil</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tamworth FC</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Rochdale</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Brackley Town</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>25</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K41" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Truro City</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>15</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X42" t="n">
+        <v>980</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Scottish League One</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Stenhousemuir</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Wolves</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X44" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>270</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>55</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Argentinian Primera Division</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>19:15:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>CA Huracan</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Belgrano</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="F46" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H46" t="n">
         <v>3.35</v>
       </c>
-      <c r="I26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="I46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J46" t="n">
         <v>2.62</v>
       </c>
-      <c r="K26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:36:43</t>
+      <c r="K46" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:47:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH46"/>
+  <dimension ref="A1:BH47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -778,13 +778,13 @@
         <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
         <v>1.69</v>
@@ -793,19 +793,19 @@
         <v>2.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
         <v>1.52</v>
@@ -823,10 +823,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -835,7 +835,7 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
         <v>1000</v>
@@ -856,7 +856,7 @@
         <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -1002,7 +1002,7 @@
         <v>1.49</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
         <v>980</v>
@@ -1065,56 +1065,56 @@
         <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="AT3" t="n">
         <v>4.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="AV3" t="n">
         <v>5.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="AX3" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.34</v>
+        <v>6.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="BC3" t="n">
         <v>7.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.43</v>
       </c>
       <c r="G4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
         <v>8.4</v>
@@ -1157,13 +1157,13 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1199,7 +1199,7 @@
         <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>980</v>
@@ -1253,10 +1253,10 @@
         <v>260</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
         <v>5.8</v>
@@ -1268,31 +1268,31 @@
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
         <v>5.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
         <v>5.4</v>
@@ -1301,14 +1301,14 @@
         <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
         <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
         <v>3.85</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AX7" t="n">
         <v>4</v>
@@ -1871,10 +1871,10 @@
         <v>2.92</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="BD7" t="n">
         <v>2.92</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G8" t="n">
         <v>3.2</v>
@@ -1942,19 +1942,19 @@
         <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
         <v>2.74</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
         <v>1.26</v>
@@ -1975,7 +1975,7 @@
         <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="Y8" t="n">
         <v>11.5</v>
@@ -1993,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
         <v>980</v>
@@ -2029,62 +2029,62 @@
         <v>980</v>
       </c>
       <c r="AP8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AR8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J9" t="n">
         <v>2.96</v>
@@ -2154,13 +2154,13 @@
         <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T9" t="n">
         <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
         <v>1.5</v>
@@ -2172,7 +2172,7 @@
         <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.4</v>
+        <v>980</v>
       </c>
       <c r="Z9" t="n">
         <v>980</v>
@@ -2226,13 +2226,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
         <v>8.6</v>
@@ -2241,44 +2241,44 @@
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="AY9" t="n">
         <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA9" t="n">
         <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF9" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF9" t="n">
+      <c r="BG9" t="n">
         <v>6.4</v>
       </c>
-      <c r="BG9" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
         <v>2.64</v>
@@ -2321,7 +2321,7 @@
         <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2360,7 +2360,7 @@
         <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
         <v>27</v>
@@ -2405,7 +2405,7 @@
         <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>70</v>
@@ -2417,7 +2417,7 @@
         <v>21</v>
       </c>
       <c r="AP10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
         <v>12</v>
@@ -2426,7 +2426,7 @@
         <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
         <v>11.5</v>
@@ -2441,7 +2441,7 @@
         <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
         <v>9.4</v>
@@ -2450,10 +2450,10 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
@@ -2462,7 +2462,7 @@
         <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2527,10 +2527,10 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
         <v>2.32</v>
@@ -2539,134 +2539,134 @@
         <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.55</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.54</v>
-      </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="H12" t="n">
         <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
@@ -2721,7 +2721,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.28</v>
@@ -2730,25 +2730,25 @@
         <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
         <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X12" t="n">
         <v>980</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G13" t="n">
         <v>1.98</v>
@@ -2900,10 +2900,10 @@
         <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
         <v>4.4</v>
@@ -2912,149 +2912,149 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
         <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.21</v>
       </c>
       <c r="W13" t="n">
         <v>2.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
         <v>1.84</v>
@@ -3097,13 +3097,13 @@
         <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
         <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3133,7 +3133,7 @@
         <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
         <v>2.2</v>
@@ -3187,7 +3187,7 @@
         <v>75</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO14" t="n">
         <v>55</v>
@@ -3199,10 +3199,10 @@
         <v>19.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT14" t="n">
         <v>9.800000000000001</v>
@@ -3214,7 +3214,7 @@
         <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3226,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3235,20 +3235,20 @@
         <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF14" t="n">
         <v>6.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K15" t="n">
         <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M15" t="n">
         <v>1.02</v>
@@ -3312,7 +3312,7 @@
         <v>3.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
         <v>1.91</v>
@@ -3327,10 +3327,10 @@
         <v>2.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="X15" t="n">
         <v>48</v>
@@ -3354,7 +3354,7 @@
         <v>21</v>
       </c>
       <c r="AE15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
         <v>21</v>
@@ -3366,7 +3366,7 @@
         <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ15" t="n">
         <v>27</v>
@@ -3384,19 +3384,19 @@
         <v>6.8</v>
       </c>
       <c r="AO15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>16</v>
@@ -3408,7 +3408,7 @@
         <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
@@ -3432,17 +3432,17 @@
         <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG15" t="n">
         <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>110</v>
+        <v>1.46</v>
       </c>
       <c r="H16" t="n">
         <v>1.04</v>
@@ -3497,13 +3497,13 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
         <v>1.2</v>
@@ -3512,7 +3512,7 @@
         <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3524,7 +3524,7 @@
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N17" t="n">
         <v>2.68</v>
@@ -3742,7 +3742,7 @@
         <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AF17" t="n">
         <v>980</v>
@@ -3751,7 +3751,7 @@
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
         <v>75</v>
@@ -3805,16 +3805,16 @@
         <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA17" t="n">
         <v>5.8</v>
       </c>
       <c r="BB17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC17" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>5.6</v>
       </c>
       <c r="BD17" t="n">
         <v>50</v>
@@ -3823,14 +3823,14 @@
         <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG17" t="n">
         <v>5.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H18" t="n">
         <v>2.18</v>
@@ -3891,16 +3891,16 @@
         <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
         <v>1.9</v>
@@ -3912,7 +3912,7 @@
         <v>1.73</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X18" t="n">
         <v>12.5</v>
@@ -3942,7 +3942,7 @@
         <v>32</v>
       </c>
       <c r="AG18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH18" t="n">
         <v>24</v>
@@ -3990,22 +3990,22 @@
         <v>9.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY18" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA18" t="n">
         <v>4.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
         <v>4.8</v>
@@ -4014,7 +4014,7 @@
         <v>4.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF18" t="n">
         <v>4.9</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
         <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
         <v>3.25</v>
@@ -4100,10 +4100,10 @@
         <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W19" t="n">
         <v>1.36</v>
@@ -4148,7 +4148,7 @@
         <v>85</v>
       </c>
       <c r="AK19" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AL19" t="n">
         <v>70</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4273,22 +4273,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P20" t="n">
         <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I21" t="n">
         <v>1.58</v>
@@ -4593,7 +4593,7 @@
         <v>7.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BE21" t="n">
         <v>7.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
         <v>3.4</v>
@@ -4649,7 +4649,7 @@
         <v>4.8</v>
       </c>
       <c r="J22" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="K22" t="n">
         <v>3.85</v>
@@ -4658,16 +4658,16 @@
         <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="O22" t="n">
         <v>1.36</v>
       </c>
       <c r="P22" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q22" t="n">
         <v>2.46</v>
@@ -4676,16 +4676,16 @@
         <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="T22" t="n">
         <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
         <v>1.7</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.31</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5049,10 +5049,10 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
         <v>1.35</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.68</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.69</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
@@ -5658,7 +5658,7 @@
         <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X27" t="n">
         <v>15</v>
@@ -5685,7 +5685,7 @@
         <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG27" t="n">
         <v>9.6</v>
@@ -5712,7 +5712,7 @@
         <v>10.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
         <v>14</v>
@@ -5763,14 +5763,14 @@
         <v>100</v>
       </c>
       <c r="BF27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG27" t="n">
         <v>85</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>4.4</v>
@@ -5813,10 +5813,10 @@
         <v>4.5</v>
       </c>
       <c r="J28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.75</v>
       </c>
       <c r="L28" t="n">
         <v>1.46</v>
@@ -5861,7 +5861,7 @@
         <v>14</v>
       </c>
       <c r="Z28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA28" t="n">
         <v>100</v>
@@ -5918,7 +5918,7 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AT28" t="n">
         <v>7.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
         <v>40</v>
       </c>
       <c r="AJ29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK29" t="n">
         <v>38</v>
@@ -6106,7 +6106,7 @@
         <v>15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
         <v>13</v>
@@ -6127,7 +6127,7 @@
         <v>18.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N31" t="n">
         <v>1.03</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="H32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I32" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K32" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6601,146 +6601,146 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O32" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V32" t="n">
         <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="X32" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH32" t="n">
         <v>30</v>
       </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI32" t="n">
         <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.05</v>
+        <v>2.74</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.05</v>
+        <v>2.98</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.05</v>
+        <v>2.38</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.05</v>
+        <v>2.44</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.05</v>
+        <v>2.78</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.05</v>
+        <v>2.98</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.05</v>
+        <v>2.44</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.05</v>
+        <v>2.44</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.05</v>
+        <v>2.72</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.05</v>
+        <v>2.98</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.05</v>
+        <v>2.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.05</v>
+        <v>2.64</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.05</v>
+        <v>2.82</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.05</v>
+        <v>2.98</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.05</v>
+        <v>2.38</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.05</v>
+        <v>2.98</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>1.99</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I33" t="n">
         <v>6.2</v>
@@ -6795,16 +6795,16 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
         <v>1.31</v>
       </c>
       <c r="P33" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R33" t="n">
         <v>1.34</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="G34" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H34" t="n">
         <v>3.2</v>
@@ -6977,7 +6977,7 @@
         <v>3.9</v>
       </c>
       <c r="J34" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
         <v>3.6</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7162,13 +7162,13 @@
         <v>2.44</v>
       </c>
       <c r="G35" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H35" t="n">
         <v>2.9</v>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>2.96</v>
@@ -7183,7 +7183,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O35" t="n">
         <v>1.35</v>
@@ -7207,10 +7207,10 @@
         <v>1.8</v>
       </c>
       <c r="V35" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W35" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X35" t="n">
         <v>17.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
         <v>4.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
         <v>1.05</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7550,28 +7550,28 @@
         <v>2.82</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="H37" t="n">
         <v>2.22</v>
       </c>
       <c r="I37" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J37" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K37" t="n">
         <v>4.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="O37" t="n">
         <v>1.16</v>
@@ -7583,22 +7583,22 @@
         <v>1.55</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="S37" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U37" t="n">
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X37" t="n">
         <v>36</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
         <v>4.6</v>
       </c>
       <c r="J39" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K39" t="n">
         <v>5</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
         <v>2.68</v>
       </c>
       <c r="I40" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>3.15</v>
@@ -8147,7 +8147,7 @@
         <v>3.75</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M40" t="n">
         <v>1.06</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G41" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H41" t="n">
         <v>17.5</v>
@@ -8353,7 +8353,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q41" t="n">
         <v>1.8</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
         <v>7.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M42" t="n">
         <v>1.03</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8702,55 +8702,55 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="G43" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J43" t="n">
         <v>2.5</v>
       </c>
-      <c r="J43" t="n">
-        <v>2.94</v>
-      </c>
       <c r="K43" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="O43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P43" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R43" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S43" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -8759,10 +8759,10 @@
         <v>1.01</v>
       </c>
       <c r="V43" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8874,14 +8874,14 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8891,191 +8891,191 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>7.8</v>
+        <v>3.3</v>
       </c>
       <c r="G44" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="H44" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="I44" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
-        <v>5.5</v>
+        <v>2.94</v>
       </c>
       <c r="K44" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="L44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.3</v>
       </c>
-      <c r="M44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V44" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X44" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH44" t="n">
         <v>23</v>
       </c>
-      <c r="Y44" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF44" t="n">
+      <c r="AI44" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL44" t="n">
         <v>75</v>
       </c>
-      <c r="AG44" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>270</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>90</v>
-      </c>
       <c r="AM44" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AN44" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AO44" t="n">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="AP44" t="n">
-        <v>22</v>
+        <v>3.7</v>
       </c>
       <c r="AQ44" t="n">
-        <v>10</v>
+        <v>3.35</v>
       </c>
       <c r="AR44" t="n">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="AS44" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="AT44" t="n">
-        <v>28</v>
+        <v>3.8</v>
       </c>
       <c r="AU44" t="n">
-        <v>11</v>
+        <v>3.25</v>
       </c>
       <c r="AV44" t="n">
-        <v>9.4</v>
+        <v>3.65</v>
       </c>
       <c r="AW44" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX44" t="n">
-        <v>55</v>
+        <v>4.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="AZ44" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="BA44" t="n">
-        <v>26</v>
+        <v>4.7</v>
       </c>
       <c r="BB44" t="n">
-        <v>48</v>
+        <v>4.8</v>
       </c>
       <c r="BC44" t="n">
-        <v>38</v>
+        <v>4.7</v>
       </c>
       <c r="BD44" t="n">
-        <v>60</v>
+        <v>4.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>90</v>
+        <v>4.9</v>
       </c>
       <c r="BF44" t="n">
-        <v>44</v>
+        <v>4.8</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9085,184 +9085,184 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="G45" t="n">
-        <v>2.38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>4.2</v>
+        <v>1.43</v>
       </c>
       <c r="I45" t="n">
-        <v>4.8</v>
+        <v>1.44</v>
       </c>
       <c r="J45" t="n">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="K45" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P45" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-01 18:47:53</t>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>
@@ -9279,184 +9279,378 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sarmiento de Junin</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S46" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X46" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-03-01 20:58:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>19:15:00</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>CA Huracan</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Belgrano</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="F47" t="n">
         <v>2.68</v>
       </c>
-      <c r="G46" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H46" t="n">
+      <c r="G47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H47" t="n">
         <v>3.35</v>
       </c>
-      <c r="I46" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J46" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="K46" t="n">
+      <c r="I47" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K47" t="n">
         <v>2.86</v>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
+      <c r="L47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P47" t="n">
         <v>1.35</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q47" t="n">
         <v>3.45</v>
       </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH46" t="inlineStr">
-        <is>
-          <t>2026-03-01 18:47:53</t>
+      <c r="R47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X47" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>400</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>2026-03-01 20:58:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
         <v>2.82</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
@@ -784,10 +784,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
         <v>2.16</v>
@@ -799,16 +799,16 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -823,7 +823,7 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AC2" t="n">
         <v>8.800000000000001</v>
@@ -868,7 +868,7 @@
         <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR2" t="n">
         <v>4.7</v>
@@ -883,7 +883,7 @@
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>5.3</v>
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>4.8</v>
@@ -907,7 +907,7 @@
         <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
         <v>5.7</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
         <v>2.7</v>
@@ -981,10 +981,10 @@
         <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -993,16 +993,16 @@
         <v>5.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
         <v>980</v>
@@ -1041,13 +1041,13 @@
         <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
         <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>980</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="n">
         <v>5.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AZ3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BB3" t="n">
         <v>6.4</v>
       </c>
-      <c r="BA3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.36</v>
+        <v>3.55</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.06</v>
+        <v>3.65</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.34</v>
+        <v>3.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1187,10 +1187,10 @@
         <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
         <v>1.11</v>
@@ -1226,7 +1226,7 @@
         <v>10.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>980</v>
@@ -1238,7 +1238,7 @@
         <v>15</v>
       </c>
       <c r="AK4" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>980</v>
@@ -1247,34 +1247,34 @@
         <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>980</v>
+        <v>8.6</v>
       </c>
       <c r="AO4" t="n">
         <v>260</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
@@ -1283,32 +1283,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE4" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6</v>
       </c>
       <c r="BF4" t="n">
         <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
         <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.79</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="G6" t="n">
         <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2.06</v>
+        <v>2.76</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1581,7 +1581,7 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
         <v>2.02</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
         <v>980</v>
       </c>
       <c r="AC7" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>980</v>
@@ -1823,7 +1823,7 @@
         <v>980</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.4</v>
+        <v>1.49</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.92</v>
+        <v>1.34</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.35</v>
+        <v>1.49</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.05</v>
+        <v>1.37</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.85</v>
+        <v>1.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>1.34</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>1.52</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.92</v>
+        <v>1.35</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>1.34</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.5</v>
+        <v>1.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.92</v>
+        <v>1.37</v>
       </c>
       <c r="BE7" t="n">
-        <v>3</v>
+        <v>1.37</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>1.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>1.34</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
         <v>2.96</v>
@@ -1936,7 +1936,7 @@
         <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
         <v>1.39</v>
@@ -1984,7 +1984,7 @@
         <v>980</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
         <v>980</v>
@@ -1993,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AE8" t="n">
         <v>980</v>
@@ -2002,7 +2002,7 @@
         <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
         <v>980</v>
@@ -2029,62 +2029,62 @@
         <v>980</v>
       </c>
       <c r="AP8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR8" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS8" t="n">
-        <v>5</v>
-      </c>
       <c r="AT8" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE8" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2121,13 +2121,13 @@
         <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
@@ -2163,19 +2163,19 @@
         <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
         <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
         <v>980</v>
@@ -2187,22 +2187,22 @@
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
         <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
         <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
         <v>65</v>
@@ -2220,65 +2220,65 @@
         <v>980</v>
       </c>
       <c r="AO9" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AP9" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG9" t="n">
         <v>5.5</v>
       </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
         <v>3.05</v>
@@ -2360,7 +2360,7 @@
         <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
         <v>27</v>
@@ -2411,22 +2411,22 @@
         <v>70</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
         <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
         <v>11.5</v>
@@ -2450,19 +2450,19 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
         <v>2.82</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2533,7 +2533,7 @@
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
         <v>1.64</v>
@@ -2551,7 +2551,7 @@
         <v>2.48</v>
       </c>
       <c r="V11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
         <v>1.55</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
         <v>1.87</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.33</v>
@@ -2727,28 +2727,28 @@
         <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
         <v>980</v>
@@ -2829,7 +2829,7 @@
         <v>4.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AY12" t="n">
         <v>7.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G13" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
@@ -2930,19 +2930,19 @@
         <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
         <v>23</v>
@@ -3017,10 +3017,10 @@
         <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3032,7 +3032,7 @@
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="BB13" t="n">
         <v>17.5</v>
@@ -3050,11 +3050,11 @@
         <v>9</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
         <v>1.84</v>
@@ -3103,7 +3103,7 @@
         <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3115,16 +3115,16 @@
         <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
         <v>1.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
         <v>1.63</v>
@@ -3151,7 +3151,7 @@
         <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
         <v>11.5</v>
@@ -3163,13 +3163,13 @@
         <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
         <v>60</v>
@@ -3178,19 +3178,19 @@
         <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="n">
         <v>8.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AP14" t="n">
         <v>19</v>
@@ -3199,10 +3199,10 @@
         <v>19.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
         <v>9.800000000000001</v>
@@ -3214,7 +3214,7 @@
         <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3226,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3235,20 +3235,20 @@
         <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="n">
         <v>1.95</v>
@@ -3318,7 +3318,7 @@
         <v>1.91</v>
       </c>
       <c r="S15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="T15" t="n">
         <v>1.43</v>
@@ -3327,10 +3327,10 @@
         <v>2.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X15" t="n">
         <v>48</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H17" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J17" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="K17" t="n">
         <v>3.1</v>
@@ -3706,40 +3706,40 @@
         <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T17" t="n">
         <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
         <v>1.42</v>
       </c>
       <c r="X17" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z17" t="n">
         <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC17" t="n">
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="AE17" t="n">
         <v>46</v>
@@ -3748,13 +3748,13 @@
         <v>980</v>
       </c>
       <c r="AG17" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
         <v>65</v>
@@ -3763,7 +3763,7 @@
         <v>55</v>
       </c>
       <c r="AL17" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="n">
         <v>190</v>
@@ -3772,19 +3772,19 @@
         <v>70</v>
       </c>
       <c r="AO17" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ17" t="n">
         <v>7.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
         <v>8.199999999999999</v>
@@ -3793,44 +3793,44 @@
         <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>15.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY17" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BD17" t="n">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H18" t="n">
         <v>2.18</v>
@@ -3894,7 +3894,7 @@
         <v>1.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
@@ -3903,10 +3903,10 @@
         <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="V18" t="n">
         <v>1.73</v>
@@ -3918,7 +3918,7 @@
         <v>12.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.4</v>
+        <v>980</v>
       </c>
       <c r="Z18" t="n">
         <v>15.5</v>
@@ -3942,13 +3942,13 @@
         <v>32</v>
       </c>
       <c r="AG18" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="AH18" t="n">
         <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AJ18" t="n">
         <v>100</v>
@@ -3978,10 +3978,10 @@
         <v>11.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
         <v>6.6</v>
@@ -3990,41 +3990,41 @@
         <v>9.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY18" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG18" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I19" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J19" t="n">
         <v>3.25</v>
@@ -4073,7 +4073,7 @@
         <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
@@ -4088,7 +4088,7 @@
         <v>1.77</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
@@ -4097,7 +4097,7 @@
         <v>3.85</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
         <v>2.02</v>
@@ -4115,40 +4115,40 @@
         <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.5</v>
+        <v>980</v>
       </c>
       <c r="AA19" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AB19" t="n">
         <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE19" t="n">
         <v>34</v>
       </c>
       <c r="AF19" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AG19" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AK19" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AL19" t="n">
         <v>70</v>
@@ -4172,7 +4172,7 @@
         <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="AT19" t="n">
         <v>10.5</v>
@@ -4184,41 +4184,41 @@
         <v>9.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="AY19" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BG19" t="n">
         <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>2.76</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -4297,10 +4297,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
         <v>4.7</v>
       </c>
       <c r="K21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>1.25</v>
@@ -4482,7 +4482,7 @@
         <v>1.64</v>
       </c>
       <c r="S21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
         <v>1.71</v>
@@ -4497,55 +4497,55 @@
         <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AB21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC21" t="n">
         <v>11.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AF21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="AK21" t="n">
         <v>80</v>
       </c>
       <c r="AL21" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM21" t="n">
         <v>90</v>
       </c>
       <c r="AN21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO21" t="n">
         <v>5.9</v>
@@ -4572,10 +4572,10 @@
         <v>9.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
         <v>22</v>
@@ -4587,26 +4587,26 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BD21" t="n">
         <v>55</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.6</v>
+        <v>48</v>
       </c>
       <c r="BG21" t="n">
         <v>5.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="H22" t="n">
         <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K22" t="n">
         <v>3.85</v>
@@ -4658,7 +4658,7 @@
         <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
         <v>2.46</v>
@@ -4679,128 +4679,128 @@
         <v>2.86</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U22" t="n">
         <v>1.93</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
         <v>1.7</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -4879,10 +4879,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -5034,49 +5034,49 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="O24" t="n">
         <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
         <v>2.06</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5133,62 +5133,62 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -5419,10 +5419,10 @@
         <v>2.5</v>
       </c>
       <c r="H26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I26" t="n">
         <v>3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3.05</v>
       </c>
       <c r="J26" t="n">
         <v>3.75</v>
@@ -5437,7 +5437,7 @@
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.21</v>
@@ -5458,10 +5458,10 @@
         <v>1.56</v>
       </c>
       <c r="U26" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.66</v>
@@ -5470,7 +5470,7 @@
         <v>22</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z26" t="n">
         <v>23</v>
@@ -5509,7 +5509,7 @@
         <v>22</v>
       </c>
       <c r="AL26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM26" t="n">
         <v>55</v>
@@ -5569,14 +5569,14 @@
         <v>48</v>
       </c>
       <c r="BF26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG26" t="n">
         <v>17</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G27" t="n">
         <v>1.68</v>
@@ -5676,7 +5676,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>23</v>
@@ -5760,7 +5760,7 @@
         <v>34</v>
       </c>
       <c r="BE27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF27" t="n">
         <v>9.4</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I28" t="n">
         <v>4.5</v>
@@ -5831,7 +5831,7 @@
         <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q28" t="n">
         <v>2.16</v>
@@ -5861,7 +5861,7 @@
         <v>14</v>
       </c>
       <c r="Z28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA28" t="n">
         <v>100</v>
@@ -5870,7 +5870,7 @@
         <v>8</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
         <v>17.5</v>
@@ -5888,7 +5888,7 @@
         <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="n">
         <v>23</v>
@@ -5954,7 +5954,7 @@
         <v>38</v>
       </c>
       <c r="BE28" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF28" t="n">
         <v>15.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -6052,37 +6052,37 @@
         <v>21</v>
       </c>
       <c r="Y29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA29" t="n">
         <v>38</v>
       </c>
       <c r="AB29" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AJ29" t="n">
         <v>55</v>
@@ -6091,7 +6091,7 @@
         <v>38</v>
       </c>
       <c r="AL29" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AM29" t="n">
         <v>85</v>
@@ -6100,7 +6100,7 @@
         <v>32</v>
       </c>
       <c r="AO29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -6109,46 +6109,46 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU29" t="n">
         <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BF29" t="n">
         <v>20</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H30" t="n">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6237,10 +6237,10 @@
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G31" t="n">
         <v>6.4</v>
@@ -6392,37 +6392,37 @@
         <v>1.7</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="J31" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K31" t="n">
         <v>4.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="T31" t="n">
         <v>1.79</v>
@@ -6431,122 +6431,122 @@
         <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W31" t="n">
         <v>1.19</v>
       </c>
       <c r="X31" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA31" t="n">
         <v>21</v>
       </c>
       <c r="AB31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC31" t="n">
         <v>11.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>18.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH31" t="n">
         <v>23</v>
       </c>
-      <c r="AH31" t="n">
-        <v>21</v>
-      </c>
       <c r="AI31" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AJ31" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AK31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN31" t="n">
         <v>90</v>
       </c>
-      <c r="AL31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>100</v>
-      </c>
       <c r="AO31" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AP31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE31" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ31" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW31" t="n">
+      <c r="BF31" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX31" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG31" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -6583,55 +6583,55 @@
         <v>1.69</v>
       </c>
       <c r="H32" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="O32" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="T32" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="U32" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="V32" t="n">
         <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X32" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
         <v>32</v>
@@ -6661,7 +6661,7 @@
         <v>13.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
@@ -6670,10 +6670,10 @@
         <v>20</v>
       </c>
       <c r="AK32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AU32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AV32" t="n">
         <v>2.44</v>
       </c>
-      <c r="AV32" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AW32" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="AY32" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="BB32" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="BF32" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -6789,13 +6789,13 @@
         <v>85</v>
       </c>
       <c r="L33" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
         <v>1.31</v>
@@ -6804,19 +6804,19 @@
         <v>1.79</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R33" t="n">
         <v>1.34</v>
       </c>
       <c r="S33" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="T33" t="n">
         <v>1.74</v>
       </c>
       <c r="U33" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V33" t="n">
         <v>1.22</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G34" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
         <v>1.37</v>
@@ -6989,22 +6989,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R34" t="n">
         <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -7013,10 +7013,10 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -7159,25 +7159,25 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="G35" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="H35" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="L35" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
@@ -7204,13 +7204,13 @@
         <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="X35" t="n">
         <v>17.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -7371,34 +7371,34 @@
         <v>4.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M36" t="n">
         <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
         <v>1.25</v>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R36" t="n">
         <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
         <v>1.66</v>
       </c>
       <c r="U36" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V36" t="n">
         <v>1.32</v>
@@ -7422,7 +7422,7 @@
         <v>11.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD36" t="n">
         <v>16.5</v>
@@ -7470,7 +7470,7 @@
         <v>21</v>
       </c>
       <c r="AS36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT36" t="n">
         <v>9.4</v>
@@ -7482,7 +7482,7 @@
         <v>12</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX36" t="n">
         <v>11</v>
@@ -7494,7 +7494,7 @@
         <v>14</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB36" t="n">
         <v>21</v>
@@ -7503,20 +7503,20 @@
         <v>17.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF36" t="n">
         <v>10</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G37" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="H37" t="n">
         <v>2.22</v>
@@ -7571,7 +7571,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>4.4</v>
+        <v>2.44</v>
       </c>
       <c r="O37" t="n">
         <v>1.16</v>
@@ -7586,10 +7586,10 @@
         <v>1.57</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T37" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
         <v>1.01</v>
@@ -7598,7 +7598,7 @@
         <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X37" t="n">
         <v>36</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G38" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="H38" t="n">
         <v>3.45</v>
@@ -7765,28 +7765,28 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="O38" t="n">
         <v>1.33</v>
       </c>
       <c r="P38" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T38" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U38" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V38" t="n">
         <v>1.28</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="G39" t="n">
         <v>2.32</v>
       </c>
       <c r="H39" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="I39" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="J39" t="n">
-        <v>3.35</v>
+        <v>2.68</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -8129,59 +8129,59 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="G40" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H40" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.32</v>
       </c>
       <c r="M40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O40" t="n">
         <v>1.06</v>
       </c>
-      <c r="N40" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.25</v>
-      </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="R40" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U40" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.43</v>
       </c>
-      <c r="W40" t="n">
-        <v>1.46</v>
-      </c>
       <c r="X40" t="n">
         <v>1000</v>
       </c>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G42" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H42" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I42" t="n">
         <v>15</v>
       </c>
       <c r="J42" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K42" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="L42" t="n">
         <v>1.2</v>
@@ -8550,13 +8550,13 @@
         <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R42" t="n">
         <v>1.51</v>
       </c>
       <c r="S42" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="T42" t="n">
         <v>1.86</v>
@@ -8565,10 +8565,10 @@
         <v>1.68</v>
       </c>
       <c r="V42" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W42" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="X42" t="n">
         <v>980</v>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR42" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV42" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AW42" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AX42" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AY42" t="n">
         <v>3.45</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA42" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD42" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE42" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="BF42" t="n">
         <v>4</v>
       </c>
       <c r="BG42" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -8905,31 +8905,31 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="H44" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>2.94</v>
       </c>
       <c r="K44" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L44" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M44" t="n">
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O44" t="n">
         <v>1.38</v>
@@ -8938,137 +8938,137 @@
         <v>1.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R44" t="n">
         <v>1.27</v>
       </c>
       <c r="S44" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T44" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U44" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="V44" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="W44" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X44" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y44" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z44" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA44" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO44" t="n">
         <v>34</v>
       </c>
-      <c r="AB44" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>26</v>
-      </c>
       <c r="AP44" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="AW44" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX44" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY44" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ44" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BB44" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC44" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG44" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -9102,13 +9102,13 @@
         <v>7.8</v>
       </c>
       <c r="G45" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H45" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="I45" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J45" t="n">
         <v>5.5</v>
@@ -9147,10 +9147,10 @@
         <v>2.14</v>
       </c>
       <c r="V45" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="W45" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
         <v>24</v>
@@ -9189,19 +9189,19 @@
         <v>29</v>
       </c>
       <c r="AJ45" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AK45" t="n">
         <v>110</v>
       </c>
       <c r="AL45" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM45" t="n">
         <v>110</v>
       </c>
       <c r="AN45" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO45" t="n">
         <v>5.4</v>
@@ -9231,7 +9231,7 @@
         <v>12.5</v>
       </c>
       <c r="AX45" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AY45" t="n">
         <v>27</v>
@@ -9246,23 +9246,23 @@
         <v>48</v>
       </c>
       <c r="BC45" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="BD45" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE45" t="n">
         <v>90</v>
       </c>
       <c r="BF45" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -9314,13 +9314,13 @@
         <v>1.01</v>
       </c>
       <c r="M46" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N46" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="P46" t="n">
         <v>1.38</v>
@@ -9347,7 +9347,7 @@
         <v>1.71</v>
       </c>
       <c r="X46" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y46" t="n">
         <v>12</v>
@@ -9356,10 +9356,10 @@
         <v>38</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB46" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC46" t="n">
         <v>8.6</v>
@@ -9368,95 +9368,95 @@
         <v>26</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="n">
         <v>15</v>
       </c>
       <c r="AG46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH46" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ46" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK46" t="n">
         <v>48</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM46" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.52</v>
+        <v>5.8</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR46" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.58</v>
+        <v>6.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>3.25</v>
+        <v>18</v>
       </c>
       <c r="AW46" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX46" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY46" t="n">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="BA46" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="BB46" t="n">
-        <v>24</v>
+        <v>4.9</v>
       </c>
       <c r="BC46" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE46" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="BF46" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="BG46" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         <v>2.68</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H47" t="n">
         <v>3.35</v>
@@ -9532,13 +9532,13 @@
         <v>2.46</v>
       </c>
       <c r="U47" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V47" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W47" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X47" t="n">
         <v>6.2</v>
@@ -9547,10 +9547,10 @@
         <v>8.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA47" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AB47" t="n">
         <v>6.8</v>
@@ -9562,25 +9562,25 @@
         <v>19</v>
       </c>
       <c r="AE47" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF47" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AH47" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI47" t="n">
         <v>160</v>
       </c>
       <c r="AJ47" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AK47" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AL47" t="n">
         <v>130</v>
@@ -9589,7 +9589,7 @@
         <v>400</v>
       </c>
       <c r="AN47" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AO47" t="n">
         <v>150</v>
@@ -9604,7 +9604,7 @@
         <v>19.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AT47" t="n">
         <v>5.9</v>
@@ -9616,7 +9616,7 @@
         <v>16.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AX47" t="n">
         <v>14</v>
@@ -9628,29 +9628,29 @@
         <v>26</v>
       </c>
       <c r="BA47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BB47" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BC47" t="n">
         <v>40</v>
       </c>
       <c r="BD47" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BE47" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF47" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BG47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-01 20:58:19</t>
+          <t>2026-03-01 23:07:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH47"/>
+  <dimension ref="A1:BH50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,10 +763,10 @@
         <v>2.98</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
@@ -835,7 +835,7 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H3" t="n">
         <v>2.84</v>
       </c>
-      <c r="G3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.82</v>
-      </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K3" t="n">
         <v>3.25</v>
@@ -978,13 +978,13 @@
         <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
         <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -999,7 +999,7 @@
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W3" t="n">
         <v>1.44</v>
@@ -1059,16 +1059,16 @@
         <v>980</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AT3" t="n">
         <v>4</v>
@@ -1077,44 +1077,44 @@
         <v>5.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BE3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG3" t="n">
         <v>3.65</v>
       </c>
-      <c r="BF3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1148,43 +1148,43 @@
         <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
@@ -1199,19 +1199,19 @@
         <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
         <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>980</v>
@@ -1253,28 +1253,28 @@
         <v>260</v>
       </c>
       <c r="AP4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
@@ -1283,32 +1283,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB4" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H5" t="n">
         <v>3.1</v>
@@ -1351,7 +1351,7 @@
         <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1363,34 +1363,34 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V5" t="n">
         <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X5" t="n">
         <v>980</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.4</v>
@@ -1751,7 +1751,7 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.4</v>
@@ -1760,25 +1760,25 @@
         <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
         <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
         <v>980</v>
@@ -1883,14 +1883,14 @@
         <v>1.37</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.33</v>
+        <v>2.22</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.34</v>
+        <v>2.22</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1957,7 +1957,7 @@
         <v>2.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>3.45</v>
@@ -2002,7 +2002,7 @@
         <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>980</v>
       </c>
       <c r="AH8" t="n">
         <v>980</v>
@@ -2029,62 +2029,62 @@
         <v>980</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AU8" t="n">
         <v>3.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AY8" t="n">
         <v>3.65</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC8" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BD8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="BG8" t="n">
         <v>4.3</v>
       </c>
-      <c r="BE8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>2.88</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2300,82 +2300,82 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SSV Ulm</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.55</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.49</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC10" t="n">
         <v>11</v>
@@ -2387,92 +2387,92 @@
         <v>32</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
         <v>17.5</v>
       </c>
-      <c r="AI10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>26</v>
+        <v>4.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2494,85 +2494,85 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>SSV Ulm</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cottbus</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.58</v>
       </c>
-      <c r="U11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.55</v>
-      </c>
       <c r="X11" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z11" t="n">
         <v>26</v>
       </c>
-      <c r="Y11" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>25</v>
-      </c>
       <c r="AA11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
         <v>15.5</v>
@@ -2581,92 +2581,92 @@
         <v>32</v>
       </c>
       <c r="AF11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>40</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>48</v>
-      </c>
       <c r="AK11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL11" t="n">
         <v>32</v>
       </c>
-      <c r="AL11" t="n">
-        <v>40</v>
-      </c>
       <c r="AM11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF11" t="n">
         <v>11</v>
       </c>
-      <c r="AW11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
+      <c r="BG11" t="n">
         <v>13</v>
       </c>
-      <c r="BA11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>12</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
@@ -2715,7 +2715,7 @@
         <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2739,16 +2739,16 @@
         <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X12" t="n">
         <v>980</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.81</v>
       </c>
       <c r="G13" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -2933,16 +2933,16 @@
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X13" t="n">
         <v>23</v>
@@ -2969,7 +2969,7 @@
         <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG13" t="n">
         <v>12.5</v>
@@ -2978,7 +2978,7 @@
         <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ13" t="n">
         <v>25</v>
@@ -2993,68 +2993,68 @@
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>15.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>22</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3118,19 +3118,19 @@
         <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
         <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
         <v>1.63</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
         <v>1.23</v>
@@ -3241,14 +3241,14 @@
         <v>6.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BG14" t="n">
         <v>6.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
         <v>1.95</v>
@@ -3402,7 +3402,7 @@
         <v>16</v>
       </c>
       <c r="AU15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV15" t="n">
         <v>15</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3500,19 +3500,19 @@
         <v>1.51</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
         <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R16" t="n">
         <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
         <v>3</v>
@@ -3990,41 +3990,41 @@
         <v>9.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY18" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD18" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
         <v>6</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Albinoleffe</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SSD Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>2.88</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS20" t="n">
         <v>2.76</v>
       </c>
-      <c r="K20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H21" t="n">
         <v>1.53</v>
@@ -4467,13 +4467,13 @@
         <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q21" t="n">
         <v>1.56</v>
@@ -4509,7 +4509,7 @@
         <v>15</v>
       </c>
       <c r="AB21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC21" t="n">
         <v>11.5</v>
@@ -4539,7 +4539,7 @@
         <v>80</v>
       </c>
       <c r="AL21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="n">
         <v>90</v>
@@ -4560,22 +4560,22 @@
         <v>10</v>
       </c>
       <c r="AS21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV21" t="n">
         <v>9.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="AY21" t="n">
         <v>22</v>
@@ -4587,16 +4587,16 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD21" t="n">
         <v>55</v>
       </c>
       <c r="BE21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF21" t="n">
         <v>48</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -4646,19 +4646,19 @@
         <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="K22" t="n">
         <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
         <v>2.46</v>
@@ -4679,13 +4679,13 @@
         <v>2.86</v>
       </c>
       <c r="T22" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U22" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
         <v>1.7</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>2.2</v>
       </c>
       <c r="I23" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="J23" t="n">
         <v>2.78</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -5016,67 +5016,67 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SSD Dolomiti Bellunesi</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K24" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.06</v>
+        <v>1.35</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>1.35</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5133,69 +5133,69 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="G25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.8</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.68</v>
       </c>
-      <c r="K25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.48</v>
+        <v>1.67</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="H26" t="n">
-        <v>2.98</v>
+        <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O26" t="n">
         <v>1.32</v>
       </c>
-      <c r="M26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.21</v>
-      </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="W26" t="n">
-        <v>1.66</v>
+        <v>2.46</v>
       </c>
       <c r="X26" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Y26" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AA26" t="n">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="AB26" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="AF26" t="n">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP26" t="n">
         <v>14</v>
       </c>
-      <c r="AI26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>20</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AS26" t="n">
         <v>44</v>
       </c>
       <c r="AT26" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AW26" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="AX26" t="n">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="BB26" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BE26" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF26" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -5598,55 +5598,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="G27" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
         <v>4.1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.55</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
@@ -5655,129 +5655,129 @@
         <v>1.97</v>
       </c>
       <c r="V27" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="Z27" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AA27" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AE27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS27" t="n">
         <v>85</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>44</v>
       </c>
       <c r="AT27" t="n">
         <v>7.8</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB27" t="n">
         <v>21</v>
       </c>
-      <c r="AW27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27" t="n">
+      <c r="BC27" t="n">
         <v>20</v>
       </c>
-      <c r="BA27" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD27" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE27" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF27" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Rapid Vienna (Am)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>SV Austria Salzburg</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3</v>
+        <v>2.28</v>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="P28" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="U28" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="V28" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="X28" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT28" t="n">
         <v>12</v>
       </c>
-      <c r="Y28" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP28" t="n">
+      <c r="AU28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AZ28" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR28" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BA28" t="n">
-        <v>65</v>
+        <v>5.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>21</v>
+        <v>5.9</v>
       </c>
       <c r="BC28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF28" t="n">
         <v>20</v>
       </c>
-      <c r="BD28" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BG28" t="n">
-        <v>65</v>
+        <v>12.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,179 +5986,179 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Rapid Vienna (Am)</t>
+          <t>Albinoleffe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SV Austria Salzburg</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.9</v>
+        <v>1.88</v>
       </c>
       <c r="G29" t="n">
-        <v>3.4</v>
+        <v>980</v>
       </c>
       <c r="H29" t="n">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="T29" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="W29" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>2.72</v>
       </c>
       <c r="H30" t="n">
-        <v>1.89</v>
+        <v>2.54</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
@@ -6213,7 +6213,7 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="O30" t="n">
         <v>1.01</v>
@@ -6222,13 +6222,13 @@
         <v>1.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -6598,31 +6598,31 @@
         <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N32" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="O32" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P32" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R32" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U32" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V32" t="n">
         <v>1.12</v>
@@ -6631,7 +6631,7 @@
         <v>2.46</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="n">
         <v>32</v>
@@ -6688,59 +6688,59 @@
         <v>2.62</v>
       </c>
       <c r="AQ32" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AX32" t="n">
         <v>2.42</v>
       </c>
-      <c r="AR32" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AV32" t="n">
+      <c r="AY32" t="n">
         <v>2.44</v>
       </c>
-      <c r="AW32" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="BB32" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="BF32" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>1.99</v>
       </c>
       <c r="H33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
         <v>6.2</v>
@@ -6789,7 +6789,7 @@
         <v>85</v>
       </c>
       <c r="L33" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -6986,13 +6986,13 @@
         <v>1.37</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N34" t="n">
         <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P34" t="n">
         <v>1.67</v>
@@ -7004,7 +7004,7 @@
         <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -7073,69 +7073,69 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AR34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="BA34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB34" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW34" t="n">
+      <c r="BC34" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB34" t="n">
+      <c r="BD34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF34" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE34" t="n">
+      <c r="BG34" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7150,186 +7150,186 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="G35" t="n">
-        <v>3.05</v>
+        <v>2.22</v>
       </c>
       <c r="H35" t="n">
-        <v>2.46</v>
+        <v>3.5</v>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K35" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="P35" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="X35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC35" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y35" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AV35" t="n">
+      <c r="BD35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF35" t="n">
         <v>10</v>
       </c>
-      <c r="AW35" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BG35" t="n">
-        <v>2.54</v>
+        <v>6.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7344,179 +7344,179 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="G36" t="n">
-        <v>2.22</v>
+        <v>2.84</v>
       </c>
       <c r="H36" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L36" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="O36" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="P36" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="T36" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="U36" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="V36" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W36" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="X36" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="Y36" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z36" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
         <v>11.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE36" t="n">
         <v>980</v>
       </c>
       <c r="AF36" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AG36" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH36" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AJ36" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM36" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>15</v>
+        <v>3.75</v>
       </c>
       <c r="AQ36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX36" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR36" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>11</v>
-      </c>
       <c r="AY36" t="n">
-        <v>9.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="AZ36" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB36" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BC36" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF36" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -7538,115 +7538,115 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Boston Utd</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="G37" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J37" t="n">
         <v>3.25</v>
       </c>
-      <c r="H37" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I37" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="J37" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K37" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L37" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>2.44</v>
+        <v>1.84</v>
       </c>
       <c r="O37" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="P37" t="n">
-        <v>2.42</v>
+        <v>1.84</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="R37" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="S37" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V37" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="W37" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="X37" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AA37" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AB37" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AC37" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AD37" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AE37" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF37" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AG37" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI37" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AJ37" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AK37" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AL37" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM37" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.04</v>
+        <v>19</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AU37" t="n">
         <v>1.91</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="AX37" t="n">
-        <v>2.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -7732,179 +7732,179 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Boston Utd</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="G38" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H38" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="I38" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="K38" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="L38" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="R38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -7926,179 +7926,179 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="F39" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U39" t="n">
         <v>1.8</v>
       </c>
-      <c r="G39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="H39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -8120,179 +8120,179 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.32</v>
+        <v>1.25</v>
       </c>
       <c r="G40" t="n">
-        <v>3.35</v>
+        <v>1.28</v>
       </c>
       <c r="H40" t="n">
-        <v>2.42</v>
+        <v>17.5</v>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="K40" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="R40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -8314,179 +8314,179 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="G41" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="H41" t="n">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J41" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="K41" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P41" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -8508,31 +8508,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.3</v>
+        <v>2.84</v>
       </c>
       <c r="G42" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="H42" t="n">
-        <v>8.800000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="I42" t="n">
-        <v>15</v>
+        <v>2.52</v>
       </c>
       <c r="J42" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="K42" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="L42" t="n">
         <v>1.2</v>
@@ -8541,146 +8541,146 @@
         <v>1.03</v>
       </c>
       <c r="N42" t="n">
-        <v>4.7</v>
+        <v>2.44</v>
       </c>
       <c r="O42" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="S42" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="T42" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.07</v>
+        <v>1.65</v>
       </c>
       <c r="W42" t="n">
-        <v>3.5</v>
+        <v>1.44</v>
       </c>
       <c r="X42" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="Y42" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="Z42" t="n">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB42" t="n">
-        <v>980</v>
+        <v>26</v>
       </c>
       <c r="AC42" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF42" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AG42" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="AH42" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ42" t="n">
-        <v>980</v>
+        <v>70</v>
       </c>
       <c r="AK42" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AL42" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN42" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>4.1</v>
+        <v>2.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.98</v>
+        <v>2.04</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.45</v>
+        <v>2.02</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.85</v>
+        <v>1.91</v>
       </c>
       <c r="AV42" t="n">
-        <v>4.5</v>
+        <v>1.96</v>
       </c>
       <c r="AW42" t="n">
-        <v>3.4</v>
+        <v>2.06</v>
       </c>
       <c r="AX42" t="n">
-        <v>3.35</v>
+        <v>2.08</v>
       </c>
       <c r="AY42" t="n">
-        <v>3.45</v>
+        <v>1.98</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.3</v>
+        <v>1.99</v>
       </c>
       <c r="BA42" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="BB42" t="n">
-        <v>3.6</v>
+        <v>2.14</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="BE42" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="BF42" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="BG42" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -9099,13 +9099,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H45" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I45" t="n">
         <v>1.45</v>
@@ -9147,10 +9147,10 @@
         <v>2.14</v>
       </c>
       <c r="V45" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="W45" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X45" t="n">
         <v>24</v>
@@ -9180,16 +9180,16 @@
         <v>75</v>
       </c>
       <c r="AG45" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH45" t="n">
         <v>22</v>
       </c>
       <c r="AI45" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ45" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AK45" t="n">
         <v>110</v>
@@ -9201,7 +9201,7 @@
         <v>110</v>
       </c>
       <c r="AN45" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AO45" t="n">
         <v>5.4</v>
@@ -9243,7 +9243,7 @@
         <v>27</v>
       </c>
       <c r="BB45" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BC45" t="n">
         <v>38</v>
@@ -9258,11 +9258,11 @@
         <v>75</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G46" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H46" t="n">
         <v>4.2</v>
       </c>
       <c r="I46" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>2.8</v>
@@ -9317,7 +9317,7 @@
         <v>1.16</v>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O46" t="n">
         <v>1.72</v>
@@ -9341,16 +9341,16 @@
         <v>1.57</v>
       </c>
       <c r="V46" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X46" t="n">
         <v>7.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z46" t="n">
         <v>38</v>
@@ -9371,7 +9371,7 @@
         <v>120</v>
       </c>
       <c r="AF46" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG46" t="n">
         <v>14</v>
@@ -9383,7 +9383,7 @@
         <v>180</v>
       </c>
       <c r="AJ46" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AK46" t="n">
         <v>48</v>
@@ -9395,7 +9395,7 @@
         <v>400</v>
       </c>
       <c r="AN46" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AO46" t="n">
         <v>230</v>
@@ -9410,7 +9410,7 @@
         <v>19.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT46" t="n">
         <v>5.4</v>
@@ -9422,7 +9422,7 @@
         <v>18</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX46" t="n">
         <v>10</v>
@@ -9431,32 +9431,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC46" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB46" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>5</v>
-      </c>
       <c r="BD46" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF46" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>5</v>
-      </c>
       <c r="BG46" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G47" t="n">
         <v>2.92</v>
@@ -9499,7 +9499,7 @@
         <v>3.8</v>
       </c>
       <c r="J47" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K47" t="n">
         <v>2.86</v>
@@ -9526,7 +9526,7 @@
         <v>1.12</v>
       </c>
       <c r="S47" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="T47" t="n">
         <v>2.46</v>
@@ -9535,7 +9535,7 @@
         <v>1.58</v>
       </c>
       <c r="V47" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W47" t="n">
         <v>1.52</v>
@@ -9550,7 +9550,7 @@
         <v>25</v>
       </c>
       <c r="AA47" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB47" t="n">
         <v>6.8</v>
@@ -9604,7 +9604,7 @@
         <v>19.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT47" t="n">
         <v>5.9</v>
@@ -9628,7 +9628,7 @@
         <v>26</v>
       </c>
       <c r="BA47" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB47" t="n">
         <v>7.6</v>
@@ -9637,7 +9637,7 @@
         <v>40</v>
       </c>
       <c r="BD47" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE47" t="n">
         <v>8.4</v>
@@ -9646,11 +9646,593 @@
         <v>7.8</v>
       </c>
       <c r="BG47" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-01 23:07:57</t>
+          <t>2026-03-02 01:18:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>21:15:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Atl Tucuman</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>2026-03-02 01:18:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X49" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>2026-03-02 01:18:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Santos Laguna</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K50" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X50" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>2026-03-02 01:18:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -766,7 +766,7 @@
         <v>2.84</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
@@ -784,10 +784,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
         <v>2.16</v>
@@ -868,7 +868,7 @@
         <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
         <v>4.7</v>
@@ -883,7 +883,7 @@
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
         <v>5.3</v>
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>4.8</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I3" t="n">
         <v>3.15</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="L3" t="n">
         <v>1.45</v>
@@ -975,7 +975,7 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O3" t="n">
         <v>1.49</v>
@@ -984,7 +984,7 @@
         <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.2</v>
@@ -999,7 +999,7 @@
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
         <v>1.44</v>
@@ -1041,10 +1041,10 @@
         <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AL3" t="n">
         <v>75</v>
@@ -1062,16 +1062,16 @@
         <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR3" t="n">
         <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AU3" t="n">
         <v>5.7</v>
@@ -1080,7 +1080,7 @@
         <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AX3" t="n">
         <v>5.2</v>
@@ -1089,32 +1089,32 @@
         <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC3" t="n">
         <v>3.75</v>
       </c>
-      <c r="BB3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC3" t="n">
+      <c r="BD3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG3" t="n">
         <v>3.7</v>
       </c>
-      <c r="BD3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4" t="n">
         <v>4.3</v>
@@ -1175,7 +1175,7 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
         <v>1.69</v>
@@ -1187,7 +1187,7 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
         <v>1.81</v>
@@ -1196,7 +1196,7 @@
         <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X4" t="n">
         <v>20</v>
@@ -1220,7 +1220,7 @@
         <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF4" t="n">
         <v>10.5</v>
@@ -1250,7 +1250,7 @@
         <v>8.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AP4" t="n">
         <v>4.3</v>
@@ -1262,7 +1262,7 @@
         <v>4.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
@@ -1283,13 +1283,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
         <v>5</v>
@@ -1298,7 +1298,7 @@
         <v>4.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
         <v>6</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.56</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>1.99</v>
       </c>
       <c r="T5" t="n">
         <v>1.78</v>
@@ -1387,10 +1387,10 @@
         <v>1.91</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>980</v>
@@ -1447,62 +1447,62 @@
         <v>65</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY5" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="AZ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE5" t="n">
+      <c r="BG5" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>2.96</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
         <v>3.65</v>
@@ -1954,7 +1954,7 @@
         <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="n">
         <v>2.76</v>
@@ -2139,7 +2139,7 @@
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.47</v>
@@ -2157,16 +2157,16 @@
         <v>4.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
         <v>11.5</v>
@@ -2208,7 +2208,7 @@
         <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
         <v>65</v>
@@ -2256,16 +2256,16 @@
         <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
         <v>5.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE9" t="n">
         <v>6</v>
@@ -2274,11 +2274,11 @@
         <v>5.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I10" t="n">
         <v>2.82</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,28 +2333,28 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
         <v>1.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.52</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.48</v>
       </c>
       <c r="V10" t="n">
         <v>1.55</v>
@@ -2411,10 +2411,10 @@
         <v>75</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
         <v>18.5</v>
@@ -2462,7 +2462,7 @@
         <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I11" t="n">
         <v>3.05</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.26</v>
@@ -2533,7 +2533,7 @@
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
         <v>1.59</v>
@@ -2542,10 +2542,10 @@
         <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U11" t="n">
         <v>2.34</v>
@@ -2554,7 +2554,7 @@
         <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
         <v>27</v>
@@ -2599,7 +2599,7 @@
         <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
         <v>70</v>
@@ -2611,22 +2611,22 @@
         <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
@@ -2635,7 +2635,7 @@
         <v>20</v>
       </c>
       <c r="AX11" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
         <v>9.4</v>
@@ -2644,10 +2644,10 @@
         <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC11" t="n">
         <v>18</v>
@@ -2656,17 +2656,17 @@
         <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
         <v>11</v>
       </c>
       <c r="BG11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
@@ -2709,13 +2709,13 @@
         <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2727,28 +2727,28 @@
         <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="X12" t="n">
         <v>980</v>
@@ -2841,7 +2841,7 @@
         <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="BC12" t="n">
         <v>4.1</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.81</v>
       </c>
       <c r="G13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -2918,31 +2918,31 @@
         <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
         <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
         <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X13" t="n">
         <v>23</v>
@@ -2999,62 +2999,62 @@
         <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>15.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS13" t="n">
         <v>4.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
         <v>4.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC13" t="n">
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>22</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
         <v>4.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
         <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3124,13 +3124,13 @@
         <v>1.54</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
         <v>1.23</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="n">
         <v>1.95</v>
@@ -3288,7 +3288,7 @@
         <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
         <v>4.4</v>
@@ -3327,76 +3327,76 @@
         <v>2.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
         <v>2.04</v>
       </c>
       <c r="X15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
         <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>38</v>
       </c>
       <c r="AJ15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
         <v>26</v>
       </c>
       <c r="AM15" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
         <v>16</v>
@@ -3408,7 +3408,7 @@
         <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
@@ -3420,7 +3420,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3432,7 +3432,7 @@
         <v>18.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
         <v>4.8</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>2.78</v>
       </c>
       <c r="I17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J17" t="n">
         <v>2.9</v>
@@ -3691,7 +3691,7 @@
         <v>1.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="O17" t="n">
         <v>1.53</v>
@@ -3715,7 +3715,7 @@
         <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.42</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
         <v>3.85</v>
       </c>
       <c r="T19" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="U19" t="n">
         <v>2.02</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
         <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V20" t="n">
         <v>1.29</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4593,20 +4593,20 @@
         <v>12</v>
       </c>
       <c r="BD21" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="BE21" t="n">
         <v>12</v>
       </c>
       <c r="BF21" t="n">
-        <v>48</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
         <v>5.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H25" t="n">
         <v>2.98</v>
@@ -5240,7 +5240,7 @@
         <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
         <v>5.5</v>
@@ -5258,7 +5258,7 @@
         <v>1.6</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
         <v>1.56</v>
@@ -5279,7 +5279,7 @@
         <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
         <v>46</v>
@@ -5324,7 +5324,7 @@
         <v>13.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP25" t="n">
         <v>19.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
         <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T26" t="n">
         <v>2</v>
@@ -5566,7 +5566,7 @@
         <v>34</v>
       </c>
       <c r="BE26" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BF26" t="n">
         <v>9.4</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
         <v>1.46</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
         <v>3.45</v>
@@ -5637,7 +5637,7 @@
         <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
         <v>2.16</v>
@@ -5652,7 +5652,7 @@
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V27" t="n">
         <v>1.28</v>
@@ -5724,7 +5724,7 @@
         <v>29</v>
       </c>
       <c r="AS27" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT27" t="n">
         <v>7.8</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
         <v>19.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
         <v>2.08</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="R31" t="n">
         <v>1.42</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6580,10 +6580,10 @@
         <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I32" t="n">
         <v>9.199999999999999</v>
@@ -6619,16 +6619,16 @@
         <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="U32" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
         <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="X32" t="n">
         <v>21</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>1.99</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I33" t="n">
         <v>6.2</v>
@@ -6795,16 +6795,16 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O33" t="n">
         <v>1.31</v>
       </c>
       <c r="P33" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R33" t="n">
         <v>1.34</v>
@@ -6816,7 +6816,7 @@
         <v>1.74</v>
       </c>
       <c r="U33" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V33" t="n">
         <v>1.22</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
         <v>1.09</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
         <v>1.4</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
         <v>1.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
         <v>1.75</v>
@@ -7210,7 +7210,7 @@
         <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X35" t="n">
         <v>18.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>2.42</v>
       </c>
       <c r="G36" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H36" t="n">
         <v>2.92</v>
@@ -7404,7 +7404,7 @@
         <v>1.4</v>
       </c>
       <c r="W36" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X36" t="n">
         <v>14</v>
@@ -7476,7 +7476,7 @@
         <v>7.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV36" t="n">
         <v>10.5</v>
@@ -7488,7 +7488,7 @@
         <v>12.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ36" t="n">
         <v>4.1</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.08</v>
       </c>
       <c r="G37" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="H37" t="n">
         <v>3.45</v>
@@ -7586,13 +7586,13 @@
         <v>1.26</v>
       </c>
       <c r="S37" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T37" t="n">
         <v>1.58</v>
       </c>
       <c r="U37" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V37" t="n">
         <v>1.28</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I38" t="n">
         <v>5.1</v>
       </c>
       <c r="J38" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="K38" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
         <v>1.55</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
         <v>1.06</v>
       </c>
       <c r="P39" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q39" t="n">
         <v>1.86</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
         <v>4.7</v>
       </c>
       <c r="O41" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P41" t="n">
         <v>2.3</v>
@@ -8362,7 +8362,7 @@
         <v>1.51</v>
       </c>
       <c r="S41" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T41" t="n">
         <v>1.86</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="G42" t="n">
         <v>3.25</v>
       </c>
       <c r="H42" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="I42" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J42" t="n">
         <v>3.75</v>
@@ -8544,7 +8544,7 @@
         <v>2.44</v>
       </c>
       <c r="O42" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P42" t="n">
         <v>2.42</v>
@@ -8556,7 +8556,7 @@
         <v>1.57</v>
       </c>
       <c r="S42" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -8565,7 +8565,7 @@
         <v>1.01</v>
       </c>
       <c r="V42" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W42" t="n">
         <v>1.44</v>
@@ -8577,25 +8577,25 @@
         <v>22</v>
       </c>
       <c r="Z42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA42" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB42" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC42" t="n">
         <v>14.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE42" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF42" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG42" t="n">
         <v>20</v>
@@ -8607,10 +8607,10 @@
         <v>44</v>
       </c>
       <c r="AJ42" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK42" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL42" t="n">
         <v>48</v>
@@ -8628,7 +8628,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="AR42" t="n">
         <v>2.04</v>
@@ -8649,7 +8649,7 @@
         <v>2.06</v>
       </c>
       <c r="AX42" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AY42" t="n">
         <v>1.98</v>
@@ -8661,10 +8661,10 @@
         <v>2.1</v>
       </c>
       <c r="BB42" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BD42" t="n">
         <v>2.1</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -8738,7 +8738,7 @@
         <v>1.54</v>
       </c>
       <c r="O43" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P43" t="n">
         <v>1.54</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
         <v>1.09</v>
       </c>
       <c r="N44" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
         <v>1.38</v>
@@ -8938,7 +8938,7 @@
         <v>1.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R44" t="n">
         <v>1.27</v>
@@ -8968,7 +8968,7 @@
         <v>16.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB44" t="n">
         <v>11.5</v>
@@ -9010,65 +9010,65 @@
         <v>55</v>
       </c>
       <c r="AO44" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP44" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ44" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR44" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW44" t="n">
         <v>7</v>
       </c>
-      <c r="AT44" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW44" t="n">
+      <c r="AX44" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX44" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AY44" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AZ44" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA44" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB44" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC44" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD44" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG44" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="G45" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H45" t="n">
         <v>1.43</v>
@@ -9147,7 +9147,7 @@
         <v>2.14</v>
       </c>
       <c r="V45" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="W45" t="n">
         <v>1.13</v>
@@ -9171,7 +9171,7 @@
         <v>12.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE45" t="n">
         <v>13.5</v>
@@ -9180,7 +9180,7 @@
         <v>75</v>
       </c>
       <c r="AG45" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH45" t="n">
         <v>22</v>
@@ -9189,7 +9189,7 @@
         <v>28</v>
       </c>
       <c r="AJ45" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AK45" t="n">
         <v>110</v>
@@ -9207,7 +9207,7 @@
         <v>5.4</v>
       </c>
       <c r="AP45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ45" t="n">
         <v>10</v>
@@ -9225,13 +9225,13 @@
         <v>11</v>
       </c>
       <c r="AV45" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW45" t="n">
         <v>12.5</v>
       </c>
       <c r="AX45" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AY45" t="n">
         <v>27</v>
@@ -9243,26 +9243,26 @@
         <v>27</v>
       </c>
       <c r="BB45" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BC45" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BD45" t="n">
         <v>55</v>
       </c>
       <c r="BE45" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="BF45" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BG45" t="n">
         <v>5.1</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
         <v>1.72</v>
       </c>
       <c r="P46" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q46" t="n">
         <v>3.2</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -9487,19 +9487,19 @@
         </is>
       </c>
       <c r="F47" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J47" t="n">
         <v>2.66</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H47" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.62</v>
       </c>
       <c r="K47" t="n">
         <v>2.86</v>
@@ -9532,13 +9532,13 @@
         <v>2.46</v>
       </c>
       <c r="U47" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V47" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W47" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X47" t="n">
         <v>6.2</v>
@@ -9547,7 +9547,7 @@
         <v>8.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA47" t="n">
         <v>100</v>
@@ -9565,7 +9565,7 @@
         <v>95</v>
       </c>
       <c r="AF47" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG47" t="n">
         <v>17</v>
@@ -9589,13 +9589,13 @@
         <v>400</v>
       </c>
       <c r="AN47" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AO47" t="n">
         <v>150</v>
       </c>
       <c r="AP47" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ47" t="n">
         <v>7.4</v>
@@ -9604,7 +9604,7 @@
         <v>19.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT47" t="n">
         <v>5.9</v>
@@ -9616,7 +9616,7 @@
         <v>16.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX47" t="n">
         <v>14</v>
@@ -9628,29 +9628,29 @@
         <v>26</v>
       </c>
       <c r="BA47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB47" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC47" t="n">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BD47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG47" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF47" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
         <v>60</v>
       </c>
       <c r="AJ48" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK48" t="n">
         <v>50</v>
@@ -9831,20 +9831,20 @@
         <v>36</v>
       </c>
       <c r="BD48" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE48" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF48" t="n">
         <v>44</v>
       </c>
       <c r="BG48" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
         <v>1.87</v>
       </c>
       <c r="G49" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H49" t="n">
         <v>4</v>
@@ -9896,13 +9896,13 @@
         <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P49" t="n">
         <v>2.02</v>
@@ -9917,16 +9917,16 @@
         <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="U49" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="V49" t="n">
         <v>1.26</v>
       </c>
       <c r="W49" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X49" t="n">
         <v>20</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -10108,10 +10108,10 @@
         <v>1.64</v>
       </c>
       <c r="S50" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T50" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U50" t="n">
         <v>2.3</v>
@@ -10132,7 +10132,7 @@
         <v>12</v>
       </c>
       <c r="AA50" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AB50" t="n">
         <v>27</v>
@@ -10153,7 +10153,7 @@
         <v>23</v>
       </c>
       <c r="AH50" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI50" t="n">
         <v>27</v>
@@ -10162,19 +10162,19 @@
         <v>150</v>
       </c>
       <c r="AK50" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL50" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM50" t="n">
         <v>75</v>
       </c>
       <c r="AN50" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO50" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP50" t="n">
         <v>22</v>
@@ -10201,7 +10201,7 @@
         <v>11</v>
       </c>
       <c r="AX50" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY50" t="n">
         <v>18.5</v>
@@ -10210,29 +10210,29 @@
         <v>16</v>
       </c>
       <c r="BA50" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB50" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC50" t="n">
         <v>11</v>
       </c>
-      <c r="BC50" t="n">
-        <v>48</v>
-      </c>
       <c r="BD50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE50" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG50" t="n">
         <v>5.6</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH51"/>
+  <dimension ref="A1:BH52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.39</v>
@@ -787,10 +787,10 @@
         <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
@@ -799,16 +799,16 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.05</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.05</v>
+        <v>1.97</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -823,19 +823,19 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K3" t="n">
         <v>3.25</v>
@@ -978,7 +978,7 @@
         <v>2.96</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
         <v>1.6</v>
@@ -996,7 +996,7 @@
         <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>1.53</v>
@@ -1014,10 +1014,10 @@
         <v>980</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>6.8</v>
@@ -1059,19 +1059,19 @@
         <v>980</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU3" t="n">
         <v>5.8</v>
@@ -1083,25 +1083,25 @@
         <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6</v>
-      </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE3" t="n">
         <v>6.6</v>
@@ -1110,11 +1110,11 @@
         <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>2.28</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.91</v>
+        <v>1.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
         <v>980</v>
@@ -1444,65 +1444,65 @@
         <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>1.38</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.85</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>1.24</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>1.29</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.5</v>
+        <v>1.38</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.3</v>
+        <v>1.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>1.29</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>1.26</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.95</v>
+        <v>1.38</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.75</v>
+        <v>1.38</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>1.29</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.5</v>
+        <v>1.24</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>1.26</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>1.29</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.3</v>
+        <v>1.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>1.22</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1533,55 +1533,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G6" t="n">
         <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
         <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>2.24</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
         <v>2.02</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.24</v>
       </c>
       <c r="I7" t="n">
         <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
         <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.05</v>
       </c>
       <c r="V7" t="n">
         <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
         <v>980</v>
@@ -1814,7 +1814,7 @@
         <v>980</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>60</v>
@@ -1835,40 +1835,40 @@
         <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.49</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AT7" t="n">
         <v>1.49</v>
       </c>
       <c r="AU7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1.37</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.5</v>
       </c>
       <c r="AW7" t="n">
         <v>1.34</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AY7" t="n">
         <v>1.49</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BB7" t="n">
         <v>1.34</v>
@@ -1877,20 +1877,20 @@
         <v>1.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BE7" t="n">
         <v>1.37</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.22</v>
+        <v>1.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.22</v>
+        <v>1.34</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
         <v>980</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
         <v>980</v>
@@ -1987,10 +1987,10 @@
         <v>980</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>980</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>980</v>
       </c>
       <c r="AD8" t="n">
         <v>980</v>
@@ -2029,62 +2029,62 @@
         <v>980</v>
       </c>
       <c r="AP8" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.9</v>
+        <v>1.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>2.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>2.38</v>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>2.36</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>2.32</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.4</v>
+        <v>2.32</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.2</v>
+        <v>2.28</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>2.36</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.1</v>
+        <v>2.36</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2139,16 +2139,16 @@
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
         <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
@@ -2160,7 +2160,7 @@
         <v>1.96</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
         <v>1.52</v>
@@ -2229,7 +2229,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
         <v>9</v>
@@ -2241,7 +2241,7 @@
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW9" t="n">
         <v>26</v>
@@ -2253,7 +2253,7 @@
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA9" t="n">
         <v>9.4</v>
@@ -2262,10 +2262,10 @@
         <v>9.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE9" t="n">
         <v>10.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
@@ -2342,13 +2342,13 @@
         <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
         <v>1.55</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="T10" t="n">
         <v>1.55</v>
@@ -2360,7 +2360,7 @@
         <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
         <v>27</v>
@@ -2405,7 +2405,7 @@
         <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>70</v>
@@ -2426,7 +2426,7 @@
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
         <v>13</v>
@@ -2450,10 +2450,10 @@
         <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -2462,7 +2462,7 @@
         <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
         <v>11</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
         <v>2.58</v>
@@ -2515,10 +2515,10 @@
         <v>2.82</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2554,7 +2554,7 @@
         <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
         <v>26</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.33</v>
@@ -2727,28 +2727,28 @@
         <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="X12" t="n">
         <v>980</v>
@@ -2805,7 +2805,7 @@
         <v>95</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.1</v>
@@ -2820,10 +2820,10 @@
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW12" t="n">
         <v>4.7</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2897,10 @@
         <v>1.92</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.75</v>
@@ -2933,13 +2933,13 @@
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>2.08</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
         <v>1.83</v>
@@ -3094,10 +3094,10 @@
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>4.5</v>
@@ -3127,13 +3127,13 @@
         <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
         <v>2.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
         <v>1.31</v>
       </c>
       <c r="G15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="I15" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,22 +3303,22 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.25</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
         <v>1.05</v>
@@ -3333,61 +3333,61 @@
         <v>3.85</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>14.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.55</v>
+        <v>3.15</v>
       </c>
       <c r="AQ15" t="n">
         <v>30</v>
@@ -3399,10 +3399,10 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.49</v>
+        <v>4.9</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="AV15" t="n">
         <v>4.2</v>
@@ -3411,38 +3411,38 @@
         <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.47</v>
+        <v>3.85</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.48</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.49</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.55</v>
+        <v>13.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.58</v>
+        <v>3.35</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.43</v>
+        <v>2.88</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="G17" t="n">
         <v>1.46</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>710</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3694,7 +3694,7 @@
         <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
         <v>2.16</v>
@@ -3706,13 +3706,13 @@
         <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T17" t="n">
         <v>1.89</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
         <v>1.07</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
         <v>3.35</v>
@@ -3870,34 +3870,34 @@
         <v>2.8</v>
       </c>
       <c r="I18" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
         <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.52</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
         <v>5.1</v>
@@ -3906,7 +3906,7 @@
         <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V18" t="n">
         <v>1.51</v>
@@ -3915,13 +3915,13 @@
         <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Y18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA18" t="n">
         <v>980</v>
@@ -3933,10 +3933,10 @@
         <v>6.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AF18" t="n">
         <v>980</v>
@@ -3972,59 +3972,59 @@
         <v>7.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT18" t="n">
         <v>8.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV18" t="n">
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC18" t="n">
         <v>40</v>
       </c>
       <c r="BD18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4067,16 +4067,16 @@
         <v>2.32</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
         <v>3.1</v>
@@ -4085,10 +4085,10 @@
         <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
         <v>1.26</v>
@@ -4187,7 +4187,7 @@
         <v>5.8</v>
       </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY19" t="n">
         <v>14</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
         <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>1.45</v>
@@ -4294,7 +4294,7 @@
         <v>1.84</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
         <v>1.73</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4443,59 +4443,59 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W21" t="n">
         <v>2.06</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X21" t="n">
         <v>1000</v>
       </c>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>6.4</v>
       </c>
       <c r="G22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
         <v>1.55</v>
       </c>
       <c r="I22" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
         <v>1.26</v>
@@ -4667,7 +4667,7 @@
         <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
         <v>1.58</v>
@@ -4679,7 +4679,7 @@
         <v>2.44</v>
       </c>
       <c r="T22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
         <v>2.24</v>
@@ -4688,7 +4688,7 @@
         <v>2.74</v>
       </c>
       <c r="W22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X22" t="n">
         <v>24</v>
@@ -4700,10 +4700,10 @@
         <v>11.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AB22" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC22" t="n">
         <v>11</v>
@@ -4718,7 +4718,7 @@
         <v>60</v>
       </c>
       <c r="AG22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH22" t="n">
         <v>19</v>
@@ -4736,13 +4736,13 @@
         <v>75</v>
       </c>
       <c r="AM22" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN22" t="n">
         <v>75</v>
       </c>
       <c r="AO22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP22" t="n">
         <v>20</v>
@@ -4757,10 +4757,10 @@
         <v>13</v>
       </c>
       <c r="AT22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV22" t="n">
         <v>9.4</v>
@@ -4769,10 +4769,10 @@
         <v>13</v>
       </c>
       <c r="AX22" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ22" t="n">
         <v>17</v>
@@ -4781,16 +4781,16 @@
         <v>22</v>
       </c>
       <c r="BB22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC22" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>11.5</v>
       </c>
       <c r="BD22" t="n">
         <v>55</v>
       </c>
       <c r="BE22" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF22" t="n">
         <v>48</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="G23" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H23" t="n">
         <v>3.25</v>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,76 +4855,76 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="O23" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="P23" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
         <v>2.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V23" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4933,68 +4933,68 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5016,67 +5016,67 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>SS Virtus Verona 1921</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inter Milan (Res)</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H24" t="n">
-        <v>2.76</v>
+        <v>2.24</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J24" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="O24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P24" t="n">
         <v>1.35</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q24" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="V24" t="n">
-        <v>1.12</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5210,31 +5210,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SS Virtus Verona 1921</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Inter Milan (Res)</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.28</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="I25" t="n">
-        <v>110</v>
+        <v>3.55</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,22 +5243,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="O25" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H26" t="n">
         <v>2.98</v>
@@ -5446,7 +5446,7 @@
         <v>2.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R26" t="n">
         <v>1.6</v>
@@ -5458,7 +5458,7 @@
         <v>1.56</v>
       </c>
       <c r="U26" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V26" t="n">
         <v>1.5</v>
@@ -5473,7 +5473,7 @@
         <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA26" t="n">
         <v>46</v>
@@ -5518,7 +5518,7 @@
         <v>14</v>
       </c>
       <c r="AO26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>19.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.64</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.65</v>
       </c>
       <c r="H27" t="n">
         <v>6.4</v>
@@ -5646,22 +5646,22 @@
         <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V27" t="n">
         <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
         <v>21</v>
@@ -5691,7 +5691,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>95</v>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="AL27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM27" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO27" t="n">
         <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>19.5</v>
@@ -5727,7 +5727,7 @@
         <v>55</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
         <v>8.800000000000001</v>
@@ -5736,10 +5736,10 @@
         <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY27" t="n">
         <v>9.6</v>
@@ -5766,11 +5766,11 @@
         <v>9</v>
       </c>
       <c r="BG27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
         <v>2.02</v>
@@ -5813,10 +5813,10 @@
         <v>4.5</v>
       </c>
       <c r="J28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.65</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.47</v>
@@ -5831,7 +5831,7 @@
         <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q28" t="n">
         <v>2.16</v>
@@ -5843,7 +5843,7 @@
         <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
         <v>1.98</v>
@@ -5852,7 +5852,7 @@
         <v>1.28</v>
       </c>
       <c r="W28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="X28" t="n">
         <v>12</v>
@@ -5885,13 +5885,13 @@
         <v>10.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK28" t="n">
         <v>22</v>
@@ -5942,13 +5942,13 @@
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD28" t="n">
         <v>38</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
         <v>2.76</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6216,19 +6216,19 @@
         <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,73 +6374,73 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Barry Town Utd</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ayr</t>
+          <t>Penybont FC</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.44</v>
+        <v>1.62</v>
       </c>
       <c r="G31" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="H31" t="n">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="I31" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>980</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>1.24</v>
       </c>
       <c r="O31" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>3.55</v>
+        <v>1.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
         <v>1000</v>
@@ -6449,28 +6449,28 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
         <v>1000</v>
@@ -6479,74 +6479,74 @@
         <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Barry Town Utd</t>
+          <t>Connahs Quay</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Penybont FC</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.62</v>
+        <v>4.8</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72</v>
+        <v>6.2</v>
       </c>
       <c r="H32" t="n">
-        <v>2.54</v>
+        <v>1.75</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>1.77</v>
       </c>
       <c r="J32" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="K32" t="n">
-        <v>980</v>
+        <v>4.3</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="P32" t="n">
-        <v>1.18</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>1.3</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="W32" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ32" t="n">
         <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,179 +6762,179 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Connahs Quay</t>
+          <t>Dundee Utd</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>St Mirren</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="G33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA33" t="n">
         <v>6.4</v>
       </c>
-      <c r="H33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V33" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BB33" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE33" t="n">
         <v>7</v>
       </c>
       <c r="BF33" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6971,164 +6971,164 @@
         <v>1.65</v>
       </c>
       <c r="H34" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="I34" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K34" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="L34" t="n">
         <v>1.32</v>
       </c>
       <c r="M34" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>1.83</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P34" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W34" t="n">
         <v>2.54</v>
       </c>
-      <c r="T34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.56</v>
-      </c>
       <c r="X34" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y34" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD34" t="n">
         <v>32</v>
       </c>
-      <c r="Z34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="AE34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG34" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH34" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AK34" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.86</v>
+        <v>4.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.94</v>
+        <v>5.1</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.74</v>
+        <v>4.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="AX34" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="BB34" t="n">
-        <v>2.58</v>
+        <v>3.95</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.78</v>
+        <v>4.6</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="BF34" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>2.94</v>
+        <v>5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
         <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T35" t="n">
         <v>1.81</v>
@@ -7267,7 +7267,7 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ35" t="n">
         <v>2.56</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -7344,103 +7344,103 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ross Co</t>
+          <t>Ayr</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="G36" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="J36" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O36" t="n">
         <v>1.37</v>
       </c>
-      <c r="M36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.41</v>
-      </c>
       <c r="P36" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R36" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V36" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W36" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ36" t="n">
         <v>1000</v>
@@ -7449,81 +7449,81 @@
         <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP36" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AR36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC36" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA36" t="n">
+      <c r="BD36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE36" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BF36" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG36" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7538,179 +7538,179 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>Ross Co</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="G37" t="n">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="H37" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="K37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ37" t="n">
         <v>4.2</v>
       </c>
-      <c r="L37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="X37" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>14</v>
-      </c>
       <c r="BA37" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BC37" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BF37" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.76</v>
       </c>
       <c r="G38" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H38" t="n">
         <v>2.3</v>
@@ -7765,10 +7765,10 @@
         <v>1.03</v>
       </c>
       <c r="N38" t="n">
-        <v>2.44</v>
+        <v>5.2</v>
       </c>
       <c r="O38" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P38" t="n">
         <v>2.44</v>
@@ -7780,131 +7780,131 @@
         <v>1.58</v>
       </c>
       <c r="S38" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V38" t="n">
         <v>1.64</v>
       </c>
       <c r="W38" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X38" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI38" t="n">
         <v>36</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AJ38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN38" t="n">
         <v>22</v>
       </c>
-      <c r="Z38" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG38" t="n">
+      <c r="AO38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP38" t="n">
         <v>20</v>
       </c>
-      <c r="AH38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AQ38" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.06</v>
+        <v>16</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.12</v>
+        <v>3.9</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.04</v>
+        <v>12.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.93</v>
+        <v>8.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.98</v>
+        <v>10</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.08</v>
+        <v>19</v>
       </c>
       <c r="AX38" t="n">
-        <v>2.08</v>
+        <v>20</v>
       </c>
       <c r="AY38" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2.02</v>
+        <v>11</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="BB38" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.12</v>
+        <v>3.9</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="BF38" t="n">
-        <v>2.22</v>
+        <v>13</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G39" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="H39" t="n">
         <v>3.5</v>
@@ -7953,16 +7953,16 @@
         <v>3.85</v>
       </c>
       <c r="L39" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M39" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="O39" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P39" t="n">
         <v>1.84</v>
@@ -7971,134 +7971,134 @@
         <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S39" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="T39" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="U39" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="V39" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W39" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC39" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z39" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BD39" t="n">
-        <v>2.22</v>
+        <v>4.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF39" t="n">
-        <v>2.3</v>
+        <v>14</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="G40" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="H40" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="J40" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K40" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
         <v>1.25</v>
       </c>
       <c r="G42" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H42" t="n">
         <v>17.5</v>
@@ -8547,10 +8547,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -8714,28 +8714,28 @@
         <v>1.31</v>
       </c>
       <c r="G43" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H43" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I43" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J43" t="n">
         <v>5.3</v>
       </c>
       <c r="K43" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="L43" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M43" t="n">
         <v>1.03</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
         <v>1.21</v>
@@ -8750,19 +8750,19 @@
         <v>1.51</v>
       </c>
       <c r="S43" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T43" t="n">
         <v>2.02</v>
       </c>
       <c r="U43" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="V43" t="n">
         <v>1.08</v>
       </c>
       <c r="W43" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X43" t="n">
         <v>980</v>
@@ -8825,7 +8825,7 @@
         <v>4.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AS43" t="n">
         <v>3.45</v>
@@ -8834,7 +8834,7 @@
         <v>3.45</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV43" t="n">
         <v>4.6</v>
@@ -8849,16 +8849,16 @@
         <v>3.45</v>
       </c>
       <c r="AZ43" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA43" t="n">
         <v>3</v>
       </c>
       <c r="BB43" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD43" t="n">
         <v>4.5</v>
@@ -8874,14 +8874,14 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8891,191 +8891,191 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="I44" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="K44" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M44" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>1.54</v>
+        <v>4</v>
       </c>
       <c r="O44" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="P44" t="n">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="R44" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="S44" t="n">
-        <v>2.04</v>
+        <v>2.98</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V44" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W44" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9090,186 +9090,186 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="G45" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="H45" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="I45" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J45" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="K45" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L45" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M45" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="O45" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P45" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="Q45" t="n">
         <v>2.04</v>
       </c>
       <c r="R45" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S45" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T45" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U45" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V45" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="W45" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X45" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y45" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AA45" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD45" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AE45" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AF45" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AG45" t="n">
         <v>14.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AI45" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AK45" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AL45" t="n">
         <v>60</v>
       </c>
       <c r="AM45" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AO45" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="AQ45" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="AR45" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="AS45" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT45" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="AU45" t="n">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="AV45" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="AW45" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX45" t="n">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="AY45" t="n">
-        <v>5.6</v>
+        <v>3.35</v>
       </c>
       <c r="AZ45" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="BA45" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BB45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BC45" t="n">
-        <v>7.8</v>
+        <v>3.95</v>
       </c>
       <c r="BD45" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="BF45" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="BG45" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9279,191 +9279,191 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC46" t="n">
         <v>7.8</v>
       </c>
-      <c r="G46" t="n">
-        <v>8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="AD46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY46" t="n">
         <v>5.5</v>
       </c>
-      <c r="K46" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N46" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X46" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>29</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>60</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>27</v>
-      </c>
       <c r="AZ46" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BA46" t="n">
-        <v>27</v>
+        <v>7.6</v>
       </c>
       <c r="BB46" t="n">
-        <v>95</v>
+        <v>7.8</v>
       </c>
       <c r="BC46" t="n">
-        <v>85</v>
+        <v>7.4</v>
       </c>
       <c r="BD46" t="n">
-        <v>75</v>
+        <v>7.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>90</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF46" t="n">
-        <v>80</v>
+        <v>7.6</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9473,184 +9473,184 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sarmiento de Junin</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U47" t="n">
         <v>2.16</v>
       </c>
-      <c r="G47" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R47" t="n">
+      <c r="V47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W47" t="n">
         <v>1.13</v>
       </c>
-      <c r="S47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.73</v>
-      </c>
       <c r="X47" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="Y47" t="n">
         <v>11</v>
       </c>
       <c r="Z47" t="n">
-        <v>38</v>
+        <v>9.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>150</v>
+        <v>12.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AD47" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>29</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>60</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA47" t="n">
         <v>26</v>
       </c>
-      <c r="AE47" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BB47" t="n">
-        <v>5.2</v>
+        <v>70</v>
       </c>
       <c r="BC47" t="n">
-        <v>5.4</v>
+        <v>85</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.8</v>
+        <v>75</v>
       </c>
       <c r="BE47" t="n">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.4</v>
+        <v>80</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -9667,184 +9667,184 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Sarmiento de Junin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.64</v>
+        <v>2.16</v>
       </c>
       <c r="G48" t="n">
-        <v>2.86</v>
+        <v>2.36</v>
       </c>
       <c r="H48" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="I48" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="J48" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="K48" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="M48" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="N48" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O48" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="P48" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="T48" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U48" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V48" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W48" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="X48" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="Y48" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AA48" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AB48" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AE48" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF48" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI48" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ48" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AK48" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AL48" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM48" t="n">
         <v>380</v>
       </c>
       <c r="AN48" t="n">
-        <v>75</v>
+        <v>980</v>
       </c>
       <c r="AO48" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AP48" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AQ48" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR48" t="n">
         <v>19.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT48" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="AU48" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV48" t="n">
         <v>16.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AX48" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY48" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ48" t="n">
-        <v>26</v>
+        <v>5.6</v>
       </c>
       <c r="BA48" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB48" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC48" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD48" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF48" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BG48" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -9861,191 +9861,191 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>21:15:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Atl Tucuman</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="G49" t="n">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="H49" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="I49" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="K49" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="N49" t="n">
-        <v>2.86</v>
+        <v>2.12</v>
       </c>
       <c r="O49" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="P49" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="S49" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="T49" t="n">
-        <v>1.97</v>
+        <v>2.46</v>
       </c>
       <c r="U49" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="V49" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="W49" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="X49" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AA49" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AB49" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD49" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="AF49" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AH49" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AI49" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AJ49" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK49" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AL49" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AM49" t="n">
-        <v>170</v>
+        <v>380</v>
       </c>
       <c r="AN49" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AO49" t="n">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="AP49" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ49" t="n">
         <v>7.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT49" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB49" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV49" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ49" t="n">
+      <c r="BC49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE49" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA49" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF49" t="n">
-        <v>44</v>
+        <v>6.8</v>
       </c>
       <c r="BG49" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10055,184 +10055,184 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:15:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pachuca</t>
+          <t>Atl Tucuman</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Necaxa</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.87</v>
+        <v>3.45</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="H50" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="J50" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M50" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="O50" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="P50" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R50" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S50" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="T50" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="U50" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="V50" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="W50" t="n">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="X50" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AB50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC50" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD50" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AF50" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AG50" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AH50" t="n">
         <v>21</v>
       </c>
       <c r="AI50" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN50" t="n">
         <v>60</v>
       </c>
-      <c r="AJ50" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL50" t="n">
+      <c r="AO50" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC50" t="n">
         <v>36</v>
       </c>
-      <c r="AM50" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX50" t="n">
+      <c r="BD50" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE50" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY50" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF50" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG50" t="n">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -10254,179 +10254,373 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Necaxa</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W51" t="n">
+        <v>2</v>
+      </c>
+      <c r="X51" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>2026-03-02 07:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>Santos Laguna</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Cruz Azul</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F52" t="n">
         <v>5.5</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G52" t="n">
         <v>6.4</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H52" t="n">
         <v>1.56</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I52" t="n">
         <v>1.65</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J52" t="n">
         <v>4.6</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K52" t="n">
         <v>5.1</v>
       </c>
-      <c r="L51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M51" t="n">
+      <c r="L52" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M52" t="n">
         <v>1.03</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N52" t="n">
         <v>5.5</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O52" t="n">
         <v>1.18</v>
       </c>
-      <c r="P51" t="n">
+      <c r="P52" t="n">
         <v>2.56</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q52" t="n">
         <v>1.55</v>
       </c>
-      <c r="R51" t="n">
+      <c r="R52" t="n">
         <v>1.62</v>
       </c>
-      <c r="S51" t="n">
+      <c r="S52" t="n">
         <v>2.38</v>
       </c>
-      <c r="T51" t="n">
+      <c r="T52" t="n">
         <v>1.64</v>
       </c>
-      <c r="U51" t="n">
+      <c r="U52" t="n">
         <v>2.3</v>
       </c>
-      <c r="V51" t="n">
+      <c r="V52" t="n">
         <v>2.54</v>
       </c>
-      <c r="W51" t="n">
+      <c r="W52" t="n">
         <v>1.18</v>
       </c>
-      <c r="X51" t="n">
+      <c r="X52" t="n">
         <v>32</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Y52" t="n">
         <v>14</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="Z52" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AA52" t="n">
         <v>970</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AB52" t="n">
         <v>28</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AC52" t="n">
         <v>12</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AD52" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE51" t="n">
+      <c r="AE52" t="n">
         <v>15.5</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AF52" t="n">
         <v>60</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AG52" t="n">
         <v>23</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AH52" t="n">
         <v>970</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AI52" t="n">
         <v>27</v>
       </c>
-      <c r="AJ51" t="n">
+      <c r="AJ52" t="n">
         <v>150</v>
       </c>
-      <c r="AK51" t="n">
+      <c r="AK52" t="n">
         <v>65</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AL52" t="n">
         <v>60</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AM52" t="n">
         <v>75</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AN52" t="n">
         <v>55</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AO52" t="n">
         <v>6.2</v>
       </c>
-      <c r="AP51" t="n">
+      <c r="AP52" t="n">
         <v>22</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AQ52" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AR52" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS51" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>23</v>
-      </c>
-      <c r="AU51" t="n">
+      <c r="AS52" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU52" t="n">
         <v>10</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AV52" t="n">
         <v>9</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AW52" t="n">
         <v>13</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="AX52" t="n">
         <v>9</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="AY52" t="n">
         <v>19.5</v>
       </c>
-      <c r="AZ51" t="n">
+      <c r="AZ52" t="n">
         <v>16</v>
       </c>
-      <c r="BA51" t="n">
+      <c r="BA52" t="n">
         <v>19.5</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BB52" t="n">
         <v>10</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BC52" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BD52" t="n">
         <v>9</v>
       </c>
-      <c r="BE51" t="n">
+      <c r="BE52" t="n">
         <v>9.4</v>
       </c>
-      <c r="BF51" t="n">
+      <c r="BF52" t="n">
         <v>40</v>
       </c>
-      <c r="BG51" t="n">
+      <c r="BG52" t="n">
         <v>5</v>
       </c>
-      <c r="BH51" t="inlineStr">
-        <is>
-          <t>2026-03-02 05:39:39</t>
+      <c r="BH52" t="inlineStr">
+        <is>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,34 +781,34 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
         <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>14.5</v>
@@ -838,7 +838,7 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -847,7 +847,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
         <v>1000</v>
@@ -871,16 +871,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
@@ -889,38 +889,38 @@
         <v>32</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
         <v>30</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
         <v>3.35</v>
@@ -966,7 +966,7 @@
         <v>2.76</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
@@ -993,7 +993,7 @@
         <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
         <v>1.96</v>
@@ -1059,7 +1059,7 @@
         <v>980</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.6</v>
@@ -1089,7 +1089,7 @@
         <v>5.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BA3" t="n">
         <v>3.95</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
@@ -1190,91 +1190,91 @@
         <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>980</v>
       </c>
       <c r="Y4" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AA4" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AB4" t="n">
         <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF4" t="n">
         <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AI4" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>980</v>
       </c>
       <c r="AL4" t="n">
         <v>980</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN4" t="n">
         <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.7</v>
+        <v>50</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
@@ -1283,10 +1283,10 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>10.5</v>
@@ -1295,20 +1295,20 @@
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
         <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -1351,7 +1351,7 @@
         <v>3.65</v>
       </c>
       <c r="J5" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
@@ -1363,19 +1363,19 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>4.1</v>
@@ -1390,7 +1390,7 @@
         <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X5" t="n">
         <v>980</v>
@@ -1426,7 +1426,7 @@
         <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
         <v>980</v>
@@ -1447,62 +1447,62 @@
         <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX5" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="AY5" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC5" t="n">
         <v>3.1</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BD5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
@@ -1563,7 +1563,7 @@
         <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
         <v>2.24</v>
@@ -1578,7 +1578,7 @@
         <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
         <v>8.6</v>
@@ -1617,7 +1617,7 @@
         <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV6" t="n">
         <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD6" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
         <v>12.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.52</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H7" t="n">
         <v>3.05</v>
@@ -1793,7 +1793,7 @@
         <v>90</v>
       </c>
       <c r="AB7" t="n">
-        <v>980</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
         <v>1000</v>
@@ -1859,7 +1859,7 @@
         <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AY7" t="n">
         <v>3.7</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>2.82</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K8" t="n">
         <v>3.45</v>
@@ -1969,7 +1969,7 @@
         <v>1.68</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
         <v>1.46</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2124,13 +2124,13 @@
         <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2145,7 +2145,7 @@
         <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
         <v>1.64</v>
@@ -2157,7 +2157,7 @@
         <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
         <v>2.52</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
         <v>1.6</v>
@@ -2363,13 +2363,13 @@
         <v>1.65</v>
       </c>
       <c r="X10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
         <v>50</v>
@@ -2378,34 +2378,34 @@
         <v>17</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
         <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="n">
         <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI10" t="n">
         <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
         <v>70</v>
@@ -2414,7 +2414,7 @@
         <v>15.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
         <v>19.5</v>
@@ -2423,10 +2423,10 @@
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="AT10" t="n">
         <v>12.5</v>
@@ -2438,7 +2438,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="AX10" t="n">
         <v>16.5</v>
@@ -2450,19 +2450,19 @@
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>42</v>
       </c>
       <c r="BF10" t="n">
         <v>11.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="n">
         <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
         <v>2.98</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -2530,10 +2530,10 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
         <v>2.36</v>
@@ -2542,10 +2542,10 @@
         <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
         <v>1.96</v>
@@ -2560,19 +2560,19 @@
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z11" t="n">
         <v>20</v>
       </c>
       <c r="AA11" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD11" t="n">
         <v>13.5</v>
@@ -2611,7 +2611,7 @@
         <v>46</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.6</v>
@@ -2620,7 +2620,7 @@
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2632,7 +2632,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>17</v>
@@ -2641,32 +2641,32 @@
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2697,40 +2697,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="G12" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="H12" t="n">
         <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R12" t="n">
         <v>1.31</v>
@@ -2739,16 +2739,16 @@
         <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
         <v>1.86</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="X12" t="n">
         <v>980</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AR12" t="n">
         <v>3.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AV12" t="n">
         <v>2.58</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AX12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AY12" t="n">
         <v>2.38</v>
       </c>
-      <c r="AY12" t="n">
-        <v>2.36</v>
-      </c>
       <c r="AZ12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BB12" t="n">
         <v>2.56</v>
       </c>
-      <c r="BA12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>2.54</v>
-      </c>
       <c r="BC12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BF12" t="n">
         <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.79</v>
       </c>
       <c r="G13" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="H13" t="n">
         <v>4.5</v>
@@ -2906,7 +2906,7 @@
         <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2933,16 +2933,16 @@
         <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
         <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X13" t="n">
         <v>20</v>
@@ -2951,7 +2951,7 @@
         <v>23</v>
       </c>
       <c r="Z13" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA13" t="n">
         <v>130</v>
@@ -2963,10 +2963,10 @@
         <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
         <v>15</v>
@@ -2996,7 +2996,7 @@
         <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP13" t="n">
         <v>15.5</v>
@@ -3005,10 +3005,10 @@
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3041,20 +3041,20 @@
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF13" t="n">
         <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3121,46 +3121,46 @@
         <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y14" t="n">
         <v>26</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
         <v>13.5</v>
@@ -3169,10 +3169,10 @@
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
         <v>19</v>
@@ -3181,10 +3181,10 @@
         <v>17</v>
       </c>
       <c r="AL14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN14" t="n">
         <v>7.8</v>
@@ -3199,10 +3199,10 @@
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3229,7 +3229,7 @@
         <v>40</v>
       </c>
       <c r="BB14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
         <v>13.5</v>
@@ -3238,17 +3238,17 @@
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
         <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
         <v>1.19</v>
       </c>
       <c r="T15" t="n">
-        <v>1.05</v>
+        <v>1.78</v>
       </c>
       <c r="U15" t="n">
         <v>1.05</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>1.19</v>
       </c>
       <c r="G16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="H16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
         <v>12.5</v>
@@ -3497,7 +3497,7 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.11</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
         <v>1.11</v>
@@ -3524,40 +3524,40 @@
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="X16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
@@ -3566,13 +3566,13 @@
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
         <v>3.3</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.22</v>
+        <v>1.53</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.26</v>
+        <v>1.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.26</v>
+        <v>1.28</v>
       </c>
       <c r="AT16" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>15.5</v>
+        <v>3.45</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.8</v>
+        <v>1.16</v>
       </c>
       <c r="AW16" t="n">
         <v>6.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.2</v>
+        <v>1.28</v>
       </c>
       <c r="BA16" t="n">
         <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.14</v>
+        <v>1.28</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.26</v>
+        <v>1.31</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.22</v>
+        <v>1.18</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H17" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
         <v>3.85</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,34 +3691,34 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>1.12</v>
       </c>
       <c r="P17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U17" t="n">
         <v>3.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.15</v>
       </c>
       <c r="V17" t="n">
         <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="X17" t="n">
         <v>980</v>
@@ -3736,28 +3736,28 @@
         <v>21</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>18.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AF17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
         <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK17" t="n">
         <v>18</v>
@@ -3772,7 +3772,7 @@
         <v>6.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP17" t="n">
         <v>15.5</v>
@@ -3784,53 +3784,53 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU17" t="n">
         <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>7.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>7.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3876,16 +3876,16 @@
         <v>5.1</v>
       </c>
       <c r="K18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
@@ -3894,19 +3894,19 @@
         <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="V18" t="n">
         <v>1.1</v>
@@ -3918,7 +3918,7 @@
         <v>19.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z18" t="n">
         <v>110</v>
@@ -3933,19 +3933,19 @@
         <v>12</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE18" t="n">
         <v>190</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
         <v>150</v>
@@ -3969,28 +3969,28 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
         <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX18" t="n">
         <v>7.4</v>
@@ -4002,7 +4002,7 @@
         <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB18" t="n">
         <v>9.6</v>
@@ -4011,20 +4011,20 @@
         <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4055,61 +4055,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.54</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R19" t="n">
         <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="V19" t="n">
         <v>1.54</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="n">
         <v>8.4</v>
@@ -4127,25 +4127,25 @@
         <v>6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
         <v>980</v>
       </c>
       <c r="AF19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
         <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>65</v>
       </c>
       <c r="AJ19" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
         <v>980</v>
@@ -4154,7 +4154,7 @@
         <v>75</v>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN19" t="n">
         <v>65</v>
@@ -4163,16 +4163,16 @@
         <v>980</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -4184,41 +4184,41 @@
         <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
         <v>40</v>
       </c>
       <c r="BD19" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G20" t="n">
         <v>4.2</v>
       </c>
       <c r="H20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
         <v>1.48</v>
@@ -4276,19 +4276,19 @@
         <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
         <v>1.71</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R20" t="n">
         <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T20" t="n">
         <v>1.92</v>
@@ -4297,16 +4297,16 @@
         <v>1.96</v>
       </c>
       <c r="V20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z20" t="n">
         <v>15.5</v>
@@ -4357,7 +4357,7 @@
         <v>980</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.4</v>
@@ -4366,53 +4366,53 @@
         <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>14</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H21" t="n">
         <v>2.22</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J21" t="n">
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.45</v>
@@ -4467,7 +4467,7 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.37</v>
@@ -4479,10 +4479,10 @@
         <v>2.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T21" t="n">
         <v>1.84</v>
@@ -4497,16 +4497,16 @@
         <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
         <v>14</v>
       </c>
       <c r="AA21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB21" t="n">
         <v>15.5</v>
@@ -4560,7 +4560,7 @@
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT21" t="n">
         <v>11.5</v>
@@ -4572,10 +4572,10 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY21" t="n">
         <v>13.5</v>
@@ -4584,29 +4584,29 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG21" t="n">
         <v>14.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
         <v>3.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.35</v>
@@ -4661,31 +4661,31 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
         <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
         <v>1.72</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.36</v>
+        <v>2.82</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AV22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AX22" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>6.2</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I23" t="n">
         <v>1.58</v>
@@ -4861,22 +4861,22 @@
         <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U23" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="n">
         <v>2.72</v>
@@ -4900,13 +4900,13 @@
         <v>27</v>
       </c>
       <c r="AC23" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
         <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF23" t="n">
         <v>60</v>
@@ -4927,22 +4927,22 @@
         <v>80</v>
       </c>
       <c r="AL23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN23" t="n">
         <v>80</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP23" t="n">
         <v>20</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
         <v>9.6</v>
@@ -4963,7 +4963,7 @@
         <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY23" t="n">
         <v>21</v>
@@ -4975,26 +4975,26 @@
         <v>25</v>
       </c>
       <c r="BB23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC23" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BD23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE23" t="n">
         <v>15</v>
       </c>
-      <c r="BE23" t="n">
-        <v>70</v>
-      </c>
       <c r="BF23" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G24" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H24" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="I24" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J24" t="n">
         <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5064,7 +5064,7 @@
         <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
         <v>1.06</v>
@@ -5076,7 +5076,7 @@
         <v>1.51</v>
       </c>
       <c r="W24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>3.3</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>2.8</v>
@@ -5267,7 +5267,7 @@
         <v>1.74</v>
       </c>
       <c r="V25" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
         <v>1.57</v>
@@ -5366,10 +5366,10 @@
         <v>4.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
         <v>5.2</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>3.05</v>
       </c>
       <c r="G26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H26" t="n">
         <v>2.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J26" t="n">
         <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.4</v>
@@ -5437,22 +5437,22 @@
         <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="O26" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
         <v>1.94</v>
@@ -5461,16 +5461,16 @@
         <v>1.88</v>
       </c>
       <c r="V26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X26" t="n">
         <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
         <v>17</v>
@@ -5485,7 +5485,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
@@ -5500,16 +5500,16 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5521,7 +5521,7 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ26" t="n">
         <v>7.6</v>
@@ -5530,7 +5530,7 @@
         <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
         <v>9</v>
@@ -5542,7 +5542,7 @@
         <v>9.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>5.8</v>
       </c>
       <c r="AX26" t="n">
         <v>16</v>
@@ -5554,16 +5554,16 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE26" t="n">
         <v>6.6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>3.85</v>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
         <v>3.2</v>
@@ -5658,7 +5658,7 @@
         <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X27" t="n">
         <v>13</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -5828,19 +5828,19 @@
         <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R28" t="n">
         <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
         <v>1.94</v>
@@ -5849,10 +5849,10 @@
         <v>1.85</v>
       </c>
       <c r="V28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X28" t="n">
         <v>14</v>
@@ -5870,7 +5870,7 @@
         <v>9</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
         <v>25</v>
@@ -5882,10 +5882,10 @@
         <v>13.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
@@ -5909,13 +5909,13 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS28" t="n">
         <v>4.2</v>
@@ -5927,7 +5927,7 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AW28" t="n">
         <v>4.1</v>
@@ -5939,16 +5939,16 @@
         <v>7.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA28" t="n">
         <v>4.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD28" t="n">
         <v>4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G29" t="n">
         <v>2.64</v>
       </c>
       <c r="H29" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I29" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="J29" t="n">
         <v>3.75</v>
@@ -6025,31 +6025,31 @@
         <v>1.21</v>
       </c>
       <c r="P29" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R29" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S29" t="n">
         <v>2.64</v>
       </c>
       <c r="T29" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U29" t="n">
         <v>2.68</v>
       </c>
       <c r="V29" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
         <v>16</v>
@@ -6073,7 +6073,7 @@
         <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
@@ -6097,7 +6097,7 @@
         <v>55</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO29" t="n">
         <v>17.5</v>
@@ -6109,7 +6109,7 @@
         <v>15</v>
       </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS29" t="n">
         <v>38</v>
@@ -6127,7 +6127,7 @@
         <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY29" t="n">
         <v>11.5</v>
@@ -6151,14 +6151,14 @@
         <v>48</v>
       </c>
       <c r="BF29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG29" t="n">
         <v>16.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -6213,13 +6213,13 @@
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O30" t="n">
         <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
         <v>1.99</v>
@@ -6234,7 +6234,7 @@
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V30" t="n">
         <v>1.17</v>
@@ -6243,7 +6243,7 @@
         <v>2.52</v>
       </c>
       <c r="X30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y30" t="n">
         <v>20</v>
@@ -6267,7 +6267,7 @@
         <v>95</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
@@ -6288,7 +6288,7 @@
         <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN30" t="n">
         <v>9.6</v>
@@ -6312,16 +6312,16 @@
         <v>7.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV30" t="n">
         <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY30" t="n">
         <v>9.6</v>
@@ -6342,7 +6342,7 @@
         <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="BF30" t="n">
         <v>9.199999999999999</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
         <v>8</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
         <v>18.5</v>
@@ -6470,7 +6470,7 @@
         <v>21</v>
       </c>
       <c r="AI31" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ31" t="n">
         <v>24</v>
@@ -6479,7 +6479,7 @@
         <v>22</v>
       </c>
       <c r="AL31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM31" t="n">
         <v>100</v>
@@ -6500,7 +6500,7 @@
         <v>28</v>
       </c>
       <c r="AS31" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AT31" t="n">
         <v>7.8</v>
@@ -6512,7 +6512,7 @@
         <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX31" t="n">
         <v>10.5</v>
@@ -6524,7 +6524,7 @@
         <v>19.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB31" t="n">
         <v>22</v>
@@ -6536,7 +6536,7 @@
         <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="BF31" t="n">
         <v>16</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G32" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H32" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I32" t="n">
         <v>2.56</v>
@@ -6613,13 +6613,13 @@
         <v>1.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
         <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U32" t="n">
         <v>2.28</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
         <v>2.32</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
         <v>3.55</v>
@@ -6825,7 +6825,7 @@
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y33" t="n">
         <v>7.6</v>
@@ -6888,7 +6888,7 @@
         <v>10.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
@@ -6900,10 +6900,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW33" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AX33" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AY33" t="n">
         <v>15</v>
@@ -6912,29 +6912,29 @@
         <v>19</v>
       </c>
       <c r="BA33" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE33" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF33" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7159,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H35" t="n">
         <v>1.71</v>
       </c>
       <c r="I35" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>4.5</v>
@@ -7183,7 +7183,7 @@
         <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>1.25</v>
@@ -7192,137 +7192,137 @@
         <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R35" t="n">
         <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T35" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="U35" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="V35" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="W35" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH35" t="n">
         <v>21</v>
       </c>
-      <c r="AB35" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>24</v>
-      </c>
       <c r="AI35" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN35" t="n">
         <v>90</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>100</v>
       </c>
       <c r="AO35" t="n">
         <v>11</v>
       </c>
       <c r="AP35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU35" t="n">
         <v>8</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AV35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG35" t="n">
         <v>8</v>
       </c>
-      <c r="AS35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G36" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I36" t="n">
         <v>3.3</v>
@@ -7368,7 +7368,7 @@
         <v>3.25</v>
       </c>
       <c r="K36" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L36" t="n">
         <v>1.38</v>
@@ -7377,22 +7377,22 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P36" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
         <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T36" t="n">
         <v>1.74</v>
@@ -7404,13 +7404,13 @@
         <v>1.43</v>
       </c>
       <c r="W36" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y36" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z36" t="n">
         <v>23</v>
@@ -7419,16 +7419,16 @@
         <v>55</v>
       </c>
       <c r="AB36" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC36" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD36" t="n">
         <v>14.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF36" t="n">
         <v>17.5</v>
@@ -7461,7 +7461,7 @@
         <v>36</v>
       </c>
       <c r="AP36" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>10.5</v>
@@ -7470,7 +7470,7 @@
         <v>18</v>
       </c>
       <c r="AS36" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT36" t="n">
         <v>9.4</v>
@@ -7482,7 +7482,7 @@
         <v>11.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX36" t="n">
         <v>14</v>
@@ -7494,29 +7494,29 @@
         <v>14.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC36" t="n">
         <v>20</v>
       </c>
       <c r="BD36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF36" t="n">
         <v>17.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>1.52</v>
       </c>
       <c r="G37" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H37" t="n">
         <v>6.2</v>
@@ -7562,7 +7562,7 @@
         <v>4.1</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L37" t="n">
         <v>1.27</v>
@@ -7634,7 +7634,7 @@
         <v>26</v>
       </c>
       <c r="AI37" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ37" t="n">
         <v>17</v>
@@ -7643,13 +7643,13 @@
         <v>19</v>
       </c>
       <c r="AL37" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
@@ -7661,10 +7661,10 @@
         <v>19</v>
       </c>
       <c r="AR37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT37" t="n">
         <v>7.6</v>
@@ -7673,13 +7673,13 @@
         <v>8.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY37" t="n">
         <v>8.6</v>
@@ -7688,7 +7688,7 @@
         <v>19</v>
       </c>
       <c r="BA37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB37" t="n">
         <v>11</v>
@@ -7697,20 +7697,20 @@
         <v>14</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE37" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF37" t="n">
         <v>6.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>1.89</v>
       </c>
       <c r="G38" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H38" t="n">
         <v>3.85</v>
@@ -7753,7 +7753,7 @@
         <v>4.9</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K38" t="n">
         <v>4.1</v>
@@ -7765,34 +7765,34 @@
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O38" t="n">
         <v>1.32</v>
       </c>
       <c r="P38" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q38" t="n">
         <v>1.94</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T38" t="n">
         <v>1.79</v>
       </c>
       <c r="U38" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V38" t="n">
         <v>1.27</v>
       </c>
       <c r="W38" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X38" t="n">
         <v>980</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX38" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX38" t="n">
+      <c r="AY38" t="n">
         <v>4</v>
       </c>
-      <c r="AY38" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="BE38" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
         <v>2.76</v>
       </c>
       <c r="H39" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I39" t="n">
         <v>3.55</v>
@@ -7950,7 +7950,7 @@
         <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L39" t="n">
         <v>1.39</v>
@@ -7959,13 +7959,13 @@
         <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P39" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q39" t="n">
         <v>2.2</v>
@@ -7977,16 +7977,16 @@
         <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U39" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V39" t="n">
         <v>1.39</v>
       </c>
       <c r="W39" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X39" t="n">
         <v>13</v>
@@ -8004,7 +8004,7 @@
         <v>10.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD39" t="n">
         <v>980</v>
@@ -8013,7 +8013,7 @@
         <v>980</v>
       </c>
       <c r="AF39" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="AG39" t="n">
         <v>14</v>
@@ -8022,7 +8022,7 @@
         <v>23</v>
       </c>
       <c r="AI39" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ39" t="n">
         <v>1000</v>
@@ -8043,7 +8043,7 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ39" t="n">
         <v>9.199999999999999</v>
@@ -8052,7 +8052,7 @@
         <v>16.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.9</v>
+        <v>44</v>
       </c>
       <c r="AT39" t="n">
         <v>7.8</v>
@@ -8064,7 +8064,7 @@
         <v>11</v>
       </c>
       <c r="AW39" t="n">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="AX39" t="n">
         <v>12</v>
@@ -8073,32 +8073,32 @@
         <v>10</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB39" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF39" t="n">
         <v>5.8</v>
       </c>
-      <c r="BE39" t="n">
+      <c r="BG39" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF39" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -8132,10 +8132,10 @@
         <v>2.34</v>
       </c>
       <c r="G40" t="n">
-        <v>2.86</v>
+        <v>2.54</v>
       </c>
       <c r="H40" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I40" t="n">
         <v>3.6</v>
@@ -8147,22 +8147,22 @@
         <v>3.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M40" t="n">
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O40" t="n">
         <v>1.39</v>
       </c>
       <c r="P40" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R40" t="n">
         <v>1.26</v>
@@ -8180,7 +8180,7 @@
         <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G41" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H41" t="n">
         <v>2.26</v>
       </c>
       <c r="I41" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="J41" t="n">
         <v>3.85</v>
       </c>
       <c r="K41" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8350,7 +8350,7 @@
         <v>5.5</v>
       </c>
       <c r="O41" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P41" t="n">
         <v>2.66</v>
@@ -8359,7 +8359,7 @@
         <v>1.52</v>
       </c>
       <c r="R41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S41" t="n">
         <v>2.3</v>
@@ -8371,7 +8371,7 @@
         <v>2.62</v>
       </c>
       <c r="V41" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W41" t="n">
         <v>1.46</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H42" t="n">
         <v>3.9</v>
@@ -8532,7 +8532,7 @@
         <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L42" t="n">
         <v>1.33</v>
@@ -8568,7 +8568,7 @@
         <v>1.28</v>
       </c>
       <c r="W42" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="X42" t="n">
         <v>14.5</v>
@@ -8613,7 +8613,7 @@
         <v>24</v>
       </c>
       <c r="AL42" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
@@ -8646,7 +8646,7 @@
         <v>14.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="AX42" t="n">
         <v>10.5</v>
@@ -8667,7 +8667,7 @@
         <v>18.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BE42" t="n">
         <v>8.199999999999999</v>
@@ -8676,11 +8676,11 @@
         <v>12.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G43" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="H43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I43" t="n">
         <v>3.65</v>
       </c>
       <c r="J43" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K43" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8741,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
         <v>1.57</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -8905,13 +8905,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G44" t="n">
         <v>3.2</v>
       </c>
       <c r="H44" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I44" t="n">
         <v>3.3</v>
@@ -8920,7 +8920,7 @@
         <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L44" t="n">
         <v>1.34</v>
@@ -8947,10 +8947,10 @@
         <v>3.1</v>
       </c>
       <c r="T44" t="n">
-        <v>1.05</v>
+        <v>1.66</v>
       </c>
       <c r="U44" t="n">
-        <v>1.05</v>
+        <v>1.87</v>
       </c>
       <c r="V44" t="n">
         <v>1.44</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -9102,13 +9102,13 @@
         <v>1.3</v>
       </c>
       <c r="G45" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H45" t="n">
         <v>14</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="J45" t="n">
         <v>5</v>
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q45" t="n">
         <v>1.9</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -9302,13 +9302,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="J46" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K46" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9329,13 +9329,13 @@
         <v>1.53</v>
       </c>
       <c r="R46" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S46" t="n">
         <v>2.44</v>
       </c>
       <c r="T46" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
         <v>1.68</v>
@@ -9353,13 +9353,13 @@
         <v>980</v>
       </c>
       <c r="Z46" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC46" t="n">
         <v>16.5</v>
@@ -9401,62 +9401,62 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ46" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AR46" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT46" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU46" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AV46" t="n">
         <v>5</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AX46" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AY46" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ46" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB46" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC46" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF46" t="n">
         <v>4</v>
       </c>
       <c r="BG46" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>4.1</v>
       </c>
       <c r="J47" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K47" t="n">
         <v>4.1</v>
@@ -9526,10 +9526,10 @@
         <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U47" t="n">
         <v>2.18</v>
@@ -9544,7 +9544,7 @@
         <v>19.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z47" t="n">
         <v>34</v>
@@ -9604,7 +9604,7 @@
         <v>21</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT47" t="n">
         <v>9.199999999999999</v>
@@ -9628,7 +9628,7 @@
         <v>14</v>
       </c>
       <c r="BA47" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB47" t="n">
         <v>19.5</v>
@@ -9646,11 +9646,11 @@
         <v>10.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -9690,13 +9690,13 @@
         <v>3.1</v>
       </c>
       <c r="I48" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="K48" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9711,28 +9711,28 @@
         <v>1.44</v>
       </c>
       <c r="P48" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R48" t="n">
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T48" t="n">
         <v>1.93</v>
       </c>
       <c r="U48" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V48" t="n">
         <v>1.31</v>
       </c>
       <c r="W48" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X48" t="n">
         <v>12.5</v>
@@ -9777,7 +9777,7 @@
         <v>40</v>
       </c>
       <c r="AL48" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AM48" t="n">
         <v>1000</v>
@@ -9810,7 +9810,7 @@
         <v>3.45</v>
       </c>
       <c r="AW48" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX48" t="n">
         <v>3.45</v>
@@ -9834,7 +9834,7 @@
         <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF48" t="n">
         <v>3.85</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G49" t="n">
         <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J49" t="n">
         <v>3.35</v>
       </c>
       <c r="K49" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L49" t="n">
         <v>1.34</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -10069,58 +10069,58 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="G50" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="H50" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="I50" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="J50" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K50" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L50" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M50" t="n">
         <v>1.04</v>
       </c>
       <c r="N50" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O50" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P50" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R50" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S50" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T50" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U50" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V50" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="W50" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X50" t="n">
         <v>26</v>
@@ -10129,82 +10129,82 @@
         <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AA50" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AB50" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AC50" t="n">
         <v>11.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AE50" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG50" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI50" t="n">
         <v>28</v>
       </c>
       <c r="AJ50" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK50" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN50" t="n">
         <v>80</v>
       </c>
-      <c r="AM50" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>85</v>
-      </c>
       <c r="AO50" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AP50" t="n">
         <v>24</v>
       </c>
       <c r="AQ50" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS50" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT50" t="n">
         <v>27</v>
       </c>
       <c r="AU50" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV50" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW50" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX50" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AY50" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ50" t="n">
         <v>20</v>
@@ -10213,26 +10213,26 @@
         <v>26</v>
       </c>
       <c r="BB50" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="BC50" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD50" t="n">
         <v>60</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>55</v>
       </c>
       <c r="BE50" t="n">
         <v>85</v>
       </c>
       <c r="BF50" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BG50" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -10278,25 +10278,25 @@
         <v>2.82</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L51" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="M51" t="n">
         <v>1.18</v>
       </c>
       <c r="N51" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="O51" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="P51" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R51" t="n">
         <v>1.12</v>
@@ -10308,7 +10308,7 @@
         <v>2.62</v>
       </c>
       <c r="U51" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V51" t="n">
         <v>1.27</v>
@@ -10347,7 +10347,7 @@
         <v>14</v>
       </c>
       <c r="AH51" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI51" t="n">
         <v>170</v>
@@ -10356,7 +10356,7 @@
         <v>50</v>
       </c>
       <c r="AK51" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL51" t="n">
         <v>1000</v>
@@ -10374,7 +10374,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR51" t="n">
         <v>20</v>
@@ -10389,7 +10389,7 @@
         <v>6.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AW51" t="n">
         <v>38</v>
@@ -10401,19 +10401,19 @@
         <v>11.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BA51" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB51" t="n">
         <v>24</v>
       </c>
       <c r="BC51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD51" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE51" t="n">
         <v>13</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G52" t="n">
         <v>2.82</v>
@@ -10472,7 +10472,7 @@
         <v>2.74</v>
       </c>
       <c r="K52" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="L52" t="n">
         <v>1.74</v>
@@ -10520,7 +10520,7 @@
         <v>22</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB52" t="n">
         <v>6.8</v>
@@ -10544,13 +10544,13 @@
         <v>32</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ52" t="n">
         <v>55</v>
       </c>
       <c r="AK52" t="n">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="AL52" t="n">
         <v>130</v>
@@ -10565,7 +10565,7 @@
         <v>140</v>
       </c>
       <c r="AP52" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ52" t="n">
         <v>7.4</v>
@@ -10574,7 +10574,7 @@
         <v>19</v>
       </c>
       <c r="AS52" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AT52" t="n">
         <v>5.9</v>
@@ -10601,10 +10601,10 @@
         <v>42</v>
       </c>
       <c r="BB52" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BC52" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BD52" t="n">
         <v>40</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -10854,13 +10854,13 @@
         <v>2.5</v>
       </c>
       <c r="I54" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L54" t="n">
         <v>1.52</v>
@@ -10950,7 +10950,7 @@
         <v>60</v>
       </c>
       <c r="AO54" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AP54" t="n">
         <v>8.6</v>
@@ -10986,13 +10986,13 @@
         <v>6.6</v>
       </c>
       <c r="BA54" t="n">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BB54" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BC54" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BD54" t="n">
         <v>8.4</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="G55" t="n">
         <v>1.98</v>
@@ -11054,7 +11054,7 @@
         <v>3.75</v>
       </c>
       <c r="K55" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11174,7 +11174,7 @@
         <v>10.5</v>
       </c>
       <c r="AY55" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ55" t="n">
         <v>15</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -11239,16 +11239,16 @@
         <v>6.2</v>
       </c>
       <c r="H56" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I56" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J56" t="n">
         <v>4.6</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -11281,7 +11281,7 @@
         <v>2.24</v>
       </c>
       <c r="V56" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W56" t="n">
         <v>1.19</v>
@@ -11365,7 +11365,7 @@
         <v>13.5</v>
       </c>
       <c r="AX56" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AY56" t="n">
         <v>6.2</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -760,19 +760,19 @@
         <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -787,10 +787,10 @@
         <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
@@ -802,22 +802,22 @@
         <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
         <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -826,10 +826,10 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
         <v>50</v>
@@ -838,7 +838,7 @@
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -856,7 +856,7 @@
         <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -868,13 +868,13 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -895,32 +895,32 @@
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
         <v>30</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -951,40 +951,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
         <v>3.35</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I3" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J3" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
         <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -996,7 +996,7 @@
         <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
         <v>1.51</v>
@@ -1005,10 +1005,10 @@
         <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>980</v>
       </c>
       <c r="Z3" t="n">
         <v>980</v>
@@ -1017,7 +1017,7 @@
         <v>980</v>
       </c>
       <c r="AB3" t="n">
-        <v>980</v>
+        <v>10</v>
       </c>
       <c r="AC3" t="n">
         <v>7</v>
@@ -1038,10 +1038,10 @@
         <v>980</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="n">
         <v>980</v>
@@ -1062,59 +1062,59 @@
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1172,46 +1172,46 @@
         <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="X4" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
         <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="n">
         <v>320</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
@@ -1232,13 +1232,13 @@
         <v>980</v>
       </c>
       <c r="AI4" t="n">
-        <v>140</v>
+        <v>520</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="AK4" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
         <v>980</v>
@@ -1253,28 +1253,28 @@
         <v>220</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
@@ -1283,10 +1283,10 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>10.5</v>
@@ -1295,20 +1295,20 @@
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
         <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
         <v>3.65</v>
       </c>
       <c r="J5" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
@@ -1363,7 +1363,7 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O5" t="n">
         <v>1.41</v>
@@ -1372,16 +1372,16 @@
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
         <v>1.98</v>
@@ -1390,7 +1390,7 @@
         <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
         <v>980</v>
@@ -1408,7 +1408,7 @@
         <v>980</v>
       </c>
       <c r="AC5" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>980</v>
@@ -1426,7 +1426,7 @@
         <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
         <v>980</v>
@@ -1444,65 +1444,65 @@
         <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AR5" t="n">
         <v>4.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>4.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.38</v>
@@ -1575,10 +1575,10 @@
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
@@ -1587,10 +1587,10 @@
         <v>2.04</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1611,13 +1611,13 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1626,7 +1626,7 @@
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1635,68 +1635,68 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX6" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5</v>
-      </c>
       <c r="AY6" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
         <v>12.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H7" t="n">
         <v>3.05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -1751,16 +1751,16 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -1772,16 +1772,16 @@
         <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
         <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X7" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
         <v>980</v>
@@ -1796,7 +1796,7 @@
         <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
         <v>980</v>
@@ -1814,10 +1814,10 @@
         <v>980</v>
       </c>
       <c r="AI7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>980</v>
@@ -1835,62 +1835,62 @@
         <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>3.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AT7" t="n">
         <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV7" t="n">
         <v>4</v>
       </c>
       <c r="AW7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX7" t="n">
         <v>4</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>3.85</v>
       </c>
-      <c r="AY7" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1933,10 +1933,10 @@
         <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.43</v>
@@ -1954,7 +1954,7 @@
         <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -1963,10 +1963,10 @@
         <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="U8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V8" t="n">
         <v>1.52</v>
@@ -1975,7 +1975,7 @@
         <v>1.46</v>
       </c>
       <c r="X8" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="n">
         <v>11</v>
@@ -1990,7 +1990,7 @@
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>17.5</v>
@@ -2017,7 +2017,7 @@
         <v>980</v>
       </c>
       <c r="AL8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2032,13 +2032,13 @@
         <v>3.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AR8" t="n">
         <v>4.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT8" t="n">
         <v>7.4</v>
@@ -2059,10 +2059,10 @@
         <v>4.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB8" t="n">
         <v>5.5</v>
@@ -2071,10 +2071,10 @@
         <v>5.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
         <v>5.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G9" t="n">
         <v>2.74</v>
@@ -2151,19 +2151,19 @@
         <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
         <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
         <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
         <v>1.58</v>
@@ -2214,13 +2214,13 @@
         <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
         <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP9" t="n">
         <v>18.5</v>
@@ -2232,7 +2232,7 @@
         <v>19</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
         <v>12.5</v>
@@ -2244,7 +2244,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
         <v>17.5</v>
@@ -2256,19 +2256,19 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
         <v>11</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2348,10 +2348,10 @@
         <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U10" t="n">
         <v>2.5</v>
@@ -2393,7 +2393,7 @@
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>38</v>
@@ -2450,16 +2450,16 @@
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
         <v>42</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2512,10 +2512,10 @@
         <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>3.05</v>
@@ -2527,13 +2527,13 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
         <v>2.36</v>
@@ -2542,13 +2542,13 @@
         <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T11" t="n">
         <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
@@ -2557,61 +2557,61 @@
         <v>1.46</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AF11" t="n">
-        <v>980</v>
+        <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>60</v>
       </c>
       <c r="AJ11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL11" t="n">
         <v>65</v>
       </c>
-      <c r="AK11" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>60</v>
-      </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AO11" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.6</v>
@@ -2620,19 +2620,19 @@
         <v>15.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AX11" t="n">
         <v>17</v>
@@ -2641,32 +2641,32 @@
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>28</v>
       </c>
-      <c r="BD11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H12" t="n">
         <v>4.8</v>
@@ -2709,7 +2709,7 @@
         <v>5.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -2721,16 +2721,16 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
         <v>1.31</v>
@@ -2739,19 +2739,19 @@
         <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U12" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
         <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
         <v>980</v>
@@ -2787,10 +2787,10 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
         <v>980</v>
@@ -2805,16 +2805,16 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AT12" t="n">
         <v>2.32</v>
@@ -2826,7 +2826,7 @@
         <v>2.58</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AX12" t="n">
         <v>2.4</v>
@@ -2838,7 +2838,7 @@
         <v>2.58</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BB12" t="n">
         <v>2.56</v>
@@ -2847,7 +2847,7 @@
         <v>2.56</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BE12" t="n">
         <v>2.84</v>
@@ -2856,11 +2856,11 @@
         <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.79</v>
       </c>
       <c r="G13" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="H13" t="n">
         <v>4.5</v>
@@ -2933,16 +2933,16 @@
         <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
         <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
         <v>20</v>
@@ -2954,7 +2954,7 @@
         <v>40</v>
       </c>
       <c r="AA13" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
@@ -2978,7 +2978,7 @@
         <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AJ13" t="n">
         <v>24</v>
@@ -3005,10 +3005,10 @@
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3020,7 +3020,7 @@
         <v>13.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3041,20 +3041,20 @@
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
         <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
@@ -3118,16 +3118,16 @@
         <v>2.42</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.57</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.58</v>
       </c>
       <c r="S14" t="n">
         <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
         <v>2.34</v>
@@ -3136,7 +3136,7 @@
         <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
         <v>27</v>
@@ -3148,7 +3148,7 @@
         <v>44</v>
       </c>
       <c r="AA14" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>13</v>
@@ -3157,7 +3157,7 @@
         <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
         <v>60</v>
@@ -3190,7 +3190,7 @@
         <v>7.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP14" t="n">
         <v>20</v>
@@ -3199,10 +3199,10 @@
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>10</v>
@@ -3214,7 +3214,7 @@
         <v>17.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3238,17 +3238,17 @@
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF14" t="n">
         <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
@@ -3321,128 +3321,128 @@
         <v>1.19</v>
       </c>
       <c r="T15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.05</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="G16" t="n">
         <v>1.21</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I16" t="n">
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K16" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,7 +3497,7 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>1.11</v>
       </c>
       <c r="O16" t="n">
         <v>1.11</v>
@@ -3524,7 +3524,7 @@
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,28 +3581,28 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.17</v>
+        <v>4.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.28</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
         <v>4.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX16" t="n">
         <v>4.3</v>
@@ -3611,10 +3611,10 @@
         <v>4.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.28</v>
+        <v>1.71</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BB16" t="n">
         <v>4.2</v>
@@ -3623,20 +3623,20 @@
         <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="BF16" t="n">
         <v>2.62</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.18</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G17" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3709,16 +3709,16 @@
         <v>1.95</v>
       </c>
       <c r="T17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U17" t="n">
         <v>3.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="X17" t="n">
         <v>980</v>
@@ -3775,7 +3775,7 @@
         <v>18</v>
       </c>
       <c r="AP17" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AQ17" t="n">
         <v>23</v>
@@ -3793,7 +3793,7 @@
         <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>7.6</v>
@@ -3808,19 +3808,19 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD17" t="n">
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BF17" t="n">
         <v>5.8</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3873,13 +3873,13 @@
         <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K18" t="n">
         <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3891,7 +3891,7 @@
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
         <v>1.76</v>
@@ -3900,19 +3900,19 @@
         <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T18" t="n">
         <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V18" t="n">
         <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="X18" t="n">
         <v>19.5</v>
@@ -3921,7 +3921,7 @@
         <v>32</v>
       </c>
       <c r="Z18" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA18" t="n">
         <v>410</v>
@@ -3948,7 +3948,7 @@
         <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>520</v>
       </c>
       <c r="AJ18" t="n">
         <v>12</v>
@@ -3960,7 +3960,7 @@
         <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>190</v>
+        <v>430</v>
       </c>
       <c r="AN18" t="n">
         <v>6.2</v>
@@ -3975,10 +3975,10 @@
         <v>26</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AS18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3987,10 +3987,10 @@
         <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="AW18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
         <v>7.4</v>
@@ -3999,7 +3999,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
         <v>11.5</v>
@@ -4011,20 +4011,20 @@
         <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
         <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I19" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L19" t="n">
         <v>1.57</v>
@@ -4079,16 +4079,16 @@
         <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
         <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.2</v>
@@ -4097,52 +4097,52 @@
         <v>5.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U19" t="n">
         <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X19" t="n">
         <v>8</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC19" t="n">
         <v>6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
         <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
         <v>65</v>
@@ -4151,7 +4151,7 @@
         <v>980</v>
       </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
         <v>190</v>
@@ -4160,22 +4160,22 @@
         <v>65</v>
       </c>
       <c r="AO19" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
@@ -4184,41 +4184,41 @@
         <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY19" t="n">
         <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BC19" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="BE19" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BG19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G20" t="n">
         <v>4.2</v>
@@ -4258,28 +4258,28 @@
         <v>2.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
         <v>3.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
         <v>2.26</v>
@@ -4288,31 +4288,31 @@
         <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
         <v>1.96</v>
       </c>
       <c r="V20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W20" t="n">
         <v>1.31</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB20" t="n">
         <v>12.5</v>
@@ -4324,40 +4324,40 @@
         <v>11.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AF20" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ20" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO20" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.4</v>
@@ -4369,50 +4369,50 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
       </c>
       <c r="AY20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I21" t="n">
         <v>2.28</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>1.45</v>
@@ -4467,7 +4467,7 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
         <v>1.37</v>
@@ -4479,10 +4479,10 @@
         <v>2.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
         <v>1.84</v>
@@ -4494,7 +4494,7 @@
         <v>1.78</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X21" t="n">
         <v>13.5</v>
@@ -4518,7 +4518,7 @@
         <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
         <v>980</v>
@@ -4533,19 +4533,19 @@
         <v>980</v>
       </c>
       <c r="AJ21" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AK21" t="n">
         <v>980</v>
       </c>
       <c r="AL21" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="AM21" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AO21" t="n">
         <v>21</v>
@@ -4560,7 +4560,7 @@
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AT21" t="n">
         <v>11.5</v>
@@ -4572,10 +4572,10 @@
         <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
         <v>13.5</v>
@@ -4584,29 +4584,29 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB21" t="n">
         <v>6.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
         <v>3.65</v>
@@ -4667,7 +4667,7 @@
         <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
         <v>2.06</v>
@@ -4679,19 +4679,19 @@
         <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U22" t="n">
         <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y22" t="n">
         <v>1000</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4715,7 +4715,7 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.78</v>
+        <v>6.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4855,28 +4855,28 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
         <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R23" t="n">
         <v>1.58</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T23" t="n">
         <v>1.75</v>
       </c>
       <c r="U23" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V23" t="n">
         <v>2.72</v>
@@ -4906,7 +4906,7 @@
         <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF23" t="n">
         <v>60</v>
@@ -4933,7 +4933,7 @@
         <v>90</v>
       </c>
       <c r="AN23" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO23" t="n">
         <v>6.4</v>
@@ -4951,50 +4951,50 @@
         <v>13.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY23" t="n">
         <v>21</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA23" t="n">
         <v>25</v>
       </c>
       <c r="BB23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD23" t="n">
         <v>55</v>
       </c>
       <c r="BE23" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF23" t="n">
         <v>15</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>14.5</v>
       </c>
       <c r="BG23" t="n">
         <v>5.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5034,13 +5034,13 @@
         <v>2.14</v>
       </c>
       <c r="I24" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5094,7 +5094,7 @@
         <v>980</v>
       </c>
       <c r="AC24" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AD24" t="n">
         <v>980</v>
@@ -5136,59 +5136,59 @@
         <v>1.69</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AR24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT24" t="n">
         <v>1.58</v>
       </c>
-      <c r="AS24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AU24" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
         <v>4.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD25" t="n">
         <v>5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>2.76</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K26" t="n">
         <v>3.3</v>
@@ -5452,13 +5452,13 @@
         <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V26" t="n">
         <v>1.56</v>
@@ -5470,7 +5470,7 @@
         <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z26" t="n">
         <v>17</v>
@@ -5482,10 +5482,10 @@
         <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
@@ -5500,16 +5500,16 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="n">
         <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5524,13 +5524,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT26" t="n">
         <v>9</v>
@@ -5539,44 +5539,44 @@
         <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G27" t="n">
         <v>2.26</v>
@@ -5616,7 +5616,7 @@
         <v>3.85</v>
       </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>3.2</v>
@@ -5637,13 +5637,13 @@
         <v>1.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q27" t="n">
         <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -5652,16 +5652,16 @@
         <v>1.91</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
         <v>13.5</v>
@@ -5712,7 +5712,7 @@
         <v>25</v>
       </c>
       <c r="AO27" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP27" t="n">
         <v>9.6</v>
@@ -5721,10 +5721,10 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5736,7 +5736,7 @@
         <v>14.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX27" t="n">
         <v>10.5</v>
@@ -5748,29 +5748,29 @@
         <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC27" t="n">
         <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF27" t="n">
         <v>16</v>
       </c>
       <c r="BG27" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5813,10 +5813,10 @@
         <v>5.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L28" t="n">
         <v>1.37</v>
@@ -5843,19 +5843,19 @@
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W28" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y28" t="n">
         <v>18</v>
@@ -5867,7 +5867,7 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC28" t="n">
         <v>9.6</v>
@@ -5885,7 +5885,7 @@
         <v>13</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
@@ -5909,40 +5909,40 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
         <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV28" t="n">
         <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
         <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB28" t="n">
         <v>18.5</v>
@@ -5951,20 +5951,20 @@
         <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF28" t="n">
         <v>12</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G29" t="n">
         <v>2.62</v>
       </c>
-      <c r="G29" t="n">
-        <v>2.64</v>
-      </c>
       <c r="H29" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I29" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J29" t="n">
         <v>3.75</v>
@@ -6025,10 +6025,10 @@
         <v>1.21</v>
       </c>
       <c r="P29" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R29" t="n">
         <v>1.58</v>
@@ -6046,10 +6046,10 @@
         <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y29" t="n">
         <v>16</v>
@@ -6142,7 +6142,7 @@
         <v>34</v>
       </c>
       <c r="BC29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD29" t="n">
         <v>28</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         <v>6.6</v>
       </c>
       <c r="J30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
         <v>4.3</v>
@@ -6219,16 +6219,16 @@
         <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
@@ -6252,7 +6252,7 @@
         <v>50</v>
       </c>
       <c r="AA30" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB30" t="n">
         <v>8</v>
@@ -6288,10 +6288,10 @@
         <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO30" t="n">
         <v>130</v>
@@ -6303,10 +6303,10 @@
         <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS30" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AT30" t="n">
         <v>7.6</v>
@@ -6315,13 +6315,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY30" t="n">
         <v>9.6</v>
@@ -6336,23 +6336,23 @@
         <v>14.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD30" t="n">
         <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG30" t="n">
         <v>100</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G31" t="n">
         <v>2</v>
       </c>
-      <c r="G31" t="n">
-        <v>2.02</v>
-      </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.47</v>
@@ -6419,13 +6419,13 @@
         <v>2.18</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
         <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U31" t="n">
         <v>1.98</v>
@@ -6434,7 +6434,7 @@
         <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X31" t="n">
         <v>12</v>
@@ -6443,22 +6443,22 @@
         <v>14</v>
       </c>
       <c r="Z31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA31" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB31" t="n">
         <v>8</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF31" t="n">
         <v>11</v>
@@ -6473,19 +6473,19 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK31" t="n">
         <v>22</v>
       </c>
       <c r="AL31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM31" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO31" t="n">
         <v>75</v>
@@ -6494,16 +6494,16 @@
         <v>11</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS31" t="n">
         <v>75</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU31" t="n">
         <v>7.4</v>
@@ -6524,10 +6524,10 @@
         <v>19.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
@@ -6536,17 +6536,17 @@
         <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
         <v>2.08</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R32" t="n">
         <v>1.43</v>
@@ -6676,7 +6676,7 @@
         <v>46</v>
       </c>
       <c r="AM32" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN32" t="n">
         <v>30</v>
@@ -6694,7 +6694,7 @@
         <v>13</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT32" t="n">
         <v>11</v>
@@ -6718,19 +6718,19 @@
         <v>13.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="BF32" t="n">
         <v>20</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>5.1</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I33" t="n">
         <v>2.32</v>
@@ -6834,7 +6834,7 @@
         <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB33" t="n">
         <v>12</v>
@@ -6846,10 +6846,10 @@
         <v>12</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG33" t="n">
         <v>18.5</v>
@@ -6867,7 +6867,7 @@
         <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
@@ -6888,7 +6888,7 @@
         <v>10.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
@@ -6900,10 +6900,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AX33" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY33" t="n">
         <v>15</v>
@@ -6912,7 +6912,7 @@
         <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB33" t="n">
         <v>7.6</v>
@@ -6930,11 +6930,11 @@
         <v>7.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6968,19 +6968,19 @@
         <v>1.62</v>
       </c>
       <c r="G34" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="H34" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
       </c>
       <c r="J34" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6998,7 +6998,7 @@
         <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
@@ -7013,10 +7013,10 @@
         <v>1.05</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="W34" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7162,10 +7162,10 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="H35" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="I35" t="n">
         <v>1.8</v>
@@ -7174,7 +7174,7 @@
         <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L35" t="n">
         <v>1.28</v>
@@ -7210,10 +7210,10 @@
         <v>2.24</v>
       </c>
       <c r="W35" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="n">
         <v>11</v>
@@ -7228,7 +7228,7 @@
         <v>24</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD35" t="n">
         <v>10.5</v>
@@ -7237,10 +7237,10 @@
         <v>20</v>
       </c>
       <c r="AF35" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AG35" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH35" t="n">
         <v>21</v>
@@ -7249,19 +7249,19 @@
         <v>34</v>
       </c>
       <c r="AJ35" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AK35" t="n">
         <v>75</v>
       </c>
       <c r="AL35" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
       </c>
       <c r="AN35" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO35" t="n">
         <v>11</v>
@@ -7282,7 +7282,7 @@
         <v>17</v>
       </c>
       <c r="AU35" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV35" t="n">
         <v>8.800000000000001</v>
@@ -7303,26 +7303,26 @@
         <v>27</v>
       </c>
       <c r="BB35" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG35" t="n">
         <v>8</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7356,10 +7356,10 @@
         <v>2.48</v>
       </c>
       <c r="G36" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H36" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
         <v>3.3</v>
@@ -7368,7 +7368,7 @@
         <v>3.25</v>
       </c>
       <c r="K36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L36" t="n">
         <v>1.38</v>
@@ -7377,7 +7377,7 @@
         <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
         <v>1.33</v>
@@ -7386,7 +7386,7 @@
         <v>1.87</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R36" t="n">
         <v>1.33</v>
@@ -7395,7 +7395,7 @@
         <v>3.5</v>
       </c>
       <c r="T36" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U36" t="n">
         <v>2.1</v>
@@ -7404,16 +7404,16 @@
         <v>1.43</v>
       </c>
       <c r="W36" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X36" t="n">
         <v>14</v>
       </c>
       <c r="Y36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA36" t="n">
         <v>55</v>
@@ -7422,10 +7422,10 @@
         <v>11</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE36" t="n">
         <v>38</v>
@@ -7452,7 +7452,7 @@
         <v>44</v>
       </c>
       <c r="AM36" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AN36" t="n">
         <v>25</v>
@@ -7470,7 +7470,7 @@
         <v>18</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT36" t="n">
         <v>9.4</v>
@@ -7482,7 +7482,7 @@
         <v>11.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX36" t="n">
         <v>14</v>
@@ -7497,26 +7497,26 @@
         <v>38</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC36" t="n">
         <v>20</v>
       </c>
       <c r="BD36" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BF36" t="n">
         <v>17.5</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7571,13 +7571,13 @@
         <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
         <v>1.26</v>
       </c>
       <c r="P37" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q37" t="n">
         <v>1.78</v>
@@ -7616,7 +7616,7 @@
         <v>10</v>
       </c>
       <c r="AC37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD37" t="n">
         <v>30</v>
@@ -7628,7 +7628,7 @@
         <v>11</v>
       </c>
       <c r="AG37" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH37" t="n">
         <v>26</v>
@@ -7640,7 +7640,7 @@
         <v>17</v>
       </c>
       <c r="AK37" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL37" t="n">
         <v>40</v>
@@ -7661,10 +7661,10 @@
         <v>19</v>
       </c>
       <c r="AR37" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT37" t="n">
         <v>7.6</v>
@@ -7676,7 +7676,7 @@
         <v>21</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX37" t="n">
         <v>8.199999999999999</v>
@@ -7688,7 +7688,7 @@
         <v>19</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB37" t="n">
         <v>11</v>
@@ -7697,20 +7697,20 @@
         <v>14</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF37" t="n">
         <v>6.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H38" t="n">
         <v>3.85</v>
@@ -7753,46 +7753,46 @@
         <v>4.9</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K38" t="n">
         <v>4.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O38" t="n">
         <v>1.32</v>
       </c>
       <c r="P38" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q38" t="n">
         <v>1.94</v>
       </c>
       <c r="R38" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S38" t="n">
         <v>3.25</v>
       </c>
       <c r="T38" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="U38" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V38" t="n">
         <v>1.27</v>
       </c>
       <c r="W38" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X38" t="n">
         <v>980</v>
@@ -7810,7 +7810,7 @@
         <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY38" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>2.74</v>
+        <v>5.6</v>
       </c>
       <c r="BA38" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="BB38" t="n">
-        <v>2.82</v>
+        <v>4.6</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.94</v>
+        <v>2.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.05</v>
+        <v>7.4</v>
       </c>
       <c r="BF38" t="n">
-        <v>2.74</v>
+        <v>5.1</v>
       </c>
       <c r="BG38" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H39" t="n">
         <v>3.1</v>
@@ -7947,40 +7947,40 @@
         <v>3.55</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K39" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O39" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P39" t="n">
         <v>1.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
         <v>1.77</v>
       </c>
       <c r="U39" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V39" t="n">
         <v>1.39</v>
@@ -7992,7 +7992,7 @@
         <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z39" t="n">
         <v>1000</v>
@@ -8004,7 +8004,7 @@
         <v>10.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD39" t="n">
         <v>980</v>
@@ -8016,13 +8016,13 @@
         <v>980</v>
       </c>
       <c r="AG39" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AI39" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AJ39" t="n">
         <v>1000</v>
@@ -8031,7 +8031,7 @@
         <v>1000</v>
       </c>
       <c r="AL39" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AQ39" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AR39" t="n">
         <v>16.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT39" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV39" t="n">
         <v>11</v>
       </c>
       <c r="AW39" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AX39" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AY39" t="n">
         <v>10</v>
       </c>
       <c r="AZ39" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BA39" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB39" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BE39" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BF39" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -8138,10 +8138,10 @@
         <v>3.2</v>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J40" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K40" t="n">
         <v>3.5</v>
@@ -8162,7 +8162,7 @@
         <v>1.72</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R40" t="n">
         <v>1.26</v>
@@ -8174,10 +8174,10 @@
         <v>1.05</v>
       </c>
       <c r="U40" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W40" t="n">
         <v>1.64</v>
@@ -8198,7 +8198,7 @@
         <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD40" t="n">
         <v>1000</v>
@@ -8237,62 +8237,62 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.27</v>
+        <v>7.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.27</v>
+        <v>5.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.2</v>
+        <v>2.52</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.27</v>
+        <v>17.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -8323,16 +8323,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="G41" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H41" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I41" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J41" t="n">
         <v>3.85</v>
@@ -8347,7 +8347,7 @@
         <v>1.03</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O41" t="n">
         <v>1.18</v>
@@ -8359,34 +8359,34 @@
         <v>1.52</v>
       </c>
       <c r="R41" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S41" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="T41" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U41" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V41" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W41" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="X41" t="n">
         <v>32</v>
       </c>
       <c r="Y41" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB41" t="n">
         <v>22</v>
@@ -8395,10 +8395,10 @@
         <v>12.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF41" t="n">
         <v>30</v>
@@ -8428,10 +8428,10 @@
         <v>21</v>
       </c>
       <c r="AO41" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP41" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AQ41" t="n">
         <v>13.5</v>
@@ -8440,7 +8440,7 @@
         <v>16.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AT41" t="n">
         <v>15.5</v>
@@ -8467,16 +8467,16 @@
         <v>20</v>
       </c>
       <c r="BB41" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BC41" t="n">
         <v>20</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BE41" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BF41" t="n">
         <v>12</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G42" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H42" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
         <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L42" t="n">
         <v>1.33</v>
@@ -8541,7 +8541,7 @@
         <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O42" t="n">
         <v>1.33</v>
@@ -8568,7 +8568,7 @@
         <v>1.28</v>
       </c>
       <c r="W42" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X42" t="n">
         <v>14.5</v>
@@ -8580,7 +8580,7 @@
         <v>980</v>
       </c>
       <c r="AA42" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB42" t="n">
         <v>9.199999999999999</v>
@@ -8595,7 +8595,7 @@
         <v>60</v>
       </c>
       <c r="AF42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG42" t="n">
         <v>11</v>
@@ -8607,10 +8607,10 @@
         <v>65</v>
       </c>
       <c r="AJ42" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AK42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL42" t="n">
         <v>40</v>
@@ -8628,13 +8628,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT42" t="n">
         <v>7.6</v>
@@ -8643,13 +8643,13 @@
         <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX42" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY42" t="n">
         <v>9</v>
@@ -8658,29 +8658,29 @@
         <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB42" t="n">
         <v>20</v>
       </c>
       <c r="BC42" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD42" t="n">
         <v>30</v>
       </c>
       <c r="BE42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF42" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG42" t="n">
         <v>44</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
         <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G44" t="n">
         <v>3.2</v>
@@ -8914,13 +8914,13 @@
         <v>2.44</v>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="J44" t="n">
         <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L44" t="n">
         <v>1.34</v>
@@ -8929,7 +8929,7 @@
         <v>1.02</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
         <v>1.27</v>
@@ -8947,13 +8947,13 @@
         <v>3.1</v>
       </c>
       <c r="T44" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U44" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="V44" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W44" t="n">
         <v>1.45</v>
@@ -9013,62 +9013,62 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G45" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="H45" t="n">
         <v>14</v>
       </c>
       <c r="I45" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="K45" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q45" t="n">
         <v>1.9</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -9296,19 +9296,19 @@
         <v>1.31</v>
       </c>
       <c r="G46" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="H46" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I46" t="n">
         <v>13.5</v>
       </c>
       <c r="J46" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="K46" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9335,7 +9335,7 @@
         <v>2.44</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="U46" t="n">
         <v>1.68</v>
@@ -9344,7 +9344,7 @@
         <v>1.08</v>
       </c>
       <c r="W46" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="X46" t="n">
         <v>980</v>
@@ -9383,7 +9383,7 @@
         <v>170</v>
       </c>
       <c r="AJ46" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AK46" t="n">
         <v>18</v>
@@ -9401,28 +9401,28 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="AQ46" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR46" t="n">
         <v>5.3</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT46" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX46" t="n">
         <v>4.5</v>
@@ -9431,32 +9431,32 @@
         <v>4.8</v>
       </c>
       <c r="AZ46" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB46" t="n">
         <v>4.8</v>
       </c>
       <c r="BC46" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD46" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF46" t="n">
         <v>4</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
         <v>3.55</v>
       </c>
       <c r="K47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
         <v>1.3</v>
@@ -9529,19 +9529,19 @@
         <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="U47" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V47" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X47" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y47" t="n">
         <v>18</v>
@@ -9556,7 +9556,7 @@
         <v>12.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD47" t="n">
         <v>18.5</v>
@@ -9571,7 +9571,7 @@
         <v>12.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI47" t="n">
         <v>60</v>
@@ -9586,7 +9586,7 @@
         <v>40</v>
       </c>
       <c r="AM47" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN47" t="n">
         <v>16</v>
@@ -9604,7 +9604,7 @@
         <v>21</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT47" t="n">
         <v>9.199999999999999</v>
@@ -9616,7 +9616,7 @@
         <v>12</v>
       </c>
       <c r="AW47" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX47" t="n">
         <v>10.5</v>
@@ -9628,7 +9628,7 @@
         <v>14</v>
       </c>
       <c r="BA47" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB47" t="n">
         <v>19.5</v>
@@ -9637,20 +9637,20 @@
         <v>18</v>
       </c>
       <c r="BD47" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF47" t="n">
         <v>10.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -9684,16 +9684,16 @@
         <v>2.34</v>
       </c>
       <c r="G48" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H48" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J48" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
         <v>3.45</v>
@@ -9705,37 +9705,37 @@
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="O48" t="n">
         <v>1.44</v>
       </c>
       <c r="P48" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R48" t="n">
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U48" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="V48" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W48" t="n">
         <v>1.6</v>
       </c>
       <c r="X48" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
         <v>13</v>
@@ -9756,19 +9756,19 @@
         <v>18.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF48" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG48" t="n">
         <v>14.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI48" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ48" t="n">
         <v>46</v>
@@ -9789,62 +9789,62 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="AR48" t="n">
-        <v>3.7</v>
+        <v>16.5</v>
       </c>
       <c r="AS48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC48" t="n">
         <v>4</v>
       </c>
-      <c r="AT48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW48" t="n">
+      <c r="BD48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF48" t="n">
         <v>4</v>
       </c>
-      <c r="AX48" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG48" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -9878,13 +9878,13 @@
         <v>2.82</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H49" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I49" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J49" t="n">
         <v>3.35</v>
@@ -9923,13 +9923,13 @@
         <v>2.02</v>
       </c>
       <c r="V49" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W49" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X49" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y49" t="n">
         <v>10.5</v>
@@ -9992,7 +9992,7 @@
         <v>13.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT49" t="n">
         <v>9.6</v>
@@ -10004,7 +10004,7 @@
         <v>10</v>
       </c>
       <c r="AW49" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="AX49" t="n">
         <v>17</v>
@@ -10016,29 +10016,29 @@
         <v>15.5</v>
       </c>
       <c r="BA49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC49" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BD49" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC49" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD49" t="n">
+      <c r="BE49" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF49" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>29</v>
       </c>
       <c r="BG49" t="n">
         <v>19.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -10069,22 +10069,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H50" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="I50" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K50" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L50" t="n">
         <v>1.32</v>
@@ -10096,13 +10096,13 @@
         <v>5.5</v>
       </c>
       <c r="O50" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P50" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R50" t="n">
         <v>1.59</v>
@@ -10111,28 +10111,28 @@
         <v>2.6</v>
       </c>
       <c r="T50" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U50" t="n">
         <v>2.22</v>
       </c>
       <c r="V50" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="W50" t="n">
         <v>1.16</v>
       </c>
       <c r="X50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y50" t="n">
         <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AA50" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AB50" t="n">
         <v>28</v>
@@ -10150,10 +10150,10 @@
         <v>60</v>
       </c>
       <c r="AG50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI50" t="n">
         <v>28</v>
@@ -10162,7 +10162,7 @@
         <v>210</v>
       </c>
       <c r="AK50" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL50" t="n">
         <v>75</v>
@@ -10174,19 +10174,19 @@
         <v>80</v>
       </c>
       <c r="AO50" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ50" t="n">
         <v>10</v>
       </c>
       <c r="AR50" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS50" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT50" t="n">
         <v>27</v>
@@ -10201,10 +10201,10 @@
         <v>13</v>
       </c>
       <c r="AX50" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AY50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ50" t="n">
         <v>20</v>
@@ -10213,26 +10213,26 @@
         <v>26</v>
       </c>
       <c r="BB50" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="BC50" t="n">
         <v>75</v>
       </c>
       <c r="BD50" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE50" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF50" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BG50" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>2.22</v>
       </c>
       <c r="G51" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H51" t="n">
         <v>4.3</v>
@@ -10275,61 +10275,61 @@
         <v>4.8</v>
       </c>
       <c r="J51" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K51" t="n">
         <v>2.98</v>
       </c>
       <c r="L51" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M51" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="N51" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="O51" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="P51" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="T51" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="U51" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="V51" t="n">
         <v>1.27</v>
       </c>
       <c r="W51" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X51" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Y51" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z51" t="n">
         <v>32</v>
       </c>
       <c r="AA51" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AC51" t="n">
         <v>7.6</v>
@@ -10344,55 +10344,55 @@
         <v>11.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AI51" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ51" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK51" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AL51" t="n">
         <v>1000</v>
       </c>
       <c r="AM51" t="n">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="AN51" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO51" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP51" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR51" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS51" t="n">
         <v>40</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU51" t="n">
         <v>6.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX51" t="n">
         <v>10</v>
@@ -10416,17 +10416,17 @@
         <v>38</v>
       </c>
       <c r="BE51" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="BF51" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BG51" t="n">
         <v>46</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -10481,28 +10481,28 @@
         <v>1.18</v>
       </c>
       <c r="N52" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="O52" t="n">
         <v>1.77</v>
       </c>
       <c r="P52" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R52" t="n">
         <v>1.12</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="T52" t="n">
         <v>2.5</v>
       </c>
       <c r="U52" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V52" t="n">
         <v>1.38</v>
@@ -10514,13 +10514,13 @@
         <v>6.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z52" t="n">
         <v>22</v>
       </c>
       <c r="AA52" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB52" t="n">
         <v>6.8</v>
@@ -10529,7 +10529,7 @@
         <v>7</v>
       </c>
       <c r="AD52" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE52" t="n">
         <v>1000</v>
@@ -10556,7 +10556,7 @@
         <v>130</v>
       </c>
       <c r="AM52" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AN52" t="n">
         <v>1000</v>
@@ -10577,13 +10577,13 @@
         <v>32</v>
       </c>
       <c r="AT52" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU52" t="n">
         <v>6.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW52" t="n">
         <v>32</v>
@@ -10601,7 +10601,7 @@
         <v>42</v>
       </c>
       <c r="BB52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC52" t="n">
         <v>44</v>
@@ -10610,7 +10610,7 @@
         <v>40</v>
       </c>
       <c r="BE52" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BF52" t="n">
         <v>32</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="G53" t="n">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H53" t="n">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="I53" t="n">
         <v>990</v>
       </c>
       <c r="J53" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="K53" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -10699,10 +10699,10 @@
         <v>1.05</v>
       </c>
       <c r="V53" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W53" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10759,62 +10759,62 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -10845,22 +10845,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="G54" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H54" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I54" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L54" t="n">
         <v>1.52</v>
@@ -10869,31 +10869,31 @@
         <v>1.11</v>
       </c>
       <c r="N54" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="O54" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P54" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R54" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S54" t="n">
         <v>4.7</v>
       </c>
       <c r="T54" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U54" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V54" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W54" t="n">
         <v>1.38</v>
@@ -10905,7 +10905,7 @@
         <v>8.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA54" t="n">
         <v>980</v>
@@ -10917,7 +10917,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD54" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE54" t="n">
         <v>980</v>
@@ -10944,16 +10944,16 @@
         <v>70</v>
       </c>
       <c r="AM54" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN54" t="n">
         <v>60</v>
       </c>
       <c r="AO54" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AP54" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ54" t="n">
         <v>7.4</v>
@@ -10962,10 +10962,10 @@
         <v>13.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT54" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU54" t="n">
         <v>6.4</v>
@@ -10974,16 +10974,16 @@
         <v>10.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX54" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AY54" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ54" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA54" t="n">
         <v>44</v>
@@ -10995,20 +10995,20 @@
         <v>42</v>
       </c>
       <c r="BD54" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE54" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF54" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG54" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G55" t="n">
         <v>1.98</v>
@@ -11051,10 +11051,10 @@
         <v>4.7</v>
       </c>
       <c r="J55" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11084,7 +11084,7 @@
         <v>1.76</v>
       </c>
       <c r="U55" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V55" t="n">
         <v>1.27</v>
@@ -11108,7 +11108,7 @@
         <v>10.5</v>
       </c>
       <c r="AC55" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD55" t="n">
         <v>18.5</v>
@@ -11153,10 +11153,10 @@
         <v>14.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT55" t="n">
         <v>8.6</v>
@@ -11168,7 +11168,7 @@
         <v>15</v>
       </c>
       <c r="AW55" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX55" t="n">
         <v>10.5</v>
@@ -11180,7 +11180,7 @@
         <v>15</v>
       </c>
       <c r="BA55" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB55" t="n">
         <v>18.5</v>
@@ -11189,20 +11189,20 @@
         <v>16.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BF55" t="n">
         <v>10</v>
       </c>
       <c r="BG55" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G56" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H56" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="I56" t="n">
         <v>1.63</v>
@@ -11254,7 +11254,7 @@
         <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N56" t="n">
         <v>5.3</v>
@@ -11284,10 +11284,10 @@
         <v>2.58</v>
       </c>
       <c r="W56" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X56" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="Y56" t="n">
         <v>13</v>
@@ -11326,7 +11326,7 @@
         <v>160</v>
       </c>
       <c r="AK56" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL56" t="n">
         <v>1000</v>
@@ -11341,7 +11341,7 @@
         <v>7.4</v>
       </c>
       <c r="AP56" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AQ56" t="n">
         <v>10</v>
@@ -11368,7 +11368,7 @@
         <v>42</v>
       </c>
       <c r="AY56" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AZ56" t="n">
         <v>16.5</v>
@@ -11377,26 +11377,26 @@
         <v>21</v>
       </c>
       <c r="BB56" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC56" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD56" t="n">
         <v>7.4</v>
       </c>
       <c r="BE56" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF56" t="n">
         <v>7.4</v>
       </c>
       <c r="BG56" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -760,28 +760,28 @@
         <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.25</v>
       </c>
       <c r="K2" t="n">
         <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
@@ -793,13 +793,13 @@
         <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
         <v>1.96</v>
@@ -808,58 +808,58 @@
         <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
         <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>55</v>
@@ -871,22 +871,22 @@
         <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.9</v>
+        <v>16.5</v>
       </c>
       <c r="AS2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU2" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
@@ -898,29 +898,29 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD2" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
@@ -999,16 +999,16 @@
         <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
         <v>980</v>
@@ -1020,7 +1020,7 @@
         <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
         <v>980</v>
@@ -1038,83 +1038,83 @@
         <v>980</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
         <v>980</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO3" t="n">
         <v>980</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AR3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU3" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2.78</v>
-      </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1148,49 +1148,49 @@
         <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
         <v>3.15</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
         <v>1.11</v>
@@ -1205,25 +1205,25 @@
         <v>980</v>
       </c>
       <c r="Z4" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AB4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1235,7 +1235,7 @@
         <v>520</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>65</v>
@@ -1244,13 +1244,13 @@
         <v>980</v>
       </c>
       <c r="AM4" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AP4" t="n">
         <v>10.5</v>
@@ -1259,13 +1259,13 @@
         <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU4" t="n">
         <v>8.800000000000001</v>
@@ -1274,7 +1274,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
@@ -1286,7 +1286,7 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
         <v>10.5</v>
@@ -1298,17 +1298,17 @@
         <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1354,10 +1354,10 @@
         <v>2.98</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1372,7 +1372,7 @@
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
@@ -1381,7 +1381,7 @@
         <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
         <v>1.98</v>
@@ -1393,7 +1393,7 @@
         <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
         <v>980</v>
@@ -1402,13 +1402,13 @@
         <v>980</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>980</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>980</v>
@@ -1426,7 +1426,7 @@
         <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="AJ5" t="n">
         <v>980</v>
@@ -1444,65 +1444,65 @@
         <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.7</v>
+        <v>2.52</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G6" t="n">
         <v>1.94</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
         <v>5.8</v>
@@ -1590,10 +1590,10 @@
         <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1611,22 +1611,22 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1650,13 +1650,13 @@
         <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
         <v>6.8</v>
@@ -1665,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>6.2</v>
@@ -1689,14 +1689,14 @@
         <v>8.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1727,40 +1727,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="P7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -1769,10 +1769,10 @@
         <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
         <v>1.38</v>
@@ -1781,7 +1781,7 @@
         <v>1.52</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
         <v>980</v>
@@ -1790,13 +1790,13 @@
         <v>980</v>
       </c>
       <c r="AA7" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
         <v>980</v>
@@ -1814,7 +1814,7 @@
         <v>980</v>
       </c>
       <c r="AI7" t="n">
-        <v>100</v>
+        <v>330</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -1838,59 +1838,59 @@
         <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AT7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG7" t="n">
         <v>6</v>
       </c>
-      <c r="AU7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1921,34 +1921,34 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J8" t="n">
         <v>2.82</v>
       </c>
-      <c r="G8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.96</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
         <v>1.51</v>
@@ -1966,34 +1966,34 @@
         <v>1.91</v>
       </c>
       <c r="U8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
         <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
         <v>980</v>
       </c>
       <c r="AA8" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.5</v>
+        <v>65</v>
       </c>
       <c r="AE8" t="n">
         <v>980</v>
@@ -2002,22 +2002,22 @@
         <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>980</v>
+        <v>70</v>
       </c>
       <c r="AH8" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>980</v>
       </c>
       <c r="AL8" t="n">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>980</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU8" t="n">
         <v>5.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
@@ -2142,7 +2142,7 @@
         <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
         <v>2.4</v>
@@ -2151,134 +2151,134 @@
         <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
         <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
         <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X9" t="n">
         <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z9" t="n">
         <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
         <v>40</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>38</v>
       </c>
       <c r="AM9" t="n">
         <v>200</v>
       </c>
       <c r="AN9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR9" t="n">
         <v>18</v>
       </c>
-      <c r="AO9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>19</v>
-      </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
         <v>3.75</v>
@@ -2351,43 +2351,43 @@
         <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2396,49 +2396,49 @@
         <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="n">
         <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP10" t="n">
         <v>20</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>19.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV10" t="n">
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
         <v>16.5</v>
@@ -2447,32 +2447,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -2533,7 +2533,7 @@
         <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
         <v>2.36</v>
@@ -2554,22 +2554,22 @@
         <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>7</v>
@@ -2584,13 +2584,13 @@
         <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AH11" t="n">
         <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AJ11" t="n">
         <v>50</v>
@@ -2599,7 +2599,7 @@
         <v>40</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>130</v>
@@ -2617,19 +2617,19 @@
         <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
         <v>32</v>
@@ -2644,29 +2644,29 @@
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
         <v>34</v>
       </c>
       <c r="BD11" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2700,49 +2700,49 @@
         <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
         <v>5.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
         <v>1.21</v>
@@ -2751,7 +2751,7 @@
         <v>2.16</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="Y12" t="n">
         <v>980</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD12" t="n">
         <v>980</v>
@@ -2775,13 +2775,13 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2799,68 +2799,68 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.54</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.82</v>
+        <v>7.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.32</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.38</v>
+        <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.58</v>
+        <v>10.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.56</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.56</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.68</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.84</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G13" t="n">
         <v>1.85</v>
@@ -2900,10 +2900,10 @@
         <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
         <v>4.3</v>
@@ -2912,7 +2912,7 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
         <v>4.3</v>
@@ -2933,128 +2933,128 @@
         <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
         <v>2.16</v>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>980</v>
       </c>
       <c r="Y13" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="Z13" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>980</v>
       </c>
       <c r="AC13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>1.48</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>1.48</v>
       </c>
       <c r="AS13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT13" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT13" t="n">
-        <v>9</v>
-      </c>
       <c r="AU13" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>13.5</v>
+        <v>1.42</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.9</v>
+        <v>1.49</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>1.42</v>
       </c>
       <c r="BA13" t="n">
-        <v>40</v>
+        <v>1.49</v>
       </c>
       <c r="BB13" t="n">
-        <v>17.5</v>
+        <v>1.48</v>
       </c>
       <c r="BC13" t="n">
-        <v>15.5</v>
+        <v>1.47</v>
       </c>
       <c r="BD13" t="n">
-        <v>16</v>
+        <v>1.47</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>1.43</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>2.48</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3106,13 +3106,13 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
         <v>5.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
         <v>2.42</v>
@@ -3124,13 +3124,13 @@
         <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
         <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
         <v>1.23</v>
@@ -3142,7 +3142,7 @@
         <v>27</v>
       </c>
       <c r="Y14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z14" t="n">
         <v>44</v>
@@ -3163,7 +3163,7 @@
         <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
         <v>11</v>
@@ -3175,80 +3175,80 @@
         <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL14" t="n">
         <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="AN14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO14" t="n">
         <v>46</v>
       </c>
       <c r="AP14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>20</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>21</v>
-      </c>
       <c r="AR14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>4.6</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
         <v>11</v>
@@ -3324,7 +3324,7 @@
         <v>1.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V15" t="n">
         <v>1.14</v>
@@ -3390,59 +3390,59 @@
         <v>1.05</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG15" t="n">
         <v>1.55</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3485,10 +3485,10 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G17" t="n">
         <v>1.97</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
         <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3697,7 +3697,7 @@
         <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q17" t="n">
         <v>1.39</v>
@@ -3709,7 +3709,7 @@
         <v>1.95</v>
       </c>
       <c r="T17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U17" t="n">
         <v>3.2</v>
@@ -3721,94 +3721,94 @@
         <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="Y17" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="Z17" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>36</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>980</v>
       </c>
       <c r="AN17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP17" t="n">
         <v>20</v>
       </c>
       <c r="AQ17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU17" t="n">
         <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AX17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
@@ -3826,11 +3826,11 @@
         <v>5.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>1.42</v>
       </c>
       <c r="H18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I18" t="n">
         <v>11</v>
@@ -3876,31 +3876,31 @@
         <v>5.3</v>
       </c>
       <c r="K18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
         <v>2.1</v>
@@ -3915,7 +3915,7 @@
         <v>3.4</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
         <v>32</v>
@@ -3924,7 +3924,7 @@
         <v>95</v>
       </c>
       <c r="AA18" t="n">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="AB18" t="n">
         <v>8.6</v>
@@ -3939,7 +3939,7 @@
         <v>190</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
@@ -3954,31 +3954,31 @@
         <v>12</v>
       </c>
       <c r="AK18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
         <v>430</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR18" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,22 +3990,22 @@
         <v>17</v>
       </c>
       <c r="AW18" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AX18" t="n">
         <v>7.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC18" t="n">
         <v>13</v>
@@ -4014,17 +4014,17 @@
         <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4061,37 +4061,37 @@
         <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I19" t="n">
         <v>2.8</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="L19" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M19" t="n">
         <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O19" t="n">
         <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q19" t="n">
         <v>2.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
         <v>5.7</v>
@@ -4103,25 +4103,25 @@
         <v>1.83</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W19" t="n">
         <v>1.41</v>
       </c>
       <c r="X19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA19" t="n">
         <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC19" t="n">
         <v>6.8</v>
@@ -4139,7 +4139,7 @@
         <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AI19" t="n">
         <v>70</v>
@@ -4148,19 +4148,19 @@
         <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AM19" t="n">
         <v>190</v>
       </c>
       <c r="AN19" t="n">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="AO19" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AP19" t="n">
         <v>7.4</v>
@@ -4169,10 +4169,10 @@
         <v>7.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
         <v>8.6</v>
@@ -4187,38 +4187,38 @@
         <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>19.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC19" t="n">
         <v>15.5</v>
       </c>
-      <c r="BB19" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD19" t="n">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BF19" t="n">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4267,25 +4267,25 @@
         <v>3.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P20" t="n">
         <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
         <v>4.3</v>
@@ -4306,25 +4306,25 @@
         <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AB20" t="n">
         <v>12.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
         <v>11.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
         <v>27</v>
@@ -4336,16 +4336,16 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ20" t="n">
         <v>100</v>
       </c>
       <c r="AK20" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AL20" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="AM20" t="n">
         <v>140</v>
@@ -4354,19 +4354,19 @@
         <v>75</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
         <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -4378,7 +4378,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4390,29 +4390,29 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="BD20" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BE20" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BF20" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG20" t="n">
         <v>20</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H21" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I21" t="n">
         <v>2.28</v>
@@ -4458,7 +4458,7 @@
         <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.45</v>
@@ -4467,16 +4467,16 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
         <v>1.3</v>
@@ -4485,49 +4485,49 @@
         <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
         <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AA21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB21" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
         <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AF21" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AI21" t="n">
         <v>980</v>
@@ -4548,7 +4548,7 @@
         <v>110</v>
       </c>
       <c r="AO21" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
@@ -4560,19 +4560,19 @@
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
         <v>11.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -4584,29 +4584,29 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BD21" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BE21" t="n">
         <v>29</v>
       </c>
       <c r="BF21" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="H22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J22" t="n">
         <v>3.1</v>
@@ -4670,13 +4670,13 @@
         <v>1.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T22" t="n">
         <v>1.79</v>
@@ -4685,10 +4685,10 @@
         <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="X22" t="n">
         <v>90</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4715,7 +4715,7 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
         <v>1000</v>
@@ -4748,13 +4748,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AT22" t="n">
         <v>4.9</v>
@@ -4763,10 +4763,10 @@
         <v>4.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX22" t="n">
         <v>6.2</v>
@@ -4775,32 +4775,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF22" t="n">
         <v>5.1</v>
       </c>
-      <c r="BA22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="G23" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I23" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="J23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
         <v>5</v>
@@ -4855,76 +4855,76 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V23" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="W23" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
         <v>11</v>
       </c>
       <c r="AA23" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AB23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AE23" t="n">
         <v>14.5</v>
       </c>
       <c r="AF23" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AG23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH23" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AJ23" t="n">
         <v>180</v>
       </c>
       <c r="AK23" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL23" t="n">
         <v>70</v>
@@ -4933,10 +4933,10 @@
         <v>90</v>
       </c>
       <c r="AN23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AP23" t="n">
         <v>20</v>
@@ -4945,40 +4945,40 @@
         <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BC23" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="BD23" t="n">
         <v>55</v>
@@ -4987,14 +4987,14 @@
         <v>44</v>
       </c>
       <c r="BF23" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5025,43 +5025,43 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="H24" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I24" t="n">
         <v>2.94</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
         <v>2.4</v>
@@ -5076,7 +5076,7 @@
         <v>1.51</v>
       </c>
       <c r="W24" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5094,7 +5094,7 @@
         <v>980</v>
       </c>
       <c r="AC24" t="n">
-        <v>42</v>
+        <v>16.5</v>
       </c>
       <c r="AD24" t="n">
         <v>980</v>
@@ -5109,7 +5109,7 @@
         <v>980</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -5130,65 +5130,65 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.69</v>
+        <v>5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.56</v>
+        <v>7</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.61</v>
+        <v>5.1</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.72</v>
+        <v>5.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.58</v>
+        <v>7.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.72</v>
+        <v>5.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.72</v>
+        <v>5.3</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.57</v>
+        <v>8.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.72</v>
+        <v>4.7</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.72</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.72</v>
+        <v>5.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.72</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.72</v>
+        <v>2.92</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5228,16 +5228,16 @@
         <v>3.3</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
         <v>2.8</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.12</v>
@@ -5267,7 +5267,7 @@
         <v>1.74</v>
       </c>
       <c r="V25" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
         <v>1.57</v>
@@ -5276,7 +5276,7 @@
         <v>9.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z25" t="n">
         <v>27</v>
@@ -5285,22 +5285,22 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
         <v>28</v>
@@ -5315,7 +5315,7 @@
         <v>46</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -5336,7 +5336,7 @@
         <v>19.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AT25" t="n">
         <v>6.4</v>
@@ -5348,7 +5348,7 @@
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX25" t="n">
         <v>12.5</v>
@@ -5360,29 +5360,29 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="BG25" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
         <v>3.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I26" t="n">
         <v>2.76</v>
       </c>
       <c r="J26" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K26" t="n">
         <v>3.3</v>
@@ -5443,7 +5443,7 @@
         <v>1.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q26" t="n">
         <v>2.34</v>
@@ -5455,7 +5455,7 @@
         <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U26" t="n">
         <v>1.87</v>
@@ -5476,7 +5476,7 @@
         <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB26" t="n">
         <v>11</v>
@@ -5485,10 +5485,10 @@
         <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="n">
         <v>23</v>
@@ -5500,40 +5500,40 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AJ26" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AL26" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>65</v>
+        <v>980</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP26" t="n">
         <v>8.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR26" t="n">
         <v>13.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU26" t="n">
         <v>6.2</v>
@@ -5542,7 +5542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX26" t="n">
         <v>18</v>
@@ -5551,32 +5551,32 @@
         <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5613,19 +5613,19 @@
         <v>2.26</v>
       </c>
       <c r="H27" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I27" t="n">
         <v>4.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
         <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
@@ -5721,7 +5721,7 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
         <v>7.6</v>
@@ -5748,16 +5748,16 @@
         <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC27" t="n">
         <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE27" t="n">
         <v>7.8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5801,28 +5801,28 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="G28" t="n">
         <v>2.02</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="K28" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
         <v>3.1</v>
@@ -5831,37 +5831,37 @@
         <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q28" t="n">
         <v>2.14</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="T28" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="V28" t="n">
         <v>1.21</v>
       </c>
       <c r="W28" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y28" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -5870,16 +5870,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG28" t="n">
         <v>13</v>
@@ -5897,7 +5897,7 @@
         <v>28</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
         <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BF28" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G29" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2.62</v>
       </c>
       <c r="H29" t="n">
         <v>2.82</v>
@@ -6028,13 +6028,13 @@
         <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R29" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S29" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T29" t="n">
         <v>1.57</v>
@@ -6046,7 +6046,7 @@
         <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X29" t="n">
         <v>22</v>
@@ -6091,7 +6091,7 @@
         <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM29" t="n">
         <v>55</v>
@@ -6103,16 +6103,16 @@
         <v>17.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ29" t="n">
         <v>15</v>
       </c>
       <c r="AR29" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT29" t="n">
         <v>14.5</v>
@@ -6121,10 +6121,10 @@
         <v>8.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
         <v>18.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         <v>6.6</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K30" t="n">
         <v>4.3</v>
@@ -6228,7 +6228,7 @@
         <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
@@ -6267,7 +6267,7 @@
         <v>95</v>
       </c>
       <c r="AF30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
@@ -6276,10 +6276,10 @@
         <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>17</v>
@@ -6303,10 +6303,10 @@
         <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS30" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AT30" t="n">
         <v>7.6</v>
@@ -6318,7 +6318,7 @@
         <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AX30" t="n">
         <v>8.6</v>
@@ -6330,7 +6330,7 @@
         <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="BB30" t="n">
         <v>14.5</v>
@@ -6342,7 +6342,7 @@
         <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF30" t="n">
         <v>9.4</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.99</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>4.6</v>
@@ -6428,7 +6428,7 @@
         <v>1.97</v>
       </c>
       <c r="U31" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V31" t="n">
         <v>1.27</v>
@@ -6506,7 +6506,7 @@
         <v>7.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV31" t="n">
         <v>17</v>
@@ -6536,7 +6536,7 @@
         <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF31" t="n">
         <v>15.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>4.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
         <v>1.05</v>
@@ -6631,116 +6631,116 @@
         <v>1.42</v>
       </c>
       <c r="X32" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="Y32" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z32" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AA32" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AB32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>230</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX32" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AY32" t="n">
         <v>10</v>
       </c>
-      <c r="AD32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="BB32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BD32" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5.5</v>
       </c>
       <c r="BE32" t="n">
         <v>19</v>
       </c>
       <c r="BF32" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>3.85</v>
       </c>
       <c r="G33" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="H33" t="n">
         <v>2.08</v>
@@ -6789,13 +6789,13 @@
         <v>3.55</v>
       </c>
       <c r="L33" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O33" t="n">
         <v>1.48</v>
@@ -6804,13 +6804,13 @@
         <v>1.57</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R33" t="n">
         <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T33" t="n">
         <v>2.04</v>
@@ -6834,7 +6834,7 @@
         <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AB33" t="n">
         <v>12</v>
@@ -6846,10 +6846,10 @@
         <v>12</v>
       </c>
       <c r="AE33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF33" t="n">
         <v>90</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>500</v>
       </c>
       <c r="AG33" t="n">
         <v>18.5</v>
@@ -6858,7 +6858,7 @@
         <v>24</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ33" t="n">
         <v>1000</v>
@@ -6867,7 +6867,7 @@
         <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
@@ -6918,7 +6918,7 @@
         <v>7.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD33" t="n">
         <v>7.6</v>
@@ -6927,14 +6927,14 @@
         <v>7.8</v>
       </c>
       <c r="BF33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6968,19 +6968,19 @@
         <v>1.62</v>
       </c>
       <c r="G34" t="n">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="H34" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J34" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6992,7 +6992,7 @@
         <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P34" t="n">
         <v>1.24</v>
@@ -7016,7 +7016,7 @@
         <v>1.17</v>
       </c>
       <c r="W34" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7076,49 +7076,49 @@
         <v>1.05</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BF34" t="n">
         <v>1.05</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H35" t="n">
         <v>1.76</v>
@@ -7174,37 +7174,37 @@
         <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
         <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
         <v>1.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T35" t="n">
         <v>1.76</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.77</v>
-      </c>
       <c r="U35" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V35" t="n">
         <v>2.24</v>
@@ -7216,16 +7216,16 @@
         <v>20</v>
       </c>
       <c r="Y35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA35" t="n">
         <v>20</v>
       </c>
       <c r="AB35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC35" t="n">
         <v>11.5</v>
@@ -7243,7 +7243,7 @@
         <v>23</v>
       </c>
       <c r="AH35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI35" t="n">
         <v>34</v>
@@ -7279,7 +7279,7 @@
         <v>15.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU35" t="n">
         <v>8.199999999999999</v>
@@ -7297,32 +7297,32 @@
         <v>18.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA35" t="n">
         <v>27</v>
       </c>
       <c r="BB35" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG35" t="n">
         <v>8</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G36" t="n">
         <v>2.72</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J36" t="n">
         <v>3.25</v>
@@ -7380,7 +7380,7 @@
         <v>3.55</v>
       </c>
       <c r="O36" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P36" t="n">
         <v>1.87</v>
@@ -7398,10 +7398,10 @@
         <v>1.77</v>
       </c>
       <c r="U36" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V36" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W36" t="n">
         <v>1.58</v>
@@ -7419,7 +7419,7 @@
         <v>55</v>
       </c>
       <c r="AB36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC36" t="n">
         <v>7.8</v>
@@ -7431,58 +7431,58 @@
         <v>38</v>
       </c>
       <c r="AF36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG36" t="n">
         <v>12.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AJ36" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK36" t="n">
         <v>30</v>
       </c>
       <c r="AL36" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM36" t="n">
-        <v>200</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO36" t="n">
         <v>36</v>
       </c>
       <c r="AP36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="AT36" t="n">
         <v>9.4</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AX36" t="n">
         <v>14</v>
@@ -7494,29 +7494,29 @@
         <v>14.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BC36" t="n">
         <v>20</v>
       </c>
       <c r="BD36" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BE36" t="n">
         <v>26</v>
       </c>
       <c r="BF36" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BG36" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
         <v>7.8</v>
       </c>
       <c r="J37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K37" t="n">
         <v>4.9</v>
@@ -7601,10 +7601,10 @@
         <v>2.58</v>
       </c>
       <c r="X37" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z37" t="n">
         <v>70</v>
@@ -7613,37 +7613,37 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC37" t="n">
         <v>11</v>
       </c>
       <c r="AD37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE37" t="n">
         <v>120</v>
       </c>
       <c r="AF37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG37" t="n">
         <v>10.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI37" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AJ37" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AK37" t="n">
         <v>17</v>
       </c>
       <c r="AL37" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
@@ -7661,10 +7661,10 @@
         <v>19</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT37" t="n">
         <v>7.6</v>
@@ -7676,7 +7676,7 @@
         <v>21</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX37" t="n">
         <v>8.199999999999999</v>
@@ -7688,7 +7688,7 @@
         <v>19</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BB37" t="n">
         <v>11</v>
@@ -7697,20 +7697,20 @@
         <v>14</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.8</v>
+        <v>28</v>
       </c>
       <c r="BF37" t="n">
         <v>6.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G38" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L38" t="n">
         <v>1.39</v>
@@ -7780,7 +7780,7 @@
         <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
         <v>1.72</v>
@@ -7792,7 +7792,7 @@
         <v>1.27</v>
       </c>
       <c r="W38" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X38" t="n">
         <v>980</v>
@@ -7807,10 +7807,10 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AC38" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -7819,10 +7819,10 @@
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AG38" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AH38" t="n">
         <v>1000</v>
@@ -7834,7 +7834,7 @@
         <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL38" t="n">
         <v>1000</v>
@@ -7843,7 +7843,7 @@
         <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
@@ -7852,59 +7852,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ38" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.26</v>
+        <v>3.75</v>
       </c>
       <c r="AT38" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU38" t="n">
         <v>5.9</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.22</v>
+        <v>3.55</v>
       </c>
       <c r="AX38" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AY38" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF38" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.28</v>
+        <v>5.7</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G39" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H39" t="n">
         <v>3.1</v>
@@ -7947,7 +7947,7 @@
         <v>3.55</v>
       </c>
       <c r="J39" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K39" t="n">
         <v>3.5</v>
@@ -7968,13 +7968,13 @@
         <v>1.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R39" t="n">
         <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T39" t="n">
         <v>1.77</v>
@@ -7986,13 +7986,13 @@
         <v>1.39</v>
       </c>
       <c r="W39" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X39" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Z39" t="n">
         <v>1000</v>
@@ -8007,19 +8007,19 @@
         <v>7.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>980</v>
+        <v>26</v>
       </c>
       <c r="AE39" t="n">
         <v>980</v>
       </c>
       <c r="AF39" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AI39" t="n">
         <v>250</v>
@@ -8028,7 +8028,7 @@
         <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL39" t="n">
         <v>980</v>
@@ -8049,56 +8049,56 @@
         <v>6.2</v>
       </c>
       <c r="AR39" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT39" t="n">
         <v>8.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX39" t="n">
         <v>7.6</v>
       </c>
       <c r="AY39" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ39" t="n">
         <v>12</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB39" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="BC39" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BD39" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG39" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="G40" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I40" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="J40" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L40" t="n">
         <v>1.37</v>
@@ -8174,13 +8174,13 @@
         <v>1.05</v>
       </c>
       <c r="U40" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V40" t="n">
         <v>1.4</v>
       </c>
       <c r="W40" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8240,59 +8240,59 @@
         <v>7.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AU40" t="n">
         <v>5.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.52</v>
+        <v>1.15</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="BE40" t="n">
         <v>17.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G41" t="n">
         <v>3.3</v>
       </c>
       <c r="H41" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I41" t="n">
         <v>2.44</v>
@@ -8356,13 +8356,13 @@
         <v>2.66</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R41" t="n">
         <v>1.62</v>
       </c>
       <c r="S41" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T41" t="n">
         <v>1.51</v>
@@ -8374,13 +8374,13 @@
         <v>1.7</v>
       </c>
       <c r="W41" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X41" t="n">
         <v>32</v>
       </c>
       <c r="Y41" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z41" t="n">
         <v>23</v>
@@ -8389,10 +8389,10 @@
         <v>38</v>
       </c>
       <c r="AB41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC41" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD41" t="n">
         <v>14.5</v>
@@ -8404,13 +8404,13 @@
         <v>30</v>
       </c>
       <c r="AG41" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH41" t="n">
         <v>17</v>
       </c>
-      <c r="AH41" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AI41" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ41" t="n">
         <v>55</v>
@@ -8419,19 +8419,19 @@
         <v>34</v>
       </c>
       <c r="AL41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM41" t="n">
         <v>65</v>
       </c>
       <c r="AN41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO41" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP41" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>13.5</v>
@@ -8440,7 +8440,7 @@
         <v>16.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AT41" t="n">
         <v>15.5</v>
@@ -8455,7 +8455,7 @@
         <v>18.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AY41" t="n">
         <v>10</v>
@@ -8467,26 +8467,26 @@
         <v>20</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BC41" t="n">
         <v>20</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF41" t="n">
         <v>12</v>
       </c>
       <c r="BG41" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G42" t="n">
         <v>2.02</v>
       </c>
-      <c r="G42" t="n">
-        <v>2.06</v>
-      </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
         <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L42" t="n">
         <v>1.33</v>
@@ -8559,22 +8559,22 @@
         <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U42" t="n">
         <v>2.04</v>
       </c>
       <c r="V42" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y42" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z42" t="n">
         <v>980</v>
@@ -8586,13 +8586,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE42" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF42" t="n">
         <v>13</v>
@@ -8604,7 +8604,7 @@
         <v>20</v>
       </c>
       <c r="AI42" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ42" t="n">
         <v>25</v>
@@ -8613,13 +8613,13 @@
         <v>23</v>
       </c>
       <c r="AL42" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
@@ -8628,13 +8628,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR42" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AT42" t="n">
         <v>7.6</v>
@@ -8643,13 +8643,13 @@
         <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW42" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AX42" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY42" t="n">
         <v>9</v>
@@ -8658,7 +8658,7 @@
         <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BB42" t="n">
         <v>20</v>
@@ -8670,17 +8670,17 @@
         <v>30</v>
       </c>
       <c r="BE42" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BF42" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG42" t="n">
-        <v>44</v>
+        <v>6.8</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G43" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="H43" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I43" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>3.75</v>
@@ -8741,10 +8741,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -8905,46 +8905,46 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G44" t="n">
         <v>3.2</v>
       </c>
       <c r="H44" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I44" t="n">
         <v>3.75</v>
       </c>
       <c r="J44" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K44" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="L44" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
         <v>1.02</v>
       </c>
       <c r="N44" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R44" t="n">
         <v>1.27</v>
       </c>
-      <c r="P44" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.25</v>
-      </c>
       <c r="S44" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="T44" t="n">
         <v>1.68</v>
@@ -8953,16 +8953,16 @@
         <v>2.04</v>
       </c>
       <c r="V44" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W44" t="n">
         <v>1.45</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y44" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z44" t="n">
         <v>1000</v>
@@ -8971,13 +8971,13 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC44" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
@@ -8989,7 +8989,7 @@
         <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI44" t="n">
         <v>1000</v>
@@ -9013,62 +9013,62 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.14</v>
+        <v>9.6</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.19</v>
+        <v>7.6</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.19</v>
+        <v>12.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.19</v>
+        <v>4.1</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.19</v>
+        <v>7.2</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.19</v>
+        <v>22</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.19</v>
+        <v>12</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.19</v>
+        <v>8.4</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.16</v>
+        <v>12.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.19</v>
+        <v>4.2</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.19</v>
+        <v>4.1</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.19</v>
+        <v>20</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.19</v>
+        <v>4.2</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.19</v>
+        <v>4.1</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.19</v>
+        <v>18</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.19</v>
+        <v>20</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -9099,19 +9099,19 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G45" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="H45" t="n">
         <v>14</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="J45" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="K45" t="n">
         <v>5.9</v>
@@ -9129,10 +9129,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -9302,10 +9302,10 @@
         <v>10</v>
       </c>
       <c r="I46" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="J46" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K46" t="n">
         <v>7.2</v>
@@ -9317,16 +9317,16 @@
         <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O46" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P46" t="n">
         <v>2.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="R46" t="n">
         <v>1.52</v>
@@ -9359,7 +9359,7 @@
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC46" t="n">
         <v>16.5</v>
@@ -9371,10 +9371,10 @@
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AG46" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="AH46" t="n">
         <v>980</v>
@@ -9386,7 +9386,7 @@
         <v>18</v>
       </c>
       <c r="AK46" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AL46" t="n">
         <v>980</v>
@@ -9395,68 +9395,68 @@
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AO46" t="n">
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="AQ46" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT46" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR46" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AU46" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AW46" t="n">
         <v>5.7</v>
       </c>
       <c r="AX46" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY46" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AZ46" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB46" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC46" t="n">
         <v>7.6</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF46" t="n">
         <v>4</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G47" t="n">
         <v>2.22</v>
@@ -9502,7 +9502,7 @@
         <v>3.55</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L47" t="n">
         <v>1.3</v>
@@ -9514,13 +9514,13 @@
         <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P47" t="n">
         <v>2.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R47" t="n">
         <v>1.4</v>
@@ -9535,7 +9535,7 @@
         <v>2.2</v>
       </c>
       <c r="V47" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W47" t="n">
         <v>1.83</v>
@@ -9544,16 +9544,16 @@
         <v>17.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AA47" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC47" t="n">
         <v>9</v>
@@ -9562,37 +9562,37 @@
         <v>18.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="AF47" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG47" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH47" t="n">
         <v>18</v>
       </c>
       <c r="AI47" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AJ47" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK47" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL47" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AM47" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN47" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO47" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AP47" t="n">
         <v>14.5</v>
@@ -9604,7 +9604,7 @@
         <v>21</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT47" t="n">
         <v>9.199999999999999</v>
@@ -9616,7 +9616,7 @@
         <v>12</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX47" t="n">
         <v>10.5</v>
@@ -9628,7 +9628,7 @@
         <v>14</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB47" t="n">
         <v>19.5</v>
@@ -9637,20 +9637,20 @@
         <v>18</v>
       </c>
       <c r="BD47" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE47" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>5.5</v>
       </c>
       <c r="BF47" t="n">
         <v>10.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -9681,13 +9681,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G48" t="n">
         <v>2.66</v>
       </c>
       <c r="H48" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I48" t="n">
         <v>3.75</v>
@@ -9699,7 +9699,7 @@
         <v>3.45</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
         <v>1.1</v>
@@ -9720,7 +9720,7 @@
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T48" t="n">
         <v>1.94</v>
@@ -9735,7 +9735,7 @@
         <v>1.6</v>
       </c>
       <c r="X48" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y48" t="n">
         <v>13</v>
@@ -9747,19 +9747,19 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD48" t="n">
         <v>18.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG48" t="n">
         <v>14.5</v>
@@ -9768,7 +9768,7 @@
         <v>22</v>
       </c>
       <c r="AI48" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AJ48" t="n">
         <v>46</v>
@@ -9777,7 +9777,7 @@
         <v>40</v>
       </c>
       <c r="AL48" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AM48" t="n">
         <v>1000</v>
@@ -9798,7 +9798,7 @@
         <v>16.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT48" t="n">
         <v>7.2</v>
@@ -9810,7 +9810,7 @@
         <v>11</v>
       </c>
       <c r="AW48" t="n">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="AX48" t="n">
         <v>11</v>
@@ -9822,29 +9822,29 @@
         <v>17.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB48" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BC48" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF48" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BG48" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G49" t="n">
         <v>3.05</v>
@@ -9884,7 +9884,7 @@
         <v>2.56</v>
       </c>
       <c r="I49" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J49" t="n">
         <v>3.35</v>
@@ -9893,7 +9893,7 @@
         <v>3.55</v>
       </c>
       <c r="L49" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M49" t="n">
         <v>1.08</v>
@@ -9905,10 +9905,10 @@
         <v>1.37</v>
       </c>
       <c r="P49" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R49" t="n">
         <v>1.29</v>
@@ -9923,7 +9923,7 @@
         <v>2.02</v>
       </c>
       <c r="V49" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W49" t="n">
         <v>1.48</v>
@@ -9935,7 +9935,7 @@
         <v>10.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AA49" t="n">
         <v>44</v>
@@ -9947,22 +9947,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE49" t="n">
         <v>32</v>
       </c>
       <c r="AF49" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG49" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI49" t="n">
-        <v>980</v>
+        <v>250</v>
       </c>
       <c r="AJ49" t="n">
         <v>55</v>
@@ -9971,7 +9971,7 @@
         <v>38</v>
       </c>
       <c r="AL49" t="n">
-        <v>980</v>
+        <v>270</v>
       </c>
       <c r="AM49" t="n">
         <v>130</v>
@@ -9980,65 +9980,65 @@
         <v>38</v>
       </c>
       <c r="AO49" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AP49" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ49" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR49" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT49" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU49" t="n">
         <v>6.8</v>
       </c>
       <c r="AV49" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AX49" t="n">
         <v>17</v>
       </c>
       <c r="AY49" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ49" t="n">
         <v>15.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC49" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BD49" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE49" t="n">
         <v>26</v>
       </c>
       <c r="BF49" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG49" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -10096,13 +10096,13 @@
         <v>5.5</v>
       </c>
       <c r="O50" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P50" t="n">
         <v>2.52</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R50" t="n">
         <v>1.59</v>
@@ -10129,7 +10129,7 @@
         <v>11</v>
       </c>
       <c r="Z50" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA50" t="n">
         <v>13.5</v>
@@ -10141,7 +10141,7 @@
         <v>11.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AE50" t="n">
         <v>13.5</v>
@@ -10156,7 +10156,7 @@
         <v>22</v>
       </c>
       <c r="AI50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ50" t="n">
         <v>210</v>
@@ -10177,13 +10177,13 @@
         <v>6</v>
       </c>
       <c r="AP50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ50" t="n">
         <v>10</v>
       </c>
       <c r="AR50" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS50" t="n">
         <v>13</v>
@@ -10195,7 +10195,7 @@
         <v>10.5</v>
       </c>
       <c r="AV50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW50" t="n">
         <v>13</v>
@@ -10222,17 +10222,17 @@
         <v>65</v>
       </c>
       <c r="BE50" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF50" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BG50" t="n">
         <v>5.8</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G51" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H51" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J51" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K51" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="L51" t="n">
         <v>1.7</v>
@@ -10287,10 +10287,10 @@
         <v>1.16</v>
       </c>
       <c r="N51" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O51" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="P51" t="n">
         <v>1.4</v>
@@ -10302,43 +10302,43 @@
         <v>1.13</v>
       </c>
       <c r="S51" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T51" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="U51" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V51" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W51" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X51" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Y51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA51" t="n">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="AB51" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC51" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD51" t="n">
         <v>23</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AF51" t="n">
         <v>11.5</v>
@@ -10350,49 +10350,49 @@
         <v>65</v>
       </c>
       <c r="AI51" t="n">
-        <v>150</v>
+        <v>430</v>
       </c>
       <c r="AJ51" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK51" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AM51" t="n">
         <v>390</v>
       </c>
       <c r="AN51" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AO51" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AP51" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR51" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AS51" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU51" t="n">
         <v>6.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW51" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AX51" t="n">
         <v>10</v>
@@ -10410,23 +10410,23 @@
         <v>24</v>
       </c>
       <c r="BC51" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BD51" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BE51" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="BF51" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BG51" t="n">
         <v>46</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -10466,13 +10466,13 @@
         <v>3.4</v>
       </c>
       <c r="I52" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K52" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="L52" t="n">
         <v>1.74</v>
@@ -10481,22 +10481,22 @@
         <v>1.18</v>
       </c>
       <c r="N52" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="P52" t="n">
         <v>1.37</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
         <v>1.12</v>
       </c>
       <c r="S52" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T52" t="n">
         <v>2.5</v>
@@ -10571,7 +10571,7 @@
         <v>7.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS52" t="n">
         <v>32</v>
@@ -10604,13 +10604,13 @@
         <v>25</v>
       </c>
       <c r="BC52" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BD52" t="n">
         <v>40</v>
       </c>
       <c r="BE52" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="BF52" t="n">
         <v>32</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -10651,19 +10651,19 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="G53" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H53" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="I53" t="n">
         <v>990</v>
       </c>
       <c r="J53" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="K53" t="n">
         <v>980</v>
@@ -10702,7 +10702,7 @@
         <v>1.17</v>
       </c>
       <c r="W53" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -10848,22 +10848,22 @@
         <v>3.45</v>
       </c>
       <c r="G54" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H54" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K54" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L54" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M54" t="n">
         <v>1.11</v>
@@ -10872,70 +10872,70 @@
         <v>2.96</v>
       </c>
       <c r="O54" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P54" t="n">
         <v>1.65</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R54" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S54" t="n">
         <v>4.7</v>
       </c>
       <c r="T54" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U54" t="n">
         <v>1.92</v>
       </c>
       <c r="V54" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W54" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X54" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y54" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z54" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA54" t="n">
         <v>980</v>
       </c>
       <c r="AB54" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD54" t="n">
         <v>12</v>
       </c>
       <c r="AE54" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AF54" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AG54" t="n">
         <v>15.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AI54" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ54" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK54" t="n">
         <v>980</v>
@@ -10944,25 +10944,25 @@
         <v>70</v>
       </c>
       <c r="AM54" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN54" t="n">
         <v>60</v>
       </c>
       <c r="AO54" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AP54" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ54" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR54" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS54" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AT54" t="n">
         <v>9.800000000000001</v>
@@ -10974,19 +10974,19 @@
         <v>10.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AX54" t="n">
         <v>16.5</v>
       </c>
       <c r="AY54" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AZ54" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BA54" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BB54" t="n">
         <v>42</v>
@@ -10995,20 +10995,20 @@
         <v>42</v>
       </c>
       <c r="BD54" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BE54" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BF54" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BG54" t="n">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -11039,19 +11039,19 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G55" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H55" t="n">
         <v>4.2</v>
       </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J55" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K55" t="n">
         <v>4.1</v>
@@ -11069,7 +11069,7 @@
         <v>1.29</v>
       </c>
       <c r="P55" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q55" t="n">
         <v>1.83</v>
@@ -11078,7 +11078,7 @@
         <v>1.41</v>
       </c>
       <c r="S55" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T55" t="n">
         <v>1.76</v>
@@ -11093,7 +11093,7 @@
         <v>2.02</v>
       </c>
       <c r="X55" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y55" t="n">
         <v>18</v>
@@ -11111,13 +11111,13 @@
         <v>11</v>
       </c>
       <c r="AD55" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AE55" t="n">
         <v>60</v>
       </c>
       <c r="AF55" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG55" t="n">
         <v>11</v>
@@ -11141,7 +11141,7 @@
         <v>110</v>
       </c>
       <c r="AN55" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO55" t="n">
         <v>60</v>
@@ -11150,13 +11150,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ55" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR55" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AS55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT55" t="n">
         <v>8.6</v>
@@ -11168,7 +11168,7 @@
         <v>15</v>
       </c>
       <c r="AW55" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX55" t="n">
         <v>10.5</v>
@@ -11177,32 +11177,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ55" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB55" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC55" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD55" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BE55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BF55" t="n">
         <v>10</v>
       </c>
       <c r="BG55" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G56" t="n">
         <v>6.6</v>
@@ -11251,7 +11251,7 @@
         <v>4.8</v>
       </c>
       <c r="L56" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M56" t="n">
         <v>1.04</v>
@@ -11272,7 +11272,7 @@
         <v>1.59</v>
       </c>
       <c r="S56" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T56" t="n">
         <v>1.71</v>
@@ -11281,28 +11281,28 @@
         <v>2.24</v>
       </c>
       <c r="V56" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="W56" t="n">
         <v>1.18</v>
       </c>
       <c r="X56" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y56" t="n">
         <v>13</v>
       </c>
       <c r="Z56" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA56" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="AB56" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AC56" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD56" t="n">
         <v>10.5</v>
@@ -11320,28 +11320,28 @@
         <v>980</v>
       </c>
       <c r="AI56" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AJ56" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK56" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AL56" t="n">
         <v>1000</v>
       </c>
       <c r="AM56" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN56" t="n">
         <v>65</v>
       </c>
       <c r="AO56" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AP56" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="AQ56" t="n">
         <v>10</v>
@@ -11350,53 +11350,53 @@
         <v>10</v>
       </c>
       <c r="AS56" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AT56" t="n">
-        <v>19.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU56" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV56" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW56" t="n">
         <v>13.5</v>
       </c>
       <c r="AX56" t="n">
-        <v>42</v>
+        <v>6.2</v>
       </c>
       <c r="AY56" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ56" t="n">
         <v>16.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BB56" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC56" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD56" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE56" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF56" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG56" t="n">
         <v>5.9</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
         <v>2.58</v>
@@ -766,7 +766,7 @@
         <v>3.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -775,7 +775,7 @@
         <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -805,7 +805,7 @@
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
         <v>1.63</v>
@@ -817,13 +817,13 @@
         <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
@@ -835,28 +835,28 @@
         <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
         <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
         <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
         <v>28</v>
@@ -868,7 +868,7 @@
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
         <v>16.5</v>
@@ -898,29 +898,29 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
         <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BG2" t="n">
         <v>36</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -954,28 +954,28 @@
         <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
@@ -990,7 +990,7 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
@@ -999,19 +999,19 @@
         <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
         <v>980</v>
@@ -1020,10 +1020,10 @@
         <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
         <v>980</v>
@@ -1035,86 +1035,86 @@
         <v>980</v>
       </c>
       <c r="AH3" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
         <v>980</v>
       </c>
       <c r="AL3" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
         <v>980</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6.6</v>
       </c>
-      <c r="BG3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
         <v>8.199999999999999</v>
@@ -1196,10 +1196,10 @@
         <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="Y4" t="n">
         <v>980</v>
@@ -1229,7 +1229,7 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AI4" t="n">
         <v>520</v>
@@ -1238,7 +1238,7 @@
         <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
         <v>980</v>
@@ -1253,7 +1253,7 @@
         <v>240</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
         <v>13</v>
@@ -1280,7 +1280,7 @@
         <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
         <v>16.5</v>
@@ -1292,23 +1292,23 @@
         <v>10.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
         <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF4" t="n">
         <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H5" t="n">
         <v>3.1</v>
@@ -1390,7 +1390,7 @@
         <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X5" t="n">
         <v>21</v>
@@ -1468,7 +1468,7 @@
         <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="AX5" t="n">
         <v>7.6</v>
@@ -1489,7 +1489,7 @@
         <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
         <v>2.52</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -1754,7 +1754,7 @@
         <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P7" t="n">
         <v>1.47</v>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
         <v>1.77</v>
@@ -1790,10 +1790,10 @@
         <v>980</v>
       </c>
       <c r="AA7" t="n">
-        <v>230</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -1814,7 +1814,7 @@
         <v>980</v>
       </c>
       <c r="AI7" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -1844,7 +1844,7 @@
         <v>5.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AT7" t="n">
         <v>4.4</v>
@@ -1856,7 +1856,7 @@
         <v>8.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AX7" t="n">
         <v>7.6</v>
@@ -1865,32 +1865,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BG7" t="n">
         <v>6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="n">
         <v>3.25</v>
@@ -1936,10 +1936,10 @@
         <v>2.82</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
@@ -1951,7 +1951,7 @@
         <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
         <v>2.58</v>
@@ -1969,7 +1969,7 @@
         <v>1.7</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
         <v>1.45</v>
@@ -2008,7 +2008,7 @@
         <v>65</v>
       </c>
       <c r="AI8" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>900</v>
@@ -2017,7 +2017,7 @@
         <v>980</v>
       </c>
       <c r="AL8" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2038,19 +2038,19 @@
         <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT8" t="n">
         <v>5.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2059,22 +2059,22 @@
         <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC8" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G9" t="n">
         <v>2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
@@ -2151,7 +2151,7 @@
         <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
         <v>2.6</v>
@@ -2163,7 +2163,7 @@
         <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
         <v>1.56</v>
@@ -2232,7 +2232,7 @@
         <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
         <v>13.5</v>
@@ -2259,7 +2259,7 @@
         <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
         <v>22</v>
@@ -2268,7 +2268,7 @@
         <v>14.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
         <v>14.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -2348,10 +2348,10 @@
         <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="U10" t="n">
         <v>2.52</v>
@@ -2462,7 +2462,7 @@
         <v>14.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I11" t="n">
         <v>2.96</v>
@@ -2518,7 +2518,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -2527,13 +2527,13 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
         <v>2.36</v>
@@ -2548,7 +2548,7 @@
         <v>1.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
@@ -2584,10 +2584,10 @@
         <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI11" t="n">
         <v>290</v>
@@ -2614,13 +2614,13 @@
         <v>9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2629,7 +2629,7 @@
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
         <v>32</v>
@@ -2644,7 +2644,7 @@
         <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
         <v>980</v>
       </c>
       <c r="Z12" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2781,7 +2781,7 @@
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2823,7 +2823,7 @@
         <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW12" t="n">
         <v>7.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
         <v>4.3</v>
@@ -3002,13 +3002,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AT13" t="n">
         <v>5.8</v>
@@ -3017,10 +3017,10 @@
         <v>4.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AX13" t="n">
         <v>6.4</v>
@@ -3029,19 +3029,19 @@
         <v>5.8</v>
       </c>
       <c r="AZ13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BD13" t="n">
         <v>1.42</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>1.47</v>
       </c>
       <c r="BE13" t="n">
         <v>1.43</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>1.83</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
         <v>5.4</v>
@@ -3106,7 +3106,7 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
         <v>5.2</v>
@@ -3127,10 +3127,10 @@
         <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V14" t="n">
         <v>1.23</v>
@@ -3139,7 +3139,7 @@
         <v>2.2</v>
       </c>
       <c r="X14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y14" t="n">
         <v>25</v>
@@ -3184,7 +3184,7 @@
         <v>29</v>
       </c>
       <c r="AM14" t="n">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
         <v>8.199999999999999</v>
@@ -3199,10 +3199,10 @@
         <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3214,7 +3214,7 @@
         <v>16.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
@@ -3226,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3238,17 +3238,17 @@
         <v>14.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -3324,13 +3324,13 @@
         <v>1.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
         <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="BG15" t="n">
         <v>1.55</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="K16" t="n">
         <v>9.800000000000001</v>
@@ -3524,7 +3524,7 @@
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H17" t="n">
         <v>3.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3694,19 +3694,19 @@
         <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P17" t="n">
         <v>3.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S17" t="n">
         <v>1.94</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.95</v>
       </c>
       <c r="T17" t="n">
         <v>1.41</v>
@@ -3715,25 +3715,25 @@
         <v>3.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
         <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
         <v>12</v>
@@ -3748,7 +3748,7 @@
         <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
         <v>14</v>
@@ -3757,34 +3757,34 @@
         <v>36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL17" t="n">
         <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AN17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AQ17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="n">
         <v>34</v>
       </c>
       <c r="AS17" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
         <v>16.5</v>
@@ -3793,34 +3793,34 @@
         <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AX17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BF17" t="n">
         <v>5.8</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>1.39</v>
       </c>
       <c r="G18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K18" t="n">
         <v>5.4</v>
@@ -3888,10 +3888,10 @@
         <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
         <v>1.78</v>
@@ -3903,13 +3903,13 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
         <v>3.4</v>
@@ -3921,7 +3921,7 @@
         <v>32</v>
       </c>
       <c r="Z18" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AA18" t="n">
         <v>440</v>
@@ -3939,7 +3939,7 @@
         <v>190</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
@@ -3951,7 +3951,7 @@
         <v>520</v>
       </c>
       <c r="AJ18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK18" t="n">
         <v>16.5</v>
@@ -3963,7 +3963,7 @@
         <v>430</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3972,16 +3972,16 @@
         <v>16</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU18" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
         <v>17</v>
       </c>
       <c r="AW18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY18" t="n">
         <v>9.6</v>
@@ -4002,7 +4002,7 @@
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
         <v>9.800000000000001</v>
@@ -4017,14 +4017,14 @@
         <v>36</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J19" t="n">
         <v>2.92</v>
@@ -4085,7 +4085,7 @@
         <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
         <v>2.7</v>
@@ -4100,7 +4100,7 @@
         <v>2.14</v>
       </c>
       <c r="U19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V19" t="n">
         <v>1.56</v>
@@ -4121,7 +4121,7 @@
         <v>44</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC19" t="n">
         <v>6.8</v>
@@ -4172,7 +4172,7 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AT19" t="n">
         <v>8.6</v>
@@ -4184,7 +4184,7 @@
         <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AX19" t="n">
         <v>18</v>
@@ -4202,23 +4202,23 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="BE19" t="n">
         <v>22</v>
       </c>
       <c r="BF19" t="n">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="BG19" t="n">
         <v>38</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
         <v>1.96</v>
@@ -4387,7 +4387,7 @@
         <v>14.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
         <v>40</v>
@@ -4399,7 +4399,7 @@
         <v>48</v>
       </c>
       <c r="BD20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BE20" t="n">
         <v>28</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>3.75</v>
       </c>
       <c r="G21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I21" t="n">
         <v>2.28</v>
@@ -4482,28 +4482,28 @@
         <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W21" t="n">
         <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z21" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA21" t="n">
         <v>34</v>
@@ -4512,22 +4512,22 @@
         <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
         <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
         <v>90</v>
       </c>
       <c r="AG21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AI21" t="n">
         <v>980</v>
@@ -4542,10 +4542,10 @@
         <v>380</v>
       </c>
       <c r="AM21" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN21" t="n">
         <v>500</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>110</v>
       </c>
       <c r="AO21" t="n">
         <v>55</v>
@@ -4560,7 +4560,7 @@
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AT21" t="n">
         <v>11.5</v>
@@ -4572,7 +4572,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -4590,23 +4590,23 @@
         <v>55</v>
       </c>
       <c r="BC21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE21" t="n">
         <v>29</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G22" t="n">
         <v>2.54</v>
@@ -4691,10 +4691,10 @@
         <v>1.64</v>
       </c>
       <c r="X22" t="n">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,7 +4703,7 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC22" t="n">
         <v>14</v>
@@ -4721,13 +4721,13 @@
         <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
         <v>1000</v>
@@ -4754,19 +4754,19 @@
         <v>6</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT22" t="n">
         <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
         <v>6.2</v>
@@ -4775,7 +4775,7 @@
         <v>6.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA22" t="n">
         <v>6.8</v>
@@ -4787,20 +4787,20 @@
         <v>6</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BG22" t="n">
         <v>6.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
         <v>1.57</v>
@@ -4852,10 +4852,10 @@
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.22</v>
@@ -4864,7 +4864,7 @@
         <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R23" t="n">
         <v>1.53</v>
@@ -4873,13 +4873,13 @@
         <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U23" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="W23" t="n">
         <v>1.18</v>
@@ -4888,7 +4888,7 @@
         <v>28</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Z23" t="n">
         <v>11</v>
@@ -4933,7 +4933,7 @@
         <v>90</v>
       </c>
       <c r="AN23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AO23" t="n">
         <v>7</v>
@@ -4945,13 +4945,13 @@
         <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS23" t="n">
         <v>13</v>
       </c>
       <c r="AT23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU23" t="n">
         <v>9.800000000000001</v>
@@ -4972,10 +4972,10 @@
         <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB23" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BC23" t="n">
         <v>28</v>
@@ -4987,14 +4987,14 @@
         <v>44</v>
       </c>
       <c r="BF23" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BG23" t="n">
         <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H24" t="n">
         <v>2.18</v>
@@ -5043,13 +5043,13 @@
         <v>6.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.23</v>
@@ -5061,10 +5061,10 @@
         <v>1.69</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T24" t="n">
         <v>1.06</v>
@@ -5115,7 +5115,7 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
         <v>1000</v>
@@ -5127,22 +5127,22 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO24" t="n">
         <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ24" t="n">
         <v>7</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="AT24" t="n">
         <v>7.6</v>
@@ -5154,41 +5154,41 @@
         <v>7.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.92</v>
+        <v>2</v>
       </c>
       <c r="BF24" t="n">
         <v>3.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
         <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
         <v>1.12</v>
@@ -5360,16 +5360,16 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC25" t="n">
         <v>16</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE25" t="n">
         <v>6</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G26" t="n">
         <v>3.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I26" t="n">
         <v>2.76</v>
       </c>
       <c r="J26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
@@ -5446,7 +5446,7 @@
         <v>1.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R26" t="n">
         <v>1.22</v>
@@ -5476,7 +5476,7 @@
         <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AB26" t="n">
         <v>11</v>
@@ -5506,7 +5506,7 @@
         <v>900</v>
       </c>
       <c r="AK26" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="AL26" t="n">
         <v>380</v>
@@ -5515,7 +5515,7 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>38</v>
@@ -5530,7 +5530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AT26" t="n">
         <v>8.800000000000001</v>
@@ -5554,13 +5554,13 @@
         <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BD26" t="n">
         <v>8</v>
@@ -5569,14 +5569,14 @@
         <v>8.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -5664,10 +5664,10 @@
         <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
@@ -5676,13 +5676,13 @@
         <v>8.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AF27" t="n">
         <v>13</v>
@@ -5721,10 +5721,10 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5736,7 +5736,7 @@
         <v>14.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX27" t="n">
         <v>10.5</v>
@@ -5748,29 +5748,29 @@
         <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC27" t="n">
         <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF27" t="n">
         <v>16</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -5831,13 +5831,13 @@
         <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
         <v>2.78</v>
@@ -5846,7 +5846,7 @@
         <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
         <v>1.21</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6001,10 +6001,10 @@
         <v>2.6</v>
       </c>
       <c r="H29" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I29" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J29" t="n">
         <v>3.75</v>
@@ -6028,7 +6028,7 @@
         <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R29" t="n">
         <v>1.59</v>
@@ -6043,7 +6043,7 @@
         <v>2.68</v>
       </c>
       <c r="V29" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W29" t="n">
         <v>1.62</v>
@@ -6073,7 +6073,7 @@
         <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
@@ -6127,7 +6127,7 @@
         <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>11.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6201,10 +6201,10 @@
         <v>6.6</v>
       </c>
       <c r="J30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.3</v>
       </c>
       <c r="L30" t="n">
         <v>1.42</v>
@@ -6216,19 +6216,19 @@
         <v>3.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P30" t="n">
         <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R30" t="n">
         <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
@@ -6267,7 +6267,7 @@
         <v>95</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
@@ -6300,16 +6300,16 @@
         <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS30" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AT30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU30" t="n">
         <v>8.800000000000001</v>
@@ -6321,7 +6321,7 @@
         <v>85</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY30" t="n">
         <v>9.6</v>
@@ -6330,7 +6330,7 @@
         <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BB30" t="n">
         <v>14.5</v>
@@ -6345,14 +6345,14 @@
         <v>100</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG30" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
         <v>42</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN31" t="n">
         <v>16.5</v>
@@ -6536,7 +6536,7 @@
         <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="BF31" t="n">
         <v>15.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L32" t="n">
         <v>1.26</v>
@@ -6604,7 +6604,7 @@
         <v>4.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P32" t="n">
         <v>2.08</v>
@@ -6685,16 +6685,16 @@
         <v>23</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AT32" t="n">
         <v>10.5</v>
@@ -6718,16 +6718,16 @@
         <v>12.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BB32" t="n">
         <v>3.25</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="BE32" t="n">
         <v>19</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
         <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -6894,7 +6894,7 @@
         <v>10</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV33" t="n">
         <v>9.800000000000001</v>
@@ -6930,11 +6930,11 @@
         <v>7.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6989,13 +6989,13 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O34" t="n">
         <v>1.02</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q34" t="n">
         <v>1.29</v>
@@ -7004,7 +7004,7 @@
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="T34" t="n">
         <v>1.05</v>
@@ -7034,7 +7034,7 @@
         <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="BG34" t="n">
         <v>1.55</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G35" t="n">
         <v>5.5</v>
@@ -7168,13 +7168,13 @@
         <v>1.76</v>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="J35" t="n">
         <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7201,19 +7201,19 @@
         <v>2.86</v>
       </c>
       <c r="T35" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="U35" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="V35" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="W35" t="n">
         <v>1.22</v>
       </c>
       <c r="X35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y35" t="n">
         <v>10.5</v>
@@ -7225,25 +7225,25 @@
         <v>20</v>
       </c>
       <c r="AB35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC35" t="n">
         <v>11.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF35" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AG35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH35" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI35" t="n">
         <v>34</v>
@@ -7252,34 +7252,34 @@
         <v>130</v>
       </c>
       <c r="AK35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM35" t="n">
         <v>110</v>
       </c>
       <c r="AN35" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO35" t="n">
         <v>11</v>
       </c>
       <c r="AP35" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>8.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS35" t="n">
         <v>15.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU35" t="n">
         <v>8.199999999999999</v>
@@ -7291,10 +7291,10 @@
         <v>15</v>
       </c>
       <c r="AX35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AY35" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AZ35" t="n">
         <v>16</v>
@@ -7303,26 +7303,26 @@
         <v>27</v>
       </c>
       <c r="BB35" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BC35" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BD35" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF35" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7550,13 +7550,13 @@
         <v>1.52</v>
       </c>
       <c r="G37" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I37" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
         <v>4.2</v>
@@ -7565,49 +7565,49 @@
         <v>4.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M37" t="n">
         <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
         <v>1.26</v>
       </c>
       <c r="P37" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T37" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="U37" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V37" t="n">
         <v>1.15</v>
       </c>
       <c r="W37" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y37" t="n">
         <v>25</v>
       </c>
       <c r="Z37" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
@@ -7619,10 +7619,10 @@
         <v>11</v>
       </c>
       <c r="AD37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE37" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="AF37" t="n">
         <v>10.5</v>
@@ -7631,13 +7631,13 @@
         <v>10.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI37" t="n">
         <v>400</v>
       </c>
       <c r="AJ37" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK37" t="n">
         <v>17</v>
@@ -7649,22 +7649,22 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ37" t="n">
         <v>19</v>
       </c>
       <c r="AR37" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT37" t="n">
         <v>7.6</v>
@@ -7676,7 +7676,7 @@
         <v>21</v>
       </c>
       <c r="AW37" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX37" t="n">
         <v>8.199999999999999</v>
@@ -7685,13 +7685,13 @@
         <v>8.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC37" t="n">
         <v>14</v>
@@ -7706,11 +7706,11 @@
         <v>6.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
         <v>2.1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
         <v>4.8</v>
@@ -7774,7 +7774,7 @@
         <v>1.98</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="R38" t="n">
         <v>1.34</v>
@@ -7786,7 +7786,7 @@
         <v>1.72</v>
       </c>
       <c r="U38" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="V38" t="n">
         <v>1.27</v>
@@ -7855,10 +7855,10 @@
         <v>8.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AT38" t="n">
         <v>5.1</v>
@@ -7870,7 +7870,7 @@
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AX38" t="n">
         <v>5.8</v>
@@ -7879,10 +7879,10 @@
         <v>6.2</v>
       </c>
       <c r="AZ38" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BB38" t="n">
         <v>10.5</v>
@@ -7891,20 +7891,20 @@
         <v>10.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF38" t="n">
         <v>3.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
         <v>40</v>
       </c>
       <c r="AI39" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AJ39" t="n">
         <v>1000</v>
@@ -8043,7 +8043,7 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ39" t="n">
         <v>6.2</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H40" t="n">
         <v>3.25</v>
@@ -8180,10 +8180,10 @@
         <v>1.4</v>
       </c>
       <c r="W40" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y40" t="n">
         <v>1000</v>
@@ -8240,59 +8240,59 @@
         <v>7.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.17</v>
+        <v>5.8</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.17</v>
+        <v>5.1</v>
       </c>
       <c r="AU40" t="n">
         <v>5.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.17</v>
+        <v>8.4</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.17</v>
+        <v>7.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.17</v>
+        <v>7</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="BE40" t="n">
         <v>17.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -8365,10 +8365,10 @@
         <v>2.3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="U41" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V41" t="n">
         <v>1.7</v>
@@ -8419,7 +8419,7 @@
         <v>34</v>
       </c>
       <c r="AL41" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM41" t="n">
         <v>65</v>
@@ -8431,7 +8431,7 @@
         <v>12</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>13.5</v>
@@ -8440,10 +8440,10 @@
         <v>16.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT41" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU41" t="n">
         <v>8.6</v>
@@ -8455,7 +8455,7 @@
         <v>18.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY41" t="n">
         <v>10</v>
@@ -8473,20 +8473,20 @@
         <v>20</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="BE41" t="n">
         <v>4.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BG41" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
         <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="U42" t="n">
         <v>2.04</v>
@@ -8577,7 +8577,7 @@
         <v>18</v>
       </c>
       <c r="Z42" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AA42" t="n">
         <v>900</v>
@@ -8592,7 +8592,7 @@
         <v>19</v>
       </c>
       <c r="AE42" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AF42" t="n">
         <v>13</v>
@@ -8604,7 +8604,7 @@
         <v>20</v>
       </c>
       <c r="AI42" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="AJ42" t="n">
         <v>25</v>
@@ -8613,7 +8613,7 @@
         <v>23</v>
       </c>
       <c r="AL42" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
@@ -8631,7 +8631,7 @@
         <v>13</v>
       </c>
       <c r="AR42" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AS42" t="n">
         <v>7</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8717,7 @@
         <v>2.26</v>
       </c>
       <c r="H43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I43" t="n">
         <v>3.6</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -8905,13 +8905,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G44" t="n">
         <v>3.2</v>
       </c>
       <c r="H44" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I44" t="n">
         <v>3.75</v>
@@ -8986,16 +8986,16 @@
         <v>1000</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH44" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AI44" t="n">
         <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK44" t="n">
         <v>1000</v>
@@ -9049,7 +9049,7 @@
         <v>4.2</v>
       </c>
       <c r="BB44" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC44" t="n">
         <v>20</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -9099,13 +9099,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G45" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H45" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I45" t="n">
         <v>16.5</v>
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q45" t="n">
         <v>1.86</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="G46" t="n">
         <v>1.32</v>
@@ -9302,13 +9302,13 @@
         <v>10</v>
       </c>
       <c r="I46" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="J46" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9317,25 +9317,25 @@
         <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O46" t="n">
         <v>1.21</v>
       </c>
       <c r="P46" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="R46" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S46" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T46" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U46" t="n">
         <v>1.68</v>
@@ -9353,110 +9353,110 @@
         <v>980</v>
       </c>
       <c r="Z46" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG46" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AH46" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AI46" t="n">
         <v>170</v>
       </c>
       <c r="AJ46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV46" t="n">
         <v>18</v>
       </c>
-      <c r="AK46" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR46" t="n">
+      <c r="AW46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY46" t="n">
         <v>9.4</v>
       </c>
-      <c r="AS46" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW46" t="n">
+      <c r="AZ46" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB46" t="n">
         <v>5.7</v>
       </c>
-      <c r="AX46" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC46" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BD46" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BF46" t="n">
         <v>4</v>
       </c>
       <c r="BG46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
         <v>3.55</v>
       </c>
       <c r="K47" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L47" t="n">
         <v>1.3</v>
@@ -9529,7 +9529,7 @@
         <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U47" t="n">
         <v>2.2</v>
@@ -9646,11 +9646,11 @@
         <v>10.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
         <v>1.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R48" t="n">
         <v>1.22</v>
@@ -9726,7 +9726,7 @@
         <v>1.94</v>
       </c>
       <c r="U48" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="V48" t="n">
         <v>1.36</v>
@@ -9744,7 +9744,7 @@
         <v>28</v>
       </c>
       <c r="AA48" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB48" t="n">
         <v>10</v>
@@ -9807,7 +9807,7 @@
         <v>6.2</v>
       </c>
       <c r="AV48" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW48" t="n">
         <v>4.8</v>
@@ -9831,7 +9831,7 @@
         <v>4.7</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.9</v>
+        <v>38</v>
       </c>
       <c r="BE48" t="n">
         <v>5.1</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -9899,28 +9899,28 @@
         <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="O49" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="R49" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="S49" t="n">
-        <v>3.75</v>
+        <v>2.58</v>
       </c>
       <c r="T49" t="n">
-        <v>1.81</v>
+        <v>1.05</v>
       </c>
       <c r="U49" t="n">
-        <v>2.02</v>
+        <v>1.05</v>
       </c>
       <c r="V49" t="n">
         <v>1.56</v>
@@ -9929,116 +9929,116 @@
         <v>1.48</v>
       </c>
       <c r="X49" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="Y49" t="n">
-        <v>10.5</v>
+        <v>980</v>
       </c>
       <c r="Z49" t="n">
-        <v>17.5</v>
+        <v>980</v>
       </c>
       <c r="AA49" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AB49" t="n">
-        <v>11.5</v>
+        <v>980</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD49" t="n">
-        <v>13</v>
+        <v>980</v>
       </c>
       <c r="AE49" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AF49" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AG49" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="AH49" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="AI49" t="n">
-        <v>250</v>
+        <v>980</v>
       </c>
       <c r="AJ49" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AK49" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AL49" t="n">
-        <v>270</v>
+        <v>980</v>
       </c>
       <c r="AM49" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ49" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AR49" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS49" t="n">
-        <v>14.5</v>
+        <v>1.8</v>
       </c>
       <c r="AT49" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU49" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AV49" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AW49" t="n">
-        <v>14.5</v>
+        <v>1.79</v>
       </c>
       <c r="AX49" t="n">
-        <v>17</v>
+        <v>1.75</v>
       </c>
       <c r="AY49" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AZ49" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BA49" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="BB49" t="n">
-        <v>7.8</v>
+        <v>1.81</v>
       </c>
       <c r="BC49" t="n">
-        <v>18</v>
+        <v>1.8</v>
       </c>
       <c r="BD49" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="BE49" t="n">
-        <v>26</v>
+        <v>1.83</v>
       </c>
       <c r="BF49" t="n">
-        <v>7.4</v>
+        <v>1.82</v>
       </c>
       <c r="BG49" t="n">
-        <v>7.2</v>
+        <v>1.82</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G50" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H50" t="n">
         <v>1.49</v>
@@ -10114,19 +10114,19 @@
         <v>1.79</v>
       </c>
       <c r="U50" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V50" t="n">
         <v>3</v>
       </c>
       <c r="W50" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X50" t="n">
         <v>25</v>
       </c>
       <c r="Y50" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z50" t="n">
         <v>9.800000000000001</v>
@@ -10135,7 +10135,7 @@
         <v>13.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AC50" t="n">
         <v>11.5</v>
@@ -10159,31 +10159,31 @@
         <v>27</v>
       </c>
       <c r="AJ50" t="n">
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="AK50" t="n">
         <v>90</v>
       </c>
       <c r="AL50" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM50" t="n">
         <v>95</v>
       </c>
       <c r="AN50" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO50" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AP50" t="n">
         <v>24</v>
       </c>
       <c r="AQ50" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR50" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS50" t="n">
         <v>13</v>
@@ -10222,17 +10222,17 @@
         <v>65</v>
       </c>
       <c r="BE50" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF50" t="n">
         <v>75</v>
       </c>
       <c r="BG50" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G51" t="n">
         <v>2.26</v>
@@ -10275,55 +10275,55 @@
         <v>4.9</v>
       </c>
       <c r="J51" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="K51" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L51" t="n">
         <v>1.7</v>
       </c>
       <c r="M51" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="N51" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O51" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="P51" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R51" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S51" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="T51" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="U51" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V51" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W51" t="n">
         <v>1.79</v>
       </c>
       <c r="X51" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA51" t="n">
         <v>310</v>
@@ -10347,7 +10347,7 @@
         <v>13.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AI51" t="n">
         <v>430</v>
@@ -10359,7 +10359,7 @@
         <v>60</v>
       </c>
       <c r="AL51" t="n">
-        <v>210</v>
+        <v>460</v>
       </c>
       <c r="AM51" t="n">
         <v>390</v>
@@ -10368,19 +10368,19 @@
         <v>100</v>
       </c>
       <c r="AO51" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="AP51" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR51" t="n">
         <v>26</v>
       </c>
       <c r="AS51" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT51" t="n">
         <v>5.4</v>
@@ -10392,7 +10392,7 @@
         <v>19</v>
       </c>
       <c r="AW51" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX51" t="n">
         <v>10</v>
@@ -10401,22 +10401,22 @@
         <v>11.5</v>
       </c>
       <c r="AZ51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA51" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB51" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC51" t="n">
         <v>24</v>
       </c>
       <c r="BD51" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE51" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF51" t="n">
         <v>24</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G52" t="n">
         <v>2.82</v>
@@ -10472,7 +10472,7 @@
         <v>2.78</v>
       </c>
       <c r="K52" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="L52" t="n">
         <v>1.74</v>
@@ -10484,13 +10484,13 @@
         <v>2.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="P52" t="n">
         <v>1.37</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R52" t="n">
         <v>1.12</v>
@@ -10505,7 +10505,7 @@
         <v>1.6</v>
       </c>
       <c r="V52" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W52" t="n">
         <v>1.54</v>
@@ -10520,7 +10520,7 @@
         <v>22</v>
       </c>
       <c r="AA52" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB52" t="n">
         <v>6.8</v>
@@ -10529,10 +10529,10 @@
         <v>7</v>
       </c>
       <c r="AD52" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AF52" t="n">
         <v>15.5</v>
@@ -10553,13 +10553,13 @@
         <v>55</v>
       </c>
       <c r="AL52" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM52" t="n">
         <v>400</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AO52" t="n">
         <v>140</v>
@@ -10610,7 +10610,7 @@
         <v>40</v>
       </c>
       <c r="BE52" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF52" t="n">
         <v>32</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -10845,88 +10845,88 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G54" t="n">
         <v>3.7</v>
       </c>
       <c r="H54" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I54" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
         <v>3.2</v>
       </c>
       <c r="L54" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O54" t="n">
         <v>1.53</v>
       </c>
-      <c r="M54" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1.47</v>
-      </c>
       <c r="P54" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="R54" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S54" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T54" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="U54" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="V54" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W54" t="n">
         <v>1.37</v>
       </c>
       <c r="X54" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y54" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z54" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AA54" t="n">
         <v>980</v>
       </c>
       <c r="AB54" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC54" t="n">
         <v>7</v>
       </c>
       <c r="AD54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE54" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AF54" t="n">
         <v>30</v>
       </c>
       <c r="AG54" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AH54" t="n">
         <v>29</v>
@@ -10941,46 +10941,46 @@
         <v>980</v>
       </c>
       <c r="AL54" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM54" t="n">
         <v>170</v>
       </c>
       <c r="AN54" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AO54" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AP54" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AQ54" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR54" t="n">
         <v>13</v>
       </c>
       <c r="AS54" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AT54" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU54" t="n">
         <v>6.4</v>
       </c>
       <c r="AV54" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW54" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AX54" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY54" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ54" t="n">
         <v>17</v>
@@ -10992,7 +10992,7 @@
         <v>42</v>
       </c>
       <c r="BC54" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BD54" t="n">
         <v>34</v>
@@ -11004,11 +11004,11 @@
         <v>30</v>
       </c>
       <c r="BG54" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
         <v>4.2</v>
       </c>
       <c r="I55" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>3.75</v>
@@ -11063,19 +11063,19 @@
         <v>1.06</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O55" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P55" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q55" t="n">
         <v>1.83</v>
       </c>
       <c r="R55" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S55" t="n">
         <v>3.1</v>
@@ -11084,7 +11084,7 @@
         <v>1.76</v>
       </c>
       <c r="U55" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V55" t="n">
         <v>1.27</v>
@@ -11144,7 +11144,7 @@
         <v>13</v>
       </c>
       <c r="AO55" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP55" t="n">
         <v>14.5</v>
@@ -11156,10 +11156,10 @@
         <v>6.2</v>
       </c>
       <c r="AS55" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT55" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU55" t="n">
         <v>7.8</v>
@@ -11168,7 +11168,7 @@
         <v>15</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX55" t="n">
         <v>10.5</v>
@@ -11192,7 +11192,7 @@
         <v>6.2</v>
       </c>
       <c r="BE55" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF55" t="n">
         <v>10</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -11233,28 +11233,28 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
         <v>6.6</v>
       </c>
       <c r="H56" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I56" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="J56" t="n">
         <v>4.6</v>
       </c>
       <c r="K56" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M56" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N56" t="n">
         <v>5.3</v>
@@ -11263,7 +11263,7 @@
         <v>1.2</v>
       </c>
       <c r="P56" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q56" t="n">
         <v>1.6</v>
@@ -11275,13 +11275,13 @@
         <v>2.5</v>
       </c>
       <c r="T56" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U56" t="n">
         <v>2.24</v>
       </c>
       <c r="V56" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="W56" t="n">
         <v>1.18</v>
@@ -11326,7 +11326,7 @@
         <v>170</v>
       </c>
       <c r="AK56" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL56" t="n">
         <v>1000</v>
@@ -11338,7 +11338,7 @@
         <v>65</v>
       </c>
       <c r="AO56" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AP56" t="n">
         <v>19.5</v>
@@ -11353,7 +11353,7 @@
         <v>12.5</v>
       </c>
       <c r="AT56" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU56" t="n">
         <v>9.800000000000001</v>
@@ -11365,7 +11365,7 @@
         <v>13.5</v>
       </c>
       <c r="AX56" t="n">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="AY56" t="n">
         <v>20</v>
@@ -11374,29 +11374,29 @@
         <v>16.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC56" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC56" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD56" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE56" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF56" t="n">
-        <v>6.4</v>
+        <v>48</v>
       </c>
       <c r="BG56" t="n">
         <v>5.9</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -775,109 +775,109 @@
         <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AK2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="n">
         <v>48</v>
       </c>
-      <c r="AL2" t="n">
-        <v>46</v>
-      </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
         <v>6.6</v>
@@ -886,10 +886,10 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -898,29 +898,29 @@
         <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BC2" t="n">
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -951,43 +951,43 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I3" t="n">
         <v>2.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
         <v>4.7</v>
@@ -1002,7 +1002,7 @@
         <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
         <v>21</v>
@@ -1011,7 +1011,7 @@
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
         <v>980</v>
@@ -1029,7 +1029,7 @@
         <v>980</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AG3" t="n">
         <v>980</v>
@@ -1044,7 +1044,7 @@
         <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1068,7 +1068,7 @@
         <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
         <v>5.6</v>
@@ -1080,10 +1080,10 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
@@ -1104,7 +1104,7 @@
         <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>7.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4" t="n">
         <v>4.3</v>
@@ -1163,40 +1163,40 @@
         <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
         <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
         <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X4" t="n">
         <v>30</v>
@@ -1214,7 +1214,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
         <v>980</v>
@@ -1253,16 +1253,16 @@
         <v>240</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4" t="n">
         <v>6.8</v>
@@ -1274,7 +1274,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
@@ -1283,10 +1283,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB4" t="n">
         <v>10.5</v>
@@ -1298,7 +1298,7 @@
         <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
         <v>6.8</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1342,43 +1342,43 @@
         <v>2.46</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H5" t="n">
         <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
         <v>1.89</v>
@@ -1387,10 +1387,10 @@
         <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>21</v>
@@ -1405,7 +1405,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AC5" t="n">
         <v>14</v>
@@ -1423,13 +1423,13 @@
         <v>980</v>
       </c>
       <c r="AH5" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>980</v>
@@ -1444,7 +1444,7 @@
         <v>980</v>
       </c>
       <c r="AO5" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
         <v>5.1</v>
@@ -1453,22 +1453,22 @@
         <v>5.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV5" t="n">
         <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>7.6</v>
@@ -1477,32 +1477,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>2.98</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.2</v>
+        <v>2.86</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="BF5" t="n">
         <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1548,10 +1548,10 @@
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
@@ -1566,13 +1566,13 @@
         <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1587,13 +1587,13 @@
         <v>2.04</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1629,13 +1629,13 @@
         <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,13 +1644,13 @@
         <v>5.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,10 +1659,10 @@
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1671,10 +1671,10 @@
         <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
         <v>9</v>
@@ -1683,20 +1683,20 @@
         <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H7" t="n">
         <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
         <v>1.52</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="Z7" t="n">
         <v>980</v>
@@ -1793,7 +1793,7 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
@@ -1817,13 +1817,13 @@
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AK7" t="n">
         <v>980</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
         <v>8.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.56</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.3</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
         <v>8</v>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
         <v>2.82</v>
       </c>
       <c r="I8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.25</v>
       </c>
-      <c r="J8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X8" t="n">
         <v>16</v>
@@ -1993,7 +1993,7 @@
         <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AE8" t="n">
         <v>980</v>
@@ -2008,7 +2008,7 @@
         <v>65</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AJ8" t="n">
         <v>900</v>
@@ -2029,7 +2029,7 @@
         <v>980</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AQ8" t="n">
         <v>5.1</v>
@@ -2038,10 +2038,10 @@
         <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -2056,35 +2056,35 @@
         <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC8" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BD8" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2133,28 +2133,28 @@
         <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
         <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R9" t="n">
         <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
         <v>1.59</v>
@@ -2163,7 +2163,7 @@
         <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
         <v>1.56</v>
@@ -2271,14 +2271,14 @@
         <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG9" t="n">
         <v>14.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2309,31 +2309,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -2342,13 +2342,13 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
         <v>1.55</v>
@@ -2360,7 +2360,7 @@
         <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
         <v>27</v>
@@ -2381,7 +2381,7 @@
         <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>28</v>
@@ -2405,7 +2405,7 @@
         <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
         <v>200</v>
@@ -2438,7 +2438,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX10" t="n">
         <v>16.5</v>
@@ -2450,19 +2450,19 @@
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2506,49 +2506,49 @@
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
@@ -2557,13 +2557,13 @@
         <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y11" t="n">
         <v>9.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
         <v>46</v>
@@ -2578,19 +2578,19 @@
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF11" t="n">
         <v>19.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
         <v>50</v>
@@ -2602,16 +2602,16 @@
         <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
         <v>42</v>
       </c>
       <c r="AO11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.800000000000001</v>
@@ -2620,7 +2620,7 @@
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2629,22 +2629,22 @@
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
         <v>32</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -2653,20 +2653,20 @@
         <v>34</v>
       </c>
       <c r="BD11" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE11" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF11" t="n">
         <v>29</v>
       </c>
-      <c r="BF11" t="n">
-        <v>16</v>
-      </c>
       <c r="BG11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2697,67 +2697,67 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="X12" t="n">
         <v>30</v>
       </c>
       <c r="Y12" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z12" t="n">
         <v>980</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>120</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2781,16 +2781,16 @@
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>900</v>
+        <v>23</v>
       </c>
       <c r="AK12" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
         <v>980</v>
@@ -2811,56 +2811,56 @@
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT12" t="n">
         <v>5.1</v>
       </c>
       <c r="AU12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV12" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV12" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AW12" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AX12" t="n">
         <v>9.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G13" t="n">
         <v>1.85</v>
@@ -2903,34 +2903,34 @@
         <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
         <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
         <v>1.71</v>
@@ -2939,7 +2939,7 @@
         <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
         <v>2.16</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H14" t="n">
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
@@ -3103,40 +3103,40 @@
         <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
         <v>1.61</v>
       </c>
       <c r="U14" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X14" t="n">
         <v>24</v>
@@ -3160,7 +3160,7 @@
         <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AF14" t="n">
         <v>14</v>
@@ -3190,7 +3190,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP14" t="n">
         <v>19.5</v>
@@ -3199,10 +3199,10 @@
         <v>20</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3214,7 +3214,7 @@
         <v>16.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
@@ -3226,7 +3226,7 @@
         <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3235,20 +3235,20 @@
         <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3303,13 +3303,13 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Q15" t="n">
         <v>1.2</v>
@@ -3324,7 +3324,7 @@
         <v>1.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
         <v>1.14</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3482,13 +3482,13 @@
         <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="K16" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,34 +3497,34 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
         <v>2.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="S16" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3575,13 +3575,13 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AQ16" t="n">
         <v>4.2</v>
@@ -3593,10 +3593,10 @@
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AV16" t="n">
         <v>4.2</v>
@@ -3605,38 +3605,38 @@
         <v>4.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="BA16" t="n">
         <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BG16" t="n">
         <v>6.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3667,46 +3667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
         <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O17" t="n">
         <v>1.13</v>
       </c>
       <c r="P17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S17" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="T17" t="n">
         <v>1.41</v>
@@ -3715,40 +3715,40 @@
         <v>3.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
         <v>2.02</v>
       </c>
       <c r="X17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z17" t="n">
         <v>38</v>
       </c>
-      <c r="Y17" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>42</v>
-      </c>
       <c r="AA17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE17" t="n">
         <v>85</v>
       </c>
-      <c r="AB17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>18</v>
       </c>
-      <c r="AE17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>14</v>
@@ -3757,7 +3757,7 @@
         <v>36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK17" t="n">
         <v>16.5</v>
@@ -3766,19 +3766,19 @@
         <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AN17" t="n">
         <v>6.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR17" t="n">
         <v>34</v>
@@ -3787,50 +3787,50 @@
         <v>28</v>
       </c>
       <c r="AT17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB17" t="n">
         <v>23</v>
       </c>
-      <c r="BB17" t="n">
-        <v>22</v>
-      </c>
       <c r="BC17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG17" t="n">
         <v>18</v>
       </c>
-      <c r="BE17" t="n">
-        <v>18</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H18" t="n">
         <v>10</v>
@@ -3873,64 +3873,64 @@
         <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K18" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z18" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA18" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD18" t="n">
         <v>38</v>
@@ -3939,7 +3939,7 @@
         <v>190</v>
       </c>
       <c r="AF18" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
@@ -3954,43 +3954,43 @@
         <v>11.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
         <v>430</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
         <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AW18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX18" t="n">
         <v>7.2</v>
@@ -4002,7 +4002,7 @@
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB18" t="n">
         <v>9.800000000000001</v>
@@ -4011,20 +4011,20 @@
         <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BE18" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I19" t="n">
         <v>2.78</v>
@@ -4070,25 +4070,25 @@
         <v>2.92</v>
       </c>
       <c r="K19" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L19" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
         <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O19" t="n">
         <v>1.56</v>
       </c>
       <c r="P19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R19" t="n">
         <v>1.19</v>
@@ -4127,7 +4127,7 @@
         <v>6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE19" t="n">
         <v>40</v>
@@ -4139,7 +4139,7 @@
         <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
         <v>70</v>
@@ -4148,7 +4148,7 @@
         <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="AL19" t="n">
         <v>460</v>
@@ -4163,7 +4163,7 @@
         <v>120</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.4</v>
@@ -4193,32 +4193,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA19" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="BC19" t="n">
         <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BE19" t="n">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="BF19" t="n">
         <v>55</v>
       </c>
       <c r="BG19" t="n">
-        <v>38</v>
+        <v>13.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>3.9</v>
       </c>
       <c r="G20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H20" t="n">
         <v>2.2</v>
       </c>
       <c r="I20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J20" t="n">
         <v>3.25</v>
@@ -4267,28 +4267,28 @@
         <v>3.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.42</v>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T20" t="n">
         <v>1.94</v>
@@ -4297,13 +4297,13 @@
         <v>1.96</v>
       </c>
       <c r="V20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
         <v>8.199999999999999</v>
@@ -4339,7 +4339,7 @@
         <v>48</v>
       </c>
       <c r="AJ20" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AK20" t="n">
         <v>150</v>
@@ -4360,7 +4360,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR20" t="n">
         <v>11.5</v>
@@ -4378,7 +4378,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4393,26 +4393,26 @@
         <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
         <v>48</v>
       </c>
       <c r="BD20" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BE20" t="n">
         <v>28</v>
       </c>
       <c r="BF20" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="BG20" t="n">
         <v>20</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4446,13 +4446,13 @@
         <v>3.75</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>3.3</v>
@@ -4461,22 +4461,22 @@
         <v>3.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
         <v>1.3</v>
@@ -4485,16 +4485,16 @@
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
         <v>23</v>
@@ -4506,7 +4506,7 @@
         <v>25</v>
       </c>
       <c r="AA21" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="AB21" t="n">
         <v>13</v>
@@ -4521,22 +4521,22 @@
         <v>65</v>
       </c>
       <c r="AF21" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AG21" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>46</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>980</v>
+        <v>190</v>
       </c>
       <c r="AJ21" t="n">
         <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>980</v>
+        <v>240</v>
       </c>
       <c r="AL21" t="n">
         <v>380</v>
@@ -4560,7 +4560,7 @@
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AT21" t="n">
         <v>11.5</v>
@@ -4572,10 +4572,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>13.5</v>
@@ -4584,29 +4584,29 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BB21" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BE21" t="n">
         <v>29</v>
       </c>
       <c r="BF21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="H22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="T22" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U22" t="n">
         <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="X22" t="n">
         <v>23</v>
       </c>
       <c r="Y22" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4709,7 +4709,7 @@
         <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
@@ -4721,7 +4721,7 @@
         <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4739,7 +4739,7 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
@@ -4751,22 +4751,22 @@
         <v>7.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AT22" t="n">
         <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV22" t="n">
         <v>9</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX22" t="n">
         <v>6.2</v>
@@ -4775,32 +4775,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD22" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>6.6</v>
       </c>
       <c r="BE22" t="n">
         <v>3.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="H23" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="I23" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="J23" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
         <v>1.04</v>
@@ -4858,143 +4858,143 @@
         <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="T23" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="U23" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V23" t="n">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Y23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC23" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>11</v>
-      </c>
       <c r="AD23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AF23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>130</v>
       </c>
-      <c r="AG23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>180</v>
-      </c>
       <c r="AK23" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="AN23" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AO23" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT23" t="n">
         <v>20</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>22</v>
-      </c>
       <c r="AU23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
         <v>26</v>
       </c>
       <c r="BB23" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC23" t="n">
         <v>28</v>
       </c>
       <c r="BD23" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BE23" t="n">
         <v>44</v>
       </c>
       <c r="BF23" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5025,46 +5025,46 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="G24" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="I24" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="T24" t="n">
         <v>1.06</v>
@@ -5073,13 +5073,13 @@
         <v>1.05</v>
       </c>
       <c r="V24" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y24" t="n">
         <v>980</v>
@@ -5127,22 +5127,22 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
         <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ24" t="n">
         <v>7</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="AT24" t="n">
         <v>7.6</v>
@@ -5154,31 +5154,31 @@
         <v>7.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY24" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="BE24" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BF24" t="n">
         <v>3.9</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5225,34 +5225,34 @@
         <v>2.76</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N25" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P25" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
@@ -5261,13 +5261,13 @@
         <v>5.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U25" t="n">
         <v>1.74</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
         <v>1.57</v>
@@ -5276,52 +5276,52 @@
         <v>9.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z25" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC25" t="n">
         <v>7.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AK25" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AL25" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
@@ -5336,7 +5336,7 @@
         <v>19.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AT25" t="n">
         <v>6.4</v>
@@ -5348,7 +5348,7 @@
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX25" t="n">
         <v>12.5</v>
@@ -5360,29 +5360,29 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BG25" t="n">
         <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
         <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
@@ -5446,16 +5446,16 @@
         <v>1.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R26" t="n">
         <v>1.22</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U26" t="n">
         <v>1.87</v>
@@ -5470,10 +5470,10 @@
         <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA26" t="n">
         <v>150</v>
@@ -5518,7 +5518,7 @@
         <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AP26" t="n">
         <v>8.6</v>
@@ -5554,7 +5554,7 @@
         <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
         <v>23</v>
@@ -5563,20 +5563,20 @@
         <v>7.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
@@ -5640,7 +5640,7 @@
         <v>1.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R27" t="n">
         <v>1.26</v>
@@ -5649,10 +5649,10 @@
         <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V27" t="n">
         <v>1.29</v>
@@ -5670,7 +5670,7 @@
         <v>30</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
         <v>8.4</v>
@@ -5715,13 +5715,13 @@
         <v>85</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS27" t="n">
         <v>9</v>
@@ -5733,19 +5733,19 @@
         <v>6.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW27" t="n">
         <v>8.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
         <v>8.800000000000001</v>
@@ -5754,7 +5754,7 @@
         <v>8</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>8.199999999999999</v>
@@ -5763,14 +5763,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG27" t="n">
         <v>9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5819,13 +5819,13 @@
         <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
         <v>1.39</v>
@@ -5837,16 +5837,16 @@
         <v>2.18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
         <v>2.78</v>
       </c>
       <c r="T28" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="V28" t="n">
         <v>1.21</v>
@@ -5909,46 +5909,46 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS28" t="n">
         <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA28" t="n">
         <v>5.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD28" t="n">
         <v>5.6</v>
@@ -5957,14 +5957,14 @@
         <v>6</v>
       </c>
       <c r="BF28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG28" t="n">
         <v>6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H29" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I29" t="n">
         <v>2.84</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.86</v>
       </c>
       <c r="J29" t="n">
         <v>3.75</v>
@@ -6013,28 +6013,28 @@
         <v>3.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
         <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P29" t="n">
         <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R29" t="n">
         <v>1.59</v>
       </c>
       <c r="S29" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T29" t="n">
         <v>1.57</v>
@@ -6043,13 +6043,13 @@
         <v>2.68</v>
       </c>
       <c r="V29" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
         <v>16</v>
@@ -6100,7 +6100,7 @@
         <v>15.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
         <v>20</v>
@@ -6127,7 +6127,7 @@
         <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY29" t="n">
         <v>11.5</v>
@@ -6139,7 +6139,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6189,109 +6189,109 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="G30" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I30" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V30" t="n">
         <v>1.17</v>
       </c>
       <c r="W30" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
         <v>20</v>
       </c>
       <c r="Z30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC30" t="n">
         <v>9</v>
       </c>
       <c r="AD30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE30" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF30" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ30" t="n">
         <v>15</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM30" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO30" t="n">
         <v>130</v>
@@ -6303,46 +6303,46 @@
         <v>18.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS30" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AT30" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW30" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY30" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BB30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC30" t="n">
         <v>16.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE30" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BF30" t="n">
         <v>9.199999999999999</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="G31" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="H31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J31" t="n">
         <v>3.55</v>
@@ -6416,7 +6416,7 @@
         <v>1.81</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
@@ -6425,19 +6425,19 @@
         <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U31" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y31" t="n">
         <v>14</v>
@@ -6449,13 +6449,13 @@
         <v>110</v>
       </c>
       <c r="AB31" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC31" t="n">
         <v>7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE31" t="n">
         <v>65</v>
@@ -6473,7 +6473,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
         <v>22</v>
@@ -6488,7 +6488,7 @@
         <v>16.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP31" t="n">
         <v>11</v>
@@ -6497,37 +6497,37 @@
         <v>13.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS31" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AT31" t="n">
         <v>7.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW31" t="n">
         <v>55</v>
       </c>
       <c r="AX31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
         <v>65</v>
       </c>
       <c r="BB31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
@@ -6536,17 +6536,17 @@
         <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BF31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG31" t="n">
         <v>70</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6580,43 +6580,43 @@
         <v>2.94</v>
       </c>
       <c r="G32" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="I32" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
         <v>1.64</v>
@@ -6628,119 +6628,119 @@
         <v>1.64</v>
       </c>
       <c r="W32" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X32" t="n">
-        <v>980</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Z32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF32" t="n">
         <v>23</v>
       </c>
-      <c r="AA32" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>32</v>
-      </c>
       <c r="AG32" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI32" t="n">
         <v>230</v>
       </c>
       <c r="AJ32" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK32" t="n">
         <v>220</v>
       </c>
-      <c r="AK32" t="n">
-        <v>46</v>
-      </c>
       <c r="AL32" t="n">
-        <v>130</v>
+        <v>980</v>
       </c>
       <c r="AM32" t="n">
         <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO32" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.44</v>
+        <v>10</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.54</v>
+        <v>14.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.68</v>
+        <v>9.4</v>
       </c>
       <c r="AT32" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU32" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA32" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW32" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY32" t="n">
+      <c r="BB32" t="n">
         <v>10</v>
       </c>
-      <c r="AZ32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BC32" t="n">
-        <v>2.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE32" t="n">
         <v>19</v>
       </c>
       <c r="BF32" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG32" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6780,34 +6780,34 @@
         <v>2.08</v>
       </c>
       <c r="I33" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J33" t="n">
         <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M33" t="n">
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="O33" t="n">
         <v>1.48</v>
       </c>
       <c r="P33" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
         <v>4.8</v>
@@ -6816,7 +6816,7 @@
         <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -6825,7 +6825,7 @@
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y33" t="n">
         <v>7.6</v>
@@ -6840,10 +6840,10 @@
         <v>12</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE33" t="n">
         <v>75</v>
@@ -6855,10 +6855,10 @@
         <v>18.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AI33" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ33" t="n">
         <v>1000</v>
@@ -6867,7 +6867,7 @@
         <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
@@ -6876,10 +6876,10 @@
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.2</v>
@@ -6897,7 +6897,7 @@
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW33" t="n">
         <v>13</v>
@@ -6909,32 +6909,32 @@
         <v>15</v>
       </c>
       <c r="AZ33" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB33" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF33" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="G34" t="n">
-        <v>5.5</v>
+        <v>1.86</v>
       </c>
       <c r="H34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.5</v>
-      </c>
-      <c r="I34" t="n">
-        <v>870</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.31</v>
       </c>
       <c r="T34" t="n">
         <v>1.05</v>
@@ -7013,10 +7013,10 @@
         <v>1.05</v>
       </c>
       <c r="V34" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>2.16</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7067,68 +7067,68 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="BG34" t="n">
         <v>1.55</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7159,61 +7159,61 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G35" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H35" t="n">
         <v>1.76</v>
       </c>
       <c r="I35" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J35" t="n">
         <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M35" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R35" t="n">
         <v>1.43</v>
       </c>
       <c r="S35" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="T35" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="U35" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V35" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="W35" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X35" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y35" t="n">
         <v>10.5</v>
@@ -7225,10 +7225,10 @@
         <v>20</v>
       </c>
       <c r="AB35" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
         <v>9.800000000000001</v>
@@ -7237,92 +7237,92 @@
         <v>18</v>
       </c>
       <c r="AF35" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AG35" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI35" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ35" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK35" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL35" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM35" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN35" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ35" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR35" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS35" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AT35" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV35" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW35" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AY35" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA35" t="n">
         <v>27</v>
       </c>
       <c r="BB35" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BD35" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BE35" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7353,49 +7353,49 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G36" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H36" t="n">
         <v>3.05</v>
       </c>
       <c r="I36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O36" t="n">
         <v>1.38</v>
       </c>
-      <c r="M36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.32</v>
-      </c>
       <c r="P36" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U36" t="n">
         <v>2.08</v>
@@ -7404,13 +7404,13 @@
         <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X36" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z36" t="n">
         <v>22</v>
@@ -7419,10 +7419,10 @@
         <v>55</v>
       </c>
       <c r="AB36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD36" t="n">
         <v>14</v>
@@ -7431,7 +7431,7 @@
         <v>38</v>
       </c>
       <c r="AF36" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG36" t="n">
         <v>12.5</v>
@@ -7440,7 +7440,7 @@
         <v>17.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ36" t="n">
         <v>40</v>
@@ -7452,16 +7452,16 @@
         <v>46</v>
       </c>
       <c r="AM36" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO36" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ36" t="n">
         <v>10</v>
@@ -7473,16 +7473,16 @@
         <v>42</v>
       </c>
       <c r="AT36" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV36" t="n">
         <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AX36" t="n">
         <v>14</v>
@@ -7494,29 +7494,29 @@
         <v>14.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="BB36" t="n">
         <v>30</v>
       </c>
       <c r="BC36" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD36" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BE36" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BF36" t="n">
         <v>21</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7550,124 +7550,124 @@
         <v>1.52</v>
       </c>
       <c r="G37" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K37" t="n">
         <v>4.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="M37" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P37" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T37" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="U37" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V37" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W37" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="X37" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z37" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE37" t="n">
         <v>510</v>
       </c>
       <c r="AF37" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG37" t="n">
         <v>10.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI37" t="n">
         <v>400</v>
       </c>
       <c r="AJ37" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK37" t="n">
         <v>17</v>
       </c>
       <c r="AL37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO37" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ37" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AS37" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT37" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU37" t="n">
         <v>8.6</v>
@@ -7676,25 +7676,25 @@
         <v>21</v>
       </c>
       <c r="AW37" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AX37" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY37" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA37" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB37" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD37" t="n">
         <v>18</v>
@@ -7706,11 +7706,11 @@
         <v>6.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7744,28 +7744,28 @@
         <v>1.91</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H38" t="n">
         <v>4</v>
       </c>
       <c r="I38" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
         <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O38" t="n">
         <v>1.32</v>
@@ -7774,25 +7774,25 @@
         <v>1.98</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="R38" t="n">
         <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="T38" t="n">
         <v>1.72</v>
       </c>
       <c r="U38" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V38" t="n">
         <v>1.27</v>
       </c>
       <c r="W38" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X38" t="n">
         <v>980</v>
@@ -7849,7 +7849,7 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ38" t="n">
         <v>8.4</v>
@@ -7858,7 +7858,7 @@
         <v>7.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AT38" t="n">
         <v>5.1</v>
@@ -7870,7 +7870,7 @@
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AX38" t="n">
         <v>5.8</v>
@@ -7882,7 +7882,7 @@
         <v>11.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BB38" t="n">
         <v>10.5</v>
@@ -7900,11 +7900,11 @@
         <v>3.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7935,16 +7935,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G39" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H39" t="n">
         <v>3.1</v>
       </c>
       <c r="I39" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J39" t="n">
         <v>3.2</v>
@@ -7956,37 +7956,37 @@
         <v>1.48</v>
       </c>
       <c r="M39" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O39" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P39" t="n">
         <v>1.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R39" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T39" t="n">
         <v>1.77</v>
       </c>
       <c r="U39" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V39" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W39" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X39" t="n">
         <v>21</v>
@@ -8019,7 +8019,7 @@
         <v>19.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI39" t="n">
         <v>500</v>
@@ -8028,7 +8028,7 @@
         <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
         <v>980</v>
@@ -8052,19 +8052,19 @@
         <v>10.5</v>
       </c>
       <c r="AS39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT39" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT39" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AU39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV39" t="n">
         <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX39" t="n">
         <v>7.6</v>
@@ -8076,29 +8076,29 @@
         <v>12</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB39" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC39" t="n">
         <v>22</v>
       </c>
       <c r="BD39" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE39" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8129,43 +8129,43 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="G40" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="H40" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I40" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J40" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L40" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O40" t="n">
         <v>1.39</v>
       </c>
       <c r="P40" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -8177,10 +8177,10 @@
         <v>1.9</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W40" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="X40" t="n">
         <v>90</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8326,28 +8326,28 @@
         <v>2.92</v>
       </c>
       <c r="G41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H41" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="I41" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>3.85</v>
       </c>
       <c r="K41" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M41" t="n">
         <v>1.03</v>
       </c>
       <c r="N41" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
         <v>1.18</v>
@@ -8356,25 +8356,25 @@
         <v>2.66</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R41" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S41" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T41" t="n">
         <v>1.54</v>
       </c>
       <c r="U41" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V41" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W41" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X41" t="n">
         <v>32</v>
@@ -8386,7 +8386,7 @@
         <v>23</v>
       </c>
       <c r="AA41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB41" t="n">
         <v>21</v>
@@ -8428,7 +8428,7 @@
         <v>20</v>
       </c>
       <c r="AO41" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP41" t="n">
         <v>11.5</v>
@@ -8440,7 +8440,7 @@
         <v>16.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT41" t="n">
         <v>16</v>
@@ -8467,7 +8467,7 @@
         <v>20</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC41" t="n">
         <v>20</v>
@@ -8476,7 +8476,7 @@
         <v>16</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF41" t="n">
         <v>15.5</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8517,64 +8517,64 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="H42" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I42" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L42" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="M42" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T42" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q42" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.72</v>
-      </c>
       <c r="U42" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="V42" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W42" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="X42" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z42" t="n">
         <v>80</v>
@@ -8583,16 +8583,16 @@
         <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AF42" t="n">
         <v>13</v>
@@ -8601,19 +8601,19 @@
         <v>11</v>
       </c>
       <c r="AH42" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>330</v>
+        <v>170</v>
       </c>
       <c r="AJ42" t="n">
         <v>25</v>
       </c>
       <c r="AK42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL42" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
@@ -8634,10 +8634,10 @@
         <v>13</v>
       </c>
       <c r="AS42" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT42" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU42" t="n">
         <v>7</v>
@@ -8658,7 +8658,7 @@
         <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="BB42" t="n">
         <v>20</v>
@@ -8667,20 +8667,20 @@
         <v>18</v>
       </c>
       <c r="BD42" t="n">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BF42" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8711,13 +8711,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G43" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H43" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I43" t="n">
         <v>3.6</v>
@@ -8726,7 +8726,7 @@
         <v>3.75</v>
       </c>
       <c r="K43" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8744,7 +8744,7 @@
         <v>2.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8905,58 +8905,58 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="G44" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="H44" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="I44" t="n">
-        <v>3.75</v>
+        <v>2.96</v>
       </c>
       <c r="J44" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K44" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="O44" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="P44" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="Q44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U44" t="n">
         <v>1.87</v>
       </c>
-      <c r="R44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.04</v>
-      </c>
       <c r="V44" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W44" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="X44" t="n">
         <v>16</v>
@@ -9013,7 +9013,7 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="AQ44" t="n">
         <v>7.6</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="G45" t="n">
         <v>1.35</v>
       </c>
       <c r="H45" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="I45" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="J45" t="n">
         <v>5.1</v>
       </c>
       <c r="K45" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -9129,10 +9129,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -9293,46 +9293,46 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="G46" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H46" t="n">
         <v>10</v>
       </c>
       <c r="I46" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K46" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M46" t="n">
         <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O46" t="n">
         <v>1.21</v>
       </c>
       <c r="P46" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="R46" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S46" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T46" t="n">
         <v>1.89</v>
@@ -9344,16 +9344,16 @@
         <v>1.08</v>
       </c>
       <c r="W46" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="X46" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="Y46" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="Z46" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
@@ -9371,7 +9371,7 @@
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="AG46" t="n">
         <v>11</v>
@@ -9380,19 +9380,19 @@
         <v>34</v>
       </c>
       <c r="AI46" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ46" t="n">
         <v>11</v>
       </c>
       <c r="AK46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL46" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="AM46" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AN46" t="n">
         <v>5</v>
@@ -9401,31 +9401,31 @@
         <v>290</v>
       </c>
       <c r="AP46" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ46" t="n">
         <v>16</v>
       </c>
       <c r="AR46" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AT46" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW46" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU46" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>5</v>
-      </c>
       <c r="AX46" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AY46" t="n">
         <v>9.4</v>
@@ -9434,19 +9434,19 @@
         <v>15.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB46" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC46" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE46" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF46" t="n">
         <v>4</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -9487,58 +9487,58 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G47" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H47" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K47" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M47" t="n">
         <v>1.06</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
         <v>1.27</v>
       </c>
       <c r="P47" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="U47" t="n">
         <v>2.2</v>
       </c>
       <c r="V47" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X47" t="n">
         <v>17.5</v>
@@ -9646,11 +9646,11 @@
         <v>10.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -9681,58 +9681,58 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G48" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H48" t="n">
         <v>3.3</v>
       </c>
       <c r="I48" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K48" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N48" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="O48" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P48" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="R48" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S48" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T48" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U48" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="V48" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X48" t="n">
         <v>10.5</v>
@@ -9768,16 +9768,16 @@
         <v>22</v>
       </c>
       <c r="AI48" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AK48" t="n">
         <v>40</v>
       </c>
       <c r="AL48" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
         <v>1000</v>
@@ -9789,7 +9789,7 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ48" t="n">
         <v>9</v>
@@ -9798,7 +9798,7 @@
         <v>16.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT48" t="n">
         <v>7.2</v>
@@ -9807,10 +9807,10 @@
         <v>6.2</v>
       </c>
       <c r="AV48" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX48" t="n">
         <v>11</v>
@@ -9822,29 +9822,29 @@
         <v>17.5</v>
       </c>
       <c r="BA48" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD48" t="n">
         <v>5</v>
       </c>
-      <c r="BB48" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>38</v>
-      </c>
       <c r="BE48" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG48" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -9875,170 +9875,170 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="G49" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="H49" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="I49" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>3.35</v>
       </c>
       <c r="K49" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L49" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M49" t="n">
         <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="O49" t="n">
         <v>1.38</v>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="R49" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="S49" t="n">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="T49" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="U49" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="W49" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="X49" t="n">
-        <v>980</v>
+        <v>13.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>980</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z49" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="AA49" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AB49" t="n">
-        <v>980</v>
+        <v>12.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD49" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="AE49" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AF49" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AG49" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="AH49" t="n">
-        <v>980</v>
+        <v>19.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AJ49" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AK49" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AL49" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AM49" t="n">
         <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD49" t="n">
         <v>8</v>
       </c>
-      <c r="AQ49" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BE49" t="n">
-        <v>1.83</v>
+        <v>26</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.82</v>
+        <v>7.8</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.82</v>
+        <v>19.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -10069,22 +10069,22 @@
         </is>
       </c>
       <c r="F50" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" t="n">
         <v>7.2</v>
       </c>
-      <c r="G50" t="n">
-        <v>7.4</v>
-      </c>
       <c r="H50" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="J50" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L50" t="n">
         <v>1.32</v>
@@ -10093,58 +10093,58 @@
         <v>1.04</v>
       </c>
       <c r="N50" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O50" t="n">
         <v>1.21</v>
       </c>
       <c r="P50" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R50" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S50" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T50" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U50" t="n">
         <v>2.2</v>
       </c>
       <c r="V50" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="W50" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y50" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z50" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AA50" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AB50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC50" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD50" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AE50" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AF50" t="n">
         <v>60</v>
@@ -10153,19 +10153,19 @@
         <v>26</v>
       </c>
       <c r="AH50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI50" t="n">
         <v>27</v>
       </c>
       <c r="AJ50" t="n">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="AK50" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM50" t="n">
         <v>95</v>
@@ -10174,31 +10174,31 @@
         <v>85</v>
       </c>
       <c r="AO50" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AP50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR50" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS50" t="n">
         <v>13</v>
       </c>
       <c r="AT50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU50" t="n">
         <v>10.5</v>
       </c>
       <c r="AV50" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW50" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX50" t="n">
         <v>55</v>
@@ -10213,7 +10213,7 @@
         <v>26</v>
       </c>
       <c r="BB50" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="BC50" t="n">
         <v>75</v>
@@ -10222,17 +10222,17 @@
         <v>65</v>
       </c>
       <c r="BE50" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF50" t="n">
         <v>75</v>
       </c>
       <c r="BG50" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -10263,79 +10263,79 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H51" t="n">
         <v>4.4</v>
       </c>
       <c r="I51" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J51" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L51" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="M51" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="N51" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="O51" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="P51" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R51" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S51" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="T51" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="U51" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="V51" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W51" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X51" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z51" t="n">
         <v>32</v>
       </c>
       <c r="AA51" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AB51" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC51" t="n">
         <v>7.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE51" t="n">
         <v>310</v>
@@ -10344,34 +10344,34 @@
         <v>11.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH51" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AI51" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="AJ51" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AK51" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AL51" t="n">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="AM51" t="n">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="AN51" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AO51" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ51" t="n">
         <v>9.4</v>
@@ -10380,53 +10380,53 @@
         <v>26</v>
       </c>
       <c r="AS51" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU51" t="n">
         <v>6.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW51" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AX51" t="n">
         <v>10</v>
       </c>
       <c r="AY51" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ51" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC51" t="n">
         <v>26</v>
       </c>
-      <c r="BA51" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>24</v>
-      </c>
       <c r="BD51" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="BE51" t="n">
         <v>70</v>
       </c>
       <c r="BF51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BG51" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -10457,46 +10457,46 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G52" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H52" t="n">
         <v>3.4</v>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J52" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="K52" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="L52" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="M52" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N52" t="n">
         <v>2.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="P52" t="n">
         <v>1.37</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
         <v>1.12</v>
       </c>
       <c r="S52" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="T52" t="n">
         <v>2.5</v>
@@ -10508,7 +10508,7 @@
         <v>1.4</v>
       </c>
       <c r="W52" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X52" t="n">
         <v>6.4</v>
@@ -10532,7 +10532,7 @@
         <v>18</v>
       </c>
       <c r="AE52" t="n">
-        <v>450</v>
+        <v>190</v>
       </c>
       <c r="AF52" t="n">
         <v>15.5</v>
@@ -10547,7 +10547,7 @@
         <v>160</v>
       </c>
       <c r="AJ52" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK52" t="n">
         <v>55</v>
@@ -10556,10 +10556,10 @@
         <v>120</v>
       </c>
       <c r="AM52" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="AN52" t="n">
-        <v>220</v>
+        <v>75</v>
       </c>
       <c r="AO52" t="n">
         <v>140</v>
@@ -10571,7 +10571,7 @@
         <v>7.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AS52" t="n">
         <v>32</v>
@@ -10580,7 +10580,7 @@
         <v>6</v>
       </c>
       <c r="AU52" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV52" t="n">
         <v>16</v>
@@ -10601,7 +10601,7 @@
         <v>42</v>
       </c>
       <c r="BB52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC52" t="n">
         <v>38</v>
@@ -10610,7 +10610,7 @@
         <v>40</v>
       </c>
       <c r="BE52" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF52" t="n">
         <v>32</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
         <v>1000</v>
       </c>
       <c r="AC53" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD53" t="n">
         <v>1000</v>
@@ -10762,59 +10762,59 @@
         <v>4.2</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BG53" t="n">
         <v>1.55</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -10845,58 +10845,58 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G54" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H54" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L54" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M54" t="n">
         <v>1.12</v>
       </c>
       <c r="N54" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="O54" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P54" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R54" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S54" t="n">
         <v>5.2</v>
       </c>
       <c r="T54" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U54" t="n">
         <v>1.84</v>
       </c>
       <c r="V54" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W54" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X54" t="n">
         <v>9</v>
@@ -10929,7 +10929,7 @@
         <v>20</v>
       </c>
       <c r="AH54" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI54" t="n">
         <v>1000</v>
@@ -10953,7 +10953,7 @@
         <v>980</v>
       </c>
       <c r="AP54" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ54" t="n">
         <v>7.2</v>
@@ -10962,7 +10962,7 @@
         <v>13</v>
       </c>
       <c r="AS54" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT54" t="n">
         <v>9.199999999999999</v>
@@ -10971,28 +10971,28 @@
         <v>6.4</v>
       </c>
       <c r="AV54" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW54" t="n">
         <v>27</v>
       </c>
       <c r="AX54" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY54" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ54" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BB54" t="n">
         <v>42</v>
       </c>
       <c r="BC54" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD54" t="n">
         <v>34</v>
@@ -11001,14 +11001,14 @@
         <v>44</v>
       </c>
       <c r="BF54" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BG54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -11039,85 +11039,85 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="G55" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="H55" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K55" t="n">
         <v>4.1</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M55" t="n">
         <v>1.06</v>
       </c>
       <c r="N55" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O55" t="n">
         <v>1.28</v>
       </c>
       <c r="P55" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R55" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T55" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U55" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V55" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W55" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="X55" t="n">
         <v>17.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AA55" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB55" t="n">
         <v>10.5</v>
       </c>
       <c r="AC55" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD55" t="n">
         <v>22</v>
       </c>
       <c r="AE55" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF55" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG55" t="n">
         <v>11</v>
@@ -11135,34 +11135,34 @@
         <v>21</v>
       </c>
       <c r="AL55" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AM55" t="n">
         <v>110</v>
       </c>
       <c r="AN55" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO55" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP55" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ55" t="n">
         <v>14</v>
       </c>
       <c r="AR55" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS55" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT55" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU55" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV55" t="n">
         <v>15</v>
@@ -11180,29 +11180,29 @@
         <v>15.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB55" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BC55" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD55" t="n">
         <v>6.2</v>
       </c>
       <c r="BE55" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF55" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -11236,43 +11236,43 @@
         <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H56" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="I56" t="n">
         <v>1.6</v>
       </c>
       <c r="J56" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L56" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="M56" t="n">
         <v>1.03</v>
       </c>
       <c r="N56" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O56" t="n">
         <v>1.2</v>
       </c>
       <c r="P56" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R56" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S56" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T56" t="n">
         <v>1.72</v>
@@ -11284,7 +11284,7 @@
         <v>2.66</v>
       </c>
       <c r="W56" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X56" t="n">
         <v>26</v>
@@ -11326,13 +11326,13 @@
         <v>170</v>
       </c>
       <c r="AK56" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL56" t="n">
         <v>1000</v>
       </c>
       <c r="AM56" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN56" t="n">
         <v>65</v>
@@ -11377,13 +11377,13 @@
         <v>6.4</v>
       </c>
       <c r="BB56" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC56" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD56" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE56" t="n">
         <v>7</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -757,67 +757,67 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
         <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -832,7 +832,7 @@
         <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
         <v>22</v>
@@ -841,19 +841,19 @@
         <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AK2" t="n">
         <v>80</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -865,10 +865,10 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR2" t="n">
         <v>18</v>
@@ -886,41 +886,41 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H3" t="n">
         <v>2.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
         <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
         <v>44</v>
@@ -1020,22 +1020,22 @@
         <v>10</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AG3" t="n">
-        <v>980</v>
+        <v>28</v>
       </c>
       <c r="AH3" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1044,7 +1044,7 @@
         <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1059,10 +1059,10 @@
         <v>980</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
         <v>8.4</v>
@@ -1071,7 +1071,7 @@
         <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
@@ -1080,41 +1080,41 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AX3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G4" t="n">
         <v>1.52</v>
@@ -1154,37 +1154,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
         <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
         <v>2.02</v>
@@ -1247,7 +1247,7 @@
         <v>190</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO4" t="n">
         <v>240</v>
@@ -1259,10 +1259,10 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.8</v>
@@ -1271,10 +1271,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
@@ -1286,7 +1286,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
         <v>10.5</v>
@@ -1295,20 +1295,20 @@
         <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" t="n">
         <v>3.1</v>
       </c>
-      <c r="I5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
         <v>1.89</v>
@@ -1387,10 +1387,10 @@
         <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
         <v>21</v>
@@ -1405,10 +1405,10 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD5" t="n">
         <v>980</v>
@@ -1417,13 +1417,13 @@
         <v>980</v>
       </c>
       <c r="AF5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH5" t="n">
         <v>980</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>60</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1432,7 +1432,7 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
         <v>980</v>
@@ -1447,28 +1447,28 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR5" t="n">
         <v>9</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
         <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5" t="n">
         <v>7.6</v>
@@ -1477,22 +1477,22 @@
         <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.98</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.86</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.08</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
         <v>6.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>3.4</v>
@@ -1551,22 +1551,22 @@
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.27</v>
@@ -1581,16 +1581,16 @@
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
         <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
         <v>120</v>
@@ -1602,13 +1602,13 @@
         <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF6" t="n">
         <v>20</v>
@@ -1617,7 +1617,7 @@
         <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1650,7 +1650,7 @@
         <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,10 +1659,10 @@
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1671,10 +1671,10 @@
         <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
         <v>9</v>
@@ -1683,20 +1683,20 @@
         <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
         <v>2.96</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
         <v>3.6</v>
@@ -1742,49 +1742,49 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="P7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
         <v>1.64</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
         <v>1.52</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="Z7" t="n">
         <v>980</v>
@@ -1793,13 +1793,13 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC7" t="n">
         <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AE7" t="n">
         <v>980</v>
@@ -1808,7 +1808,7 @@
         <v>980</v>
       </c>
       <c r="AG7" t="n">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
         <v>980</v>
@@ -1820,7 +1820,7 @@
         <v>220</v>
       </c>
       <c r="AK7" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
         <v>460</v>
@@ -1835,28 +1835,28 @@
         <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>7.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
         <v>5.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
         <v>7.8</v>
@@ -1865,22 +1865,22 @@
         <v>7.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD7" t="n">
         <v>28</v>
       </c>
-      <c r="BB7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE7" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
         <v>8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
         <v>2.82</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K8" t="n">
         <v>3.25</v>
@@ -1945,19 +1945,19 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O8" t="n">
         <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1990,7 +1990,7 @@
         <v>19</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>27</v>
@@ -2002,7 +2002,7 @@
         <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="AH8" t="n">
         <v>65</v>
@@ -2014,7 +2014,7 @@
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>980</v>
+        <v>210</v>
       </c>
       <c r="AL8" t="n">
         <v>500</v>
@@ -2035,22 +2035,22 @@
         <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>5.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
         <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX8" t="n">
         <v>8.4</v>
@@ -2062,29 +2062,29 @@
         <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC8" t="n">
         <v>9</v>
       </c>
-      <c r="BC8" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD8" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2124,10 +2124,10 @@
         <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
@@ -2139,31 +2139,31 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.56</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.59</v>
-      </c>
       <c r="U9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
         <v>1.56</v>
@@ -2172,13 +2172,13 @@
         <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
         <v>26</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>290</v>
       </c>
       <c r="AB9" t="n">
         <v>19</v>
@@ -2193,10 +2193,10 @@
         <v>32</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
         <v>14.5</v>
@@ -2220,7 +2220,7 @@
         <v>20</v>
       </c>
       <c r="AO9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP9" t="n">
         <v>19</v>
@@ -2232,7 +2232,7 @@
         <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT9" t="n">
         <v>13.5</v>
@@ -2259,26 +2259,26 @@
         <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
         <v>14.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
         <v>3.8</v>
@@ -2333,7 +2333,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -2342,25 +2342,25 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
         <v>1.55</v>
       </c>
       <c r="U10" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X10" t="n">
         <v>27</v>
@@ -2381,16 +2381,16 @@
         <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
         <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
@@ -2402,7 +2402,7 @@
         <v>80</v>
       </c>
       <c r="AK10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>30</v>
@@ -2411,7 +2411,7 @@
         <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO10" t="n">
         <v>21</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L11" t="n">
         <v>1.52</v>
@@ -2545,34 +2545,34 @@
         <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
         <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -2581,13 +2581,13 @@
         <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>60</v>
@@ -2596,7 +2596,7 @@
         <v>50</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
         <v>60</v>
@@ -2611,31 +2611,31 @@
         <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
         <v>40</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
         <v>32</v>
       </c>
       <c r="AX11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
@@ -2647,26 +2647,26 @@
         <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC11" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE11" t="n">
         <v>130</v>
       </c>
       <c r="BF11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BG11" t="n">
         <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
         <v>1.34</v>
@@ -2736,13 +2736,13 @@
         <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.25</v>
@@ -2754,7 +2754,7 @@
         <v>30</v>
       </c>
       <c r="Y12" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="Z12" t="n">
         <v>980</v>
@@ -2775,7 +2775,7 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
         <v>36</v>
@@ -2802,7 +2802,7 @@
         <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP12" t="n">
         <v>7.6</v>
@@ -2811,22 +2811,22 @@
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT12" t="n">
         <v>5.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="n">
         <v>9.4</v>
@@ -2838,7 +2838,7 @@
         <v>10.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
         <v>17.5</v>
@@ -2847,20 +2847,20 @@
         <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
         <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G13" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.36</v>
@@ -2915,16 +2915,16 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
         <v>1.46</v>
@@ -2936,125 +2936,125 @@
         <v>1.71</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X13" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="Z13" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB13" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="AG13" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>980</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN13" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.42</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.42</v>
+        <v>30</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.44</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.43</v>
+        <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.44</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.37</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.44</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.43</v>
+        <v>17.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.41</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.42</v>
+        <v>16</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>4.1</v>
@@ -3103,40 +3103,40 @@
         <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
         <v>24</v>
@@ -3145,7 +3145,7 @@
         <v>25</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3157,7 +3157,7 @@
         <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
         <v>150</v>
@@ -3169,10 +3169,10 @@
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
         <v>20</v>
@@ -3181,28 +3181,28 @@
         <v>17.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM14" t="n">
         <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP14" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR14" t="n">
         <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3238,17 +3238,17 @@
         <v>15</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="R15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.18</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.08</v>
+        <v>5.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.09</v>
+        <v>5.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.09</v>
+        <v>6.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.09</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.09</v>
+        <v>4.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.09</v>
+        <v>4.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.06</v>
+        <v>4.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.09</v>
+        <v>5.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.09</v>
+        <v>5.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.07</v>
+        <v>5.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.09</v>
+        <v>5.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.07</v>
+        <v>3.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H16" t="n">
         <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -3500,7 +3500,7 @@
         <v>2.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P16" t="n">
         <v>2.96</v>
@@ -3509,22 +3509,22 @@
         <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S16" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="T16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U16" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V16" t="n">
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3575,13 +3575,13 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AQ16" t="n">
         <v>4.2</v>
@@ -3593,10 +3593,10 @@
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.5</v>
+        <v>1.96</v>
       </c>
       <c r="AV16" t="n">
         <v>4.2</v>
@@ -3605,38 +3605,38 @@
         <v>4.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="BA16" t="n">
         <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC16" t="n">
         <v>4.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
         <v>4.3</v>
@@ -3697,25 +3697,25 @@
         <v>1.13</v>
       </c>
       <c r="P17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
         <v>1.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S17" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="T17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
         <v>2.02</v>
@@ -3724,25 +3724,25 @@
         <v>34</v>
       </c>
       <c r="Y17" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA17" t="n">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3766,31 +3766,31 @@
         <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AN17" t="n">
         <v>6.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR17" t="n">
         <v>34</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
@@ -3805,32 +3805,32 @@
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
         <v>15.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
         <v>18</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>1.37</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.34</v>
@@ -3885,67 +3885,67 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
         <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V18" t="n">
         <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA18" t="n">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD18" t="n">
         <v>38</v>
       </c>
       <c r="AE18" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF18" t="n">
         <v>8.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
         <v>520</v>
@@ -3963,25 +3963,25 @@
         <v>430</v>
       </c>
       <c r="AN18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR18" t="n">
         <v>32</v>
       </c>
       <c r="AS18" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU18" t="n">
         <v>10</v>
@@ -3990,19 +3990,19 @@
         <v>27</v>
       </c>
       <c r="AW18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX18" t="n">
         <v>7.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BB18" t="n">
         <v>9.800000000000001</v>
@@ -4011,20 +4011,20 @@
         <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG18" t="n">
         <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G19" t="n">
         <v>3.45</v>
@@ -4067,19 +4067,19 @@
         <v>2.78</v>
       </c>
       <c r="J19" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
         <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>1.56</v>
@@ -4088,7 +4088,7 @@
         <v>1.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
         <v>1.19</v>
@@ -4106,10 +4106,10 @@
         <v>1.56</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="n">
         <v>8.199999999999999</v>
@@ -4127,7 +4127,7 @@
         <v>6.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>40</v>
@@ -4148,7 +4148,7 @@
         <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
         <v>460</v>
@@ -4157,10 +4157,10 @@
         <v>190</v>
       </c>
       <c r="AN19" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AP19" t="n">
         <v>7.2</v>
@@ -4172,7 +4172,7 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AT19" t="n">
         <v>8.6</v>
@@ -4187,7 +4187,7 @@
         <v>34</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY19" t="n">
         <v>13.5</v>
@@ -4202,7 +4202,7 @@
         <v>55</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="BD19" t="n">
         <v>65</v>
@@ -4214,11 +4214,11 @@
         <v>55</v>
       </c>
       <c r="BG19" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G20" t="n">
         <v>4.1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I20" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J20" t="n">
         <v>3.25</v>
@@ -4276,7 +4276,7 @@
         <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P20" t="n">
         <v>1.72</v>
@@ -4291,13 +4291,13 @@
         <v>4.4</v>
       </c>
       <c r="T20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.94</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W20" t="n">
         <v>1.32</v>
@@ -4309,7 +4309,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z20" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA20" t="n">
         <v>29</v>
@@ -4330,7 +4330,7 @@
         <v>27</v>
       </c>
       <c r="AG20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4339,19 +4339,19 @@
         <v>48</v>
       </c>
       <c r="AJ20" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AK20" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AL20" t="n">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO20" t="n">
         <v>23</v>
@@ -4360,13 +4360,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR20" t="n">
         <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
@@ -4378,13 +4378,13 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ20" t="n">
         <v>18</v>
@@ -4393,7 +4393,7 @@
         <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BC20" t="n">
         <v>48</v>
@@ -4402,7 +4402,7 @@
         <v>16</v>
       </c>
       <c r="BE20" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BF20" t="n">
         <v>42</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>3.75</v>
       </c>
       <c r="G21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H21" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I21" t="n">
         <v>2.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
         <v>3.4</v>
@@ -4470,7 +4470,7 @@
         <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
         <v>1.81</v>
@@ -4479,7 +4479,7 @@
         <v>2.18</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -4488,40 +4488,40 @@
         <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X21" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="AB21" t="n">
         <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
         <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AF21" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
         <v>15.5</v>
@@ -4530,83 +4530,83 @@
         <v>18.5</v>
       </c>
       <c r="AI21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>190</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>500</v>
-      </c>
       <c r="AK21" t="n">
-        <v>240</v>
+        <v>48</v>
       </c>
       <c r="AL21" t="n">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR21" t="n">
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
         <v>22</v>
       </c>
       <c r="AX21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AY21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>32</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BC21" t="n">
         <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BF21" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>3.15</v>
@@ -4661,34 +4661,34 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
         <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V22" t="n">
         <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>23</v>
@@ -4718,13 +4718,13 @@
         <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH22" t="n">
         <v>980</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
@@ -4751,56 +4751,56 @@
         <v>7.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT22" t="n">
         <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX22" t="n">
         <v>6.2</v>
       </c>
       <c r="AY22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BA22" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="I23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="J23" t="n">
         <v>4.3</v>
@@ -4852,40 +4852,40 @@
         <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
         <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
         <v>2.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T23" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U23" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
         <v>11</v>
@@ -4894,16 +4894,16 @@
         <v>11.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AC23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE23" t="n">
         <v>16</v>
@@ -4918,37 +4918,37 @@
         <v>18</v>
       </c>
       <c r="AI23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK23" t="n">
         <v>60</v>
       </c>
       <c r="AL23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
-        <v>330</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
         <v>55</v>
       </c>
       <c r="AO23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
         <v>10.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT23" t="n">
         <v>20</v>
@@ -4963,10 +4963,10 @@
         <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AY23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>16.5</v>
@@ -4975,10 +4975,10 @@
         <v>26</v>
       </c>
       <c r="BB23" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="BC23" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BD23" t="n">
         <v>28</v>
@@ -4987,14 +4987,14 @@
         <v>44</v>
       </c>
       <c r="BF23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BG23" t="n">
         <v>7.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5025,61 +5025,61 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="H24" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="I24" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="J24" t="n">
         <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
         <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R24" t="n">
         <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T24" t="n">
-        <v>1.06</v>
+        <v>1.63</v>
       </c>
       <c r="U24" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="V24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="X24" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
         <v>980</v>
@@ -5088,13 +5088,13 @@
         <v>980</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB24" t="n">
         <v>980</v>
       </c>
       <c r="AC24" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD24" t="n">
         <v>980</v>
@@ -5109,13 +5109,13 @@
         <v>980</v>
       </c>
       <c r="AH24" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK24" t="n">
         <v>1000</v>
@@ -5127,68 +5127,68 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>7</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.98</v>
+        <v>14.5</v>
       </c>
       <c r="AT24" t="n">
         <v>7.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
         <v>7.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF24" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>3.9</v>
       </c>
       <c r="BG24" t="n">
         <v>3.45</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H25" t="n">
         <v>3.35</v>
@@ -5231,10 +5231,10 @@
         <v>3.85</v>
       </c>
       <c r="J25" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L25" t="n">
         <v>1.61</v>
@@ -5243,10 +5243,10 @@
         <v>1.13</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O25" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P25" t="n">
         <v>1.49</v>
@@ -5258,7 +5258,7 @@
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T25" t="n">
         <v>2.12</v>
@@ -5270,7 +5270,7 @@
         <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X25" t="n">
         <v>9.4</v>
@@ -5312,7 +5312,7 @@
         <v>220</v>
       </c>
       <c r="AK25" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
@@ -5321,13 +5321,13 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ25" t="n">
         <v>8.199999999999999</v>
@@ -5336,7 +5336,7 @@
         <v>19.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT25" t="n">
         <v>6.4</v>
@@ -5348,7 +5348,7 @@
         <v>13.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX25" t="n">
         <v>12.5</v>
@@ -5360,29 +5360,29 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BD25" t="n">
         <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G26" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I26" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J26" t="n">
         <v>3</v>
@@ -5431,31 +5431,31 @@
         <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="O26" t="n">
         <v>1.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
         <v>2.38</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
         <v>4.7</v>
       </c>
       <c r="T26" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U26" t="n">
         <v>1.87</v>
@@ -5491,10 +5491,10 @@
         <v>110</v>
       </c>
       <c r="AF26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
@@ -5503,13 +5503,13 @@
         <v>290</v>
       </c>
       <c r="AJ26" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL26" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5521,7 +5521,7 @@
         <v>70</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
         <v>7.6</v>
@@ -5530,7 +5530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="AT26" t="n">
         <v>8.800000000000001</v>
@@ -5554,29 +5554,29 @@
         <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB26" t="n">
         <v>23</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG26" t="n">
         <v>29</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>2.06</v>
       </c>
       <c r="G27" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H27" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I27" t="n">
         <v>4.4</v>
@@ -5625,40 +5625,40 @@
         <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U27" t="n">
         <v>1.9</v>
       </c>
       <c r="V27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X27" t="n">
         <v>12</v>
@@ -5694,7 +5694,7 @@
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
@@ -5724,7 +5724,7 @@
         <v>7.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5757,7 +5757,7 @@
         <v>22</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE27" t="n">
         <v>9.199999999999999</v>
@@ -5766,11 +5766,11 @@
         <v>18</v>
       </c>
       <c r="BG27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5801,136 +5801,136 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
         <v>1.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="V28" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="X28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z28" t="n">
         <v>120</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH28" t="n">
         <v>21</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
         <v>23</v>
       </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>21</v>
-      </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU28" t="n">
         <v>6.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX28" t="n">
         <v>9.4</v>
@@ -5939,32 +5939,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
         <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF28" t="n">
         <v>14</v>
       </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6019,16 +6019,16 @@
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P29" t="n">
         <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R29" t="n">
         <v>1.59</v>
@@ -6040,7 +6040,7 @@
         <v>1.57</v>
       </c>
       <c r="U29" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V29" t="n">
         <v>1.54</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6189,13 +6189,13 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G30" t="n">
         <v>1.62</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.63</v>
-      </c>
       <c r="H30" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I30" t="n">
         <v>7</v>
@@ -6207,40 +6207,40 @@
         <v>4.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R30" t="n">
         <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T30" t="n">
         <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V30" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X30" t="n">
         <v>14</v>
@@ -6252,19 +6252,19 @@
         <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC30" t="n">
         <v>9</v>
       </c>
       <c r="AD30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE30" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF30" t="n">
         <v>8.4</v>
@@ -6276,13 +6276,13 @@
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
         <v>40</v>
@@ -6291,19 +6291,19 @@
         <v>150</v>
       </c>
       <c r="AN30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO30" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP30" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS30" t="n">
         <v>190</v>
@@ -6333,26 +6333,26 @@
         <v>85</v>
       </c>
       <c r="BB30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC30" t="n">
         <v>16.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE30" t="n">
         <v>120</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.95</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.96</v>
       </c>
       <c r="H31" t="n">
         <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
         <v>1.47</v>
@@ -6413,22 +6413,22 @@
         <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
         <v>1.98</v>
       </c>
       <c r="U31" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
         <v>1.26</v>
@@ -6440,7 +6440,7 @@
         <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z31" t="n">
         <v>32</v>
@@ -6476,13 +6476,13 @@
         <v>21</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="n">
         <v>42</v>
       </c>
       <c r="AM31" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
         <v>16.5</v>
@@ -6494,7 +6494,7 @@
         <v>11</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR31" t="n">
         <v>30</v>
@@ -6503,7 +6503,7 @@
         <v>95</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU31" t="n">
         <v>7.4</v>
@@ -6530,23 +6530,23 @@
         <v>20</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD31" t="n">
         <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6577,19 +6577,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="G32" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H32" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I32" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K32" t="n">
         <v>3.9</v>
@@ -6613,10 +6613,10 @@
         <v>1.82</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="T32" t="n">
         <v>1.64</v>
@@ -6625,49 +6625,49 @@
         <v>2.28</v>
       </c>
       <c r="V32" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="W32" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X32" t="n">
         <v>17.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AA32" t="n">
-        <v>170</v>
+        <v>980</v>
       </c>
       <c r="AB32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC32" t="n">
         <v>8.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>170</v>
+        <v>980</v>
       </c>
       <c r="AF32" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="AG32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH32" t="n">
         <v>25</v>
       </c>
       <c r="AI32" t="n">
-        <v>230</v>
+        <v>980</v>
       </c>
       <c r="AJ32" t="n">
-        <v>980</v>
+        <v>220</v>
       </c>
       <c r="AK32" t="n">
         <v>220</v>
@@ -6679,10 +6679,10 @@
         <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AO32" t="n">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="AP32" t="n">
         <v>15</v>
@@ -6694,10 +6694,10 @@
         <v>14.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU32" t="n">
         <v>7.4</v>
@@ -6706,41 +6706,41 @@
         <v>10</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX32" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ32" t="n">
         <v>13.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD32" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE32" t="n">
         <v>19</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG32" t="n">
         <v>14.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6777,16 +6777,16 @@
         <v>4.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I33" t="n">
         <v>2.28</v>
       </c>
       <c r="J33" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L33" t="n">
         <v>1.54</v>
@@ -6795,7 +6795,7 @@
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
         <v>1.48</v>
@@ -6804,13 +6804,13 @@
         <v>1.59</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T33" t="n">
         <v>2.04</v>
@@ -6825,10 +6825,10 @@
         <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z33" t="n">
         <v>13</v>
@@ -6840,7 +6840,7 @@
         <v>12</v>
       </c>
       <c r="AC33" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD33" t="n">
         <v>11.5</v>
@@ -6852,7 +6852,7 @@
         <v>90</v>
       </c>
       <c r="AG33" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH33" t="n">
         <v>44</v>
@@ -6876,10 +6876,10 @@
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.2</v>
@@ -6888,7 +6888,7 @@
         <v>10.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
@@ -6900,7 +6900,7 @@
         <v>9.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX33" t="n">
         <v>11.5</v>
@@ -6912,29 +6912,29 @@
         <v>19.5</v>
       </c>
       <c r="BA33" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC33" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BD33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE33" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC33" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD33" t="n">
+      <c r="BF33" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>9.6</v>
       </c>
       <c r="BG33" t="n">
         <v>22</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G34" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I34" t="n">
         <v>5.3</v>
       </c>
       <c r="J34" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L34" t="n">
         <v>1.41</v>
@@ -6989,34 +6989,34 @@
         <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O34" t="n">
         <v>1.31</v>
       </c>
       <c r="P34" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q34" t="n">
         <v>1.96</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
         <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="U34" t="n">
-        <v>1.05</v>
+        <v>1.98</v>
       </c>
       <c r="V34" t="n">
         <v>1.25</v>
       </c>
       <c r="W34" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7031,10 +7031,10 @@
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC34" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AD34" t="n">
         <v>1000</v>
@@ -7043,10 +7043,10 @@
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH34" t="n">
         <v>1000</v>
@@ -7055,10 +7055,10 @@
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL34" t="n">
         <v>1000</v>
@@ -7067,68 +7067,68 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.36</v>
+        <v>7.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.36</v>
+        <v>6.2</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.36</v>
+        <v>2.58</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.37</v>
+        <v>2.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.25</v>
+        <v>4.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.36</v>
+        <v>3.65</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.37</v>
+        <v>2.66</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.33</v>
+        <v>5.3</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.33</v>
+        <v>5.2</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.35</v>
+        <v>3.4</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.37</v>
+        <v>2.74</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.36</v>
+        <v>3.65</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.35</v>
+        <v>3.4</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.37</v>
+        <v>2.58</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.37</v>
+        <v>2.7</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.34</v>
+        <v>3.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7159,25 +7159,25 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G35" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="H35" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="I35" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
@@ -7189,28 +7189,28 @@
         <v>1.26</v>
       </c>
       <c r="P35" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R35" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T35" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U35" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V35" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="W35" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X35" t="n">
         <v>16.5</v>
@@ -7219,110 +7219,110 @@
         <v>10.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB35" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD35" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AE35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH35" t="n">
         <v>18</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>19</v>
       </c>
       <c r="AI35" t="n">
         <v>32</v>
       </c>
       <c r="AJ35" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL35" t="n">
         <v>60</v>
       </c>
-      <c r="AL35" t="n">
-        <v>65</v>
-      </c>
       <c r="AM35" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN35" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR35" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AS35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY35" t="n">
         <v>15</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>17.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>15.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB35" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BD35" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE35" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G36" t="n">
         <v>2.64</v>
@@ -7362,46 +7362,46 @@
         <v>3.05</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J36" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K36" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N36" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O36" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P36" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T36" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U36" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W36" t="n">
         <v>1.6</v>
@@ -7410,25 +7410,25 @@
         <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z36" t="n">
         <v>22</v>
       </c>
       <c r="AA36" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB36" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC36" t="n">
         <v>7.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF36" t="n">
         <v>17.5</v>
@@ -7437,52 +7437,52 @@
         <v>12.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ36" t="n">
         <v>40</v>
       </c>
       <c r="AK36" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL36" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AM36" t="n">
-        <v>580</v>
+        <v>330</v>
       </c>
       <c r="AN36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO36" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP36" t="n">
         <v>10</v>
       </c>
       <c r="AQ36" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR36" t="n">
         <v>17.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AT36" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV36" t="n">
         <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX36" t="n">
         <v>14</v>
@@ -7491,32 +7491,32 @@
         <v>10</v>
       </c>
       <c r="AZ36" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA36" t="n">
         <v>42</v>
       </c>
       <c r="BB36" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BC36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD36" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BE36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BF36" t="n">
         <v>21</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G37" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H37" t="n">
         <v>6.6</v>
@@ -7559,16 +7559,16 @@
         <v>8</v>
       </c>
       <c r="J37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K37" t="n">
         <v>4.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N37" t="n">
         <v>4.1</v>
@@ -7577,37 +7577,37 @@
         <v>1.27</v>
       </c>
       <c r="P37" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T37" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V37" t="n">
         <v>1.14</v>
       </c>
       <c r="W37" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X37" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z37" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
@@ -7634,7 +7634,7 @@
         <v>24</v>
       </c>
       <c r="AI37" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
         <v>14.5</v>
@@ -7649,7 +7649,7 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
@@ -7658,43 +7658,43 @@
         <v>15</v>
       </c>
       <c r="AQ37" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR37" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW37" t="n">
         <v>10</v>
       </c>
-      <c r="AT37" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AX37" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY37" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA37" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB37" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD37" t="n">
         <v>18</v>
@@ -7703,14 +7703,14 @@
         <v>28</v>
       </c>
       <c r="BF37" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G38" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H38" t="n">
         <v>4</v>
@@ -7756,16 +7756,16 @@
         <v>3.45</v>
       </c>
       <c r="K38" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O38" t="n">
         <v>1.32</v>
@@ -7774,25 +7774,25 @@
         <v>1.98</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R38" t="n">
         <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="U38" t="n">
         <v>2.04</v>
       </c>
       <c r="V38" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W38" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X38" t="n">
         <v>980</v>
@@ -7855,7 +7855,7 @@
         <v>8.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS38" t="n">
         <v>3.95</v>
@@ -7864,13 +7864,13 @@
         <v>5.1</v>
       </c>
       <c r="AU38" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV38" t="n">
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="AX38" t="n">
         <v>5.8</v>
@@ -7882,7 +7882,7 @@
         <v>11.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BB38" t="n">
         <v>10.5</v>
@@ -7891,20 +7891,20 @@
         <v>10.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF38" t="n">
         <v>3.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7938,55 +7938,55 @@
         <v>2.44</v>
       </c>
       <c r="G39" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H39" t="n">
         <v>3.1</v>
       </c>
       <c r="I39" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K39" t="n">
         <v>3.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M39" t="n">
         <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O39" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P39" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R39" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="T39" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="U39" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="V39" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W39" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X39" t="n">
         <v>21</v>
@@ -8013,13 +8013,13 @@
         <v>980</v>
       </c>
       <c r="AF39" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AG39" t="n">
         <v>19.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AI39" t="n">
         <v>500</v>
@@ -8052,10 +8052,10 @@
         <v>10.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT39" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AU39" t="n">
         <v>6.2</v>
@@ -8064,7 +8064,7 @@
         <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX39" t="n">
         <v>7.6</v>
@@ -8076,29 +8076,29 @@
         <v>12</v>
       </c>
       <c r="BA39" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB39" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BC39" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BD39" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF39" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8129,19 +8129,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="G40" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="H40" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J40" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K40" t="n">
         <v>3.45</v>
@@ -8156,34 +8156,34 @@
         <v>3.25</v>
       </c>
       <c r="O40" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P40" t="n">
         <v>1.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T40" t="n">
-        <v>1.05</v>
+        <v>1.92</v>
       </c>
       <c r="U40" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W40" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="X40" t="n">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="Y40" t="n">
         <v>1000</v>
@@ -8195,10 +8195,10 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AC40" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD40" t="n">
         <v>1000</v>
@@ -8207,13 +8207,13 @@
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
@@ -8237,62 +8237,62 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.32</v>
+        <v>10.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.33</v>
+        <v>9</v>
       </c>
       <c r="AT40" t="n">
         <v>5.1</v>
       </c>
       <c r="AU40" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV40" t="n">
         <v>8.4</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.33</v>
+        <v>9.6</v>
       </c>
       <c r="AX40" t="n">
         <v>7.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
         <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.33</v>
+        <v>6.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.33</v>
+        <v>9</v>
       </c>
       <c r="BE40" t="n">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8323,127 +8323,127 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="G41" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="H41" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I41" t="n">
         <v>2.26</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>3.85</v>
       </c>
       <c r="K41" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N41" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O41" t="n">
         <v>1.18</v>
       </c>
       <c r="P41" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R41" t="n">
         <v>1.64</v>
       </c>
       <c r="S41" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="T41" t="n">
         <v>1.54</v>
       </c>
       <c r="U41" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V41" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="W41" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X41" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Y41" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z41" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA41" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AB41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC41" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD41" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AF41" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG41" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AJ41" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AK41" t="n">
         <v>34</v>
       </c>
       <c r="AL41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM41" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP41" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AQ41" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR41" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.7</v>
+        <v>24</v>
       </c>
       <c r="AT41" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AU41" t="n">
         <v>8.6</v>
@@ -8452,41 +8452,41 @@
         <v>10</v>
       </c>
       <c r="AW41" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="AY41" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ41" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB41" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="BC41" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.1</v>
+        <v>40</v>
       </c>
       <c r="BF41" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G42" t="n">
         <v>2.08</v>
@@ -8526,55 +8526,55 @@
         <v>4.1</v>
       </c>
       <c r="I42" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
         <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L42" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M42" t="n">
         <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O42" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P42" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R42" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="T42" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U42" t="n">
         <v>1.96</v>
       </c>
       <c r="V42" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
         <v>1.92</v>
       </c>
       <c r="X42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y42" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z42" t="n">
         <v>80</v>
@@ -8583,10 +8583,10 @@
         <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD42" t="n">
         <v>18.5</v>
@@ -8601,13 +8601,13 @@
         <v>11</v>
       </c>
       <c r="AH42" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="n">
-        <v>170</v>
+        <v>330</v>
       </c>
       <c r="AJ42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK42" t="n">
         <v>24</v>
@@ -8619,16 +8619,16 @@
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR42" t="n">
         <v>13</v>
@@ -8658,7 +8658,7 @@
         <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB42" t="n">
         <v>20</v>
@@ -8667,7 +8667,7 @@
         <v>18</v>
       </c>
       <c r="BD42" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE42" t="n">
         <v>9</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G43" t="n">
         <v>2.22</v>
@@ -8720,13 +8720,13 @@
         <v>3.45</v>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J43" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K43" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8741,10 +8741,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8905,79 +8905,79 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G44" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H44" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I44" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J44" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K44" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L44" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M44" t="n">
         <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
         <v>1.34</v>
       </c>
       <c r="P44" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q44" t="n">
         <v>2.04</v>
       </c>
       <c r="R44" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S44" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T44" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="U44" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="V44" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W44" t="n">
         <v>1.55</v>
       </c>
       <c r="X44" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="Y44" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB44" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD44" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
@@ -9013,62 +9013,62 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AQ44" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS44" t="n">
         <v>7.6</v>
       </c>
-      <c r="AR44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AT44" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AU44" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="AW44" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AX44" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AY44" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB44" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC44" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF44" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BG44" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -9105,16 +9105,16 @@
         <v>1.35</v>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I45" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="J45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K45" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -9129,10 +9129,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q45" t="n">
         <v>2</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.93</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -9293,85 +9293,85 @@
         </is>
       </c>
       <c r="F46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G46" t="n">
         <v>1.31</v>
       </c>
-      <c r="G46" t="n">
-        <v>1.33</v>
-      </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="I46" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="J46" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K46" t="n">
         <v>6.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M46" t="n">
         <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P46" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="R46" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S46" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T46" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="U46" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="V46" t="n">
         <v>1.08</v>
       </c>
       <c r="W46" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X46" t="n">
         <v>24</v>
       </c>
       <c r="Y46" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Z46" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>710</v>
       </c>
       <c r="AB46" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="AC46" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD46" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AF46" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AG46" t="n">
         <v>11</v>
@@ -9380,25 +9380,25 @@
         <v>34</v>
       </c>
       <c r="AI46" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AJ46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK46" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL46" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AM46" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AO46" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AP46" t="n">
         <v>10.5</v>
@@ -9407,56 +9407,56 @@
         <v>16</v>
       </c>
       <c r="AR46" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AS46" t="n">
-        <v>13.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT46" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AV46" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW46" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX46" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY46" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ46" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA46" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB46" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC46" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD46" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="BF46" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BG46" t="n">
         <v>15</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -9487,19 +9487,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G47" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H47" t="n">
         <v>3.6</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J47" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K47" t="n">
         <v>4</v>
@@ -9511,40 +9511,40 @@
         <v>1.06</v>
       </c>
       <c r="N47" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O47" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P47" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
         <v>1.83</v>
       </c>
       <c r="R47" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
         <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="U47" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V47" t="n">
         <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X47" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y47" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z47" t="n">
         <v>80</v>
@@ -9553,19 +9553,19 @@
         <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC47" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD47" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE47" t="n">
         <v>170</v>
       </c>
       <c r="AF47" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG47" t="n">
         <v>11.5</v>
@@ -9574,7 +9574,7 @@
         <v>18</v>
       </c>
       <c r="AI47" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AJ47" t="n">
         <v>27</v>
@@ -9595,7 +9595,7 @@
         <v>75</v>
       </c>
       <c r="AP47" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ47" t="n">
         <v>13</v>
@@ -9604,7 +9604,7 @@
         <v>21</v>
       </c>
       <c r="AS47" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="AT47" t="n">
         <v>9.199999999999999</v>
@@ -9616,7 +9616,7 @@
         <v>12</v>
       </c>
       <c r="AW47" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX47" t="n">
         <v>10.5</v>
@@ -9628,7 +9628,7 @@
         <v>14</v>
       </c>
       <c r="BA47" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BB47" t="n">
         <v>19.5</v>
@@ -9637,20 +9637,20 @@
         <v>18</v>
       </c>
       <c r="BD47" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BE47" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BF47" t="n">
         <v>10.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -9702,22 +9702,22 @@
         <v>1.52</v>
       </c>
       <c r="M48" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="O48" t="n">
         <v>1.45</v>
       </c>
       <c r="P48" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R48" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S48" t="n">
         <v>4.6</v>
@@ -9729,10 +9729,10 @@
         <v>1.72</v>
       </c>
       <c r="V48" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W48" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X48" t="n">
         <v>10.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -9878,16 +9878,16 @@
         <v>3.2</v>
       </c>
       <c r="G49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J49" t="n">
         <v>3.4</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3.35</v>
       </c>
       <c r="K49" t="n">
         <v>3.6</v>
@@ -9896,7 +9896,7 @@
         <v>1.45</v>
       </c>
       <c r="M49" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N49" t="n">
         <v>3.35</v>
@@ -9905,7 +9905,7 @@
         <v>1.38</v>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
         <v>2.1</v>
@@ -9920,25 +9920,25 @@
         <v>1.81</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
+        <v>1.05</v>
       </c>
       <c r="V49" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W49" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X49" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="Y49" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z49" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB49" t="n">
         <v>12.5</v>
@@ -9950,10 +9950,10 @@
         <v>12</v>
       </c>
       <c r="AE49" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF49" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG49" t="n">
         <v>15</v>
@@ -9962,37 +9962,37 @@
         <v>19.5</v>
       </c>
       <c r="AI49" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK49" t="n">
         <v>46</v>
       </c>
-      <c r="AJ49" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>44</v>
-      </c>
       <c r="AL49" t="n">
-        <v>120</v>
+        <v>980</v>
       </c>
       <c r="AM49" t="n">
         <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP49" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ49" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR49" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT49" t="n">
         <v>10</v>
@@ -10001,44 +10001,44 @@
         <v>6.8</v>
       </c>
       <c r="AV49" t="n">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AW49" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX49" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY49" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AZ49" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BC49" t="n">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BE49" t="n">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="BF49" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG49" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -10069,22 +10069,22 @@
         </is>
       </c>
       <c r="F50" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G50" t="n">
         <v>7</v>
       </c>
-      <c r="G50" t="n">
-        <v>7.2</v>
-      </c>
       <c r="H50" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="I50" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="J50" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K50" t="n">
         <v>5</v>
-      </c>
-      <c r="K50" t="n">
-        <v>5.1</v>
       </c>
       <c r="L50" t="n">
         <v>1.32</v>
@@ -10093,31 +10093,31 @@
         <v>1.04</v>
       </c>
       <c r="N50" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O50" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P50" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R50" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S50" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T50" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U50" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V50" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="W50" t="n">
         <v>1.16</v>
@@ -10129,19 +10129,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AA50" t="n">
         <v>14</v>
       </c>
       <c r="AB50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC50" t="n">
         <v>11</v>
       </c>
       <c r="AD50" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE50" t="n">
         <v>14</v>
@@ -10150,16 +10150,16 @@
         <v>60</v>
       </c>
       <c r="AG50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH50" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ50" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AK50" t="n">
         <v>85</v>
@@ -10171,25 +10171,25 @@
         <v>95</v>
       </c>
       <c r="AN50" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO50" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP50" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ50" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR50" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS50" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU50" t="n">
         <v>10.5</v>
@@ -10210,10 +10210,10 @@
         <v>20</v>
       </c>
       <c r="BA50" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB50" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="BC50" t="n">
         <v>75</v>
@@ -10225,14 +10225,14 @@
         <v>85</v>
       </c>
       <c r="BF50" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BG50" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -10263,58 +10263,58 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G51" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H51" t="n">
         <v>4.4</v>
       </c>
       <c r="I51" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K51" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L51" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M51" t="n">
         <v>1.16</v>
       </c>
       <c r="N51" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O51" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P51" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T51" t="n">
         <v>2.44</v>
       </c>
       <c r="U51" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V51" t="n">
         <v>1.27</v>
       </c>
       <c r="W51" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X51" t="n">
         <v>7.4</v>
@@ -10356,7 +10356,7 @@
         <v>32</v>
       </c>
       <c r="AK51" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL51" t="n">
         <v>200</v>
@@ -10365,13 +10365,13 @@
         <v>500</v>
       </c>
       <c r="AN51" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO51" t="n">
         <v>500</v>
       </c>
       <c r="AP51" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ51" t="n">
         <v>9.4</v>
@@ -10383,19 +10383,19 @@
         <v>38</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU51" t="n">
         <v>6.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AX51" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY51" t="n">
         <v>11</v>
@@ -10410,23 +10410,23 @@
         <v>23</v>
       </c>
       <c r="BC51" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BD51" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BE51" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG51" t="n">
         <v>44</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -10457,46 +10457,46 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G52" t="n">
         <v>2.8</v>
       </c>
       <c r="H52" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I52" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K52" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="L52" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="M52" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="N52" t="n">
         <v>2.2</v>
       </c>
       <c r="O52" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="P52" t="n">
         <v>1.37</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R52" t="n">
         <v>1.12</v>
       </c>
       <c r="S52" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="T52" t="n">
         <v>2.5</v>
@@ -10532,10 +10532,10 @@
         <v>18</v>
       </c>
       <c r="AE52" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF52" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG52" t="n">
         <v>15</v>
@@ -10556,13 +10556,13 @@
         <v>120</v>
       </c>
       <c r="AM52" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AN52" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO52" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP52" t="n">
         <v>5.7</v>
@@ -10571,7 +10571,7 @@
         <v>7.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS52" t="n">
         <v>32</v>
@@ -10598,13 +10598,13 @@
         <v>27</v>
       </c>
       <c r="BA52" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="BB52" t="n">
         <v>26</v>
       </c>
       <c r="BC52" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BD52" t="n">
         <v>40</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
         <v>1.17</v>
       </c>
       <c r="W53" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -10851,16 +10851,16 @@
         <v>3.6</v>
       </c>
       <c r="H54" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I54" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L54" t="n">
         <v>1.56</v>
@@ -10878,10 +10878,10 @@
         <v>1.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R54" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S54" t="n">
         <v>5.2</v>
@@ -10893,7 +10893,7 @@
         <v>1.84</v>
       </c>
       <c r="V54" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W54" t="n">
         <v>1.38</v>
@@ -10923,10 +10923,10 @@
         <v>980</v>
       </c>
       <c r="AF54" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AG54" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AH54" t="n">
         <v>30</v>
@@ -10938,7 +10938,7 @@
         <v>75</v>
       </c>
       <c r="AK54" t="n">
-        <v>980</v>
+        <v>210</v>
       </c>
       <c r="AL54" t="n">
         <v>80</v>
@@ -10962,7 +10962,7 @@
         <v>13</v>
       </c>
       <c r="AS54" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AT54" t="n">
         <v>9.199999999999999</v>
@@ -10974,28 +10974,28 @@
         <v>11.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX54" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY54" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ54" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA54" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB54" t="n">
         <v>44</v>
       </c>
-      <c r="BB54" t="n">
-        <v>42</v>
-      </c>
       <c r="BC54" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BD54" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BE54" t="n">
         <v>44</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -11039,19 +11039,19 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G55" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="H55" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J55" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K55" t="n">
         <v>4.1</v>
@@ -11063,34 +11063,34 @@
         <v>1.06</v>
       </c>
       <c r="N55" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O55" t="n">
         <v>1.28</v>
       </c>
       <c r="P55" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S55" t="n">
         <v>3.15</v>
       </c>
       <c r="T55" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U55" t="n">
         <v>2.16</v>
       </c>
       <c r="V55" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W55" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X55" t="n">
         <v>17.5</v>
@@ -11099,7 +11099,7 @@
         <v>19.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AA55" t="n">
         <v>110</v>
@@ -11108,13 +11108,13 @@
         <v>10.5</v>
       </c>
       <c r="AC55" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD55" t="n">
         <v>22</v>
       </c>
       <c r="AE55" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF55" t="n">
         <v>13</v>
@@ -11141,68 +11141,68 @@
         <v>110</v>
       </c>
       <c r="AN55" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO55" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP55" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ55" t="n">
         <v>14</v>
       </c>
       <c r="AR55" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT55" t="n">
         <v>8.6</v>
       </c>
       <c r="AU55" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV55" t="n">
         <v>15</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX55" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY55" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ55" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC55" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA55" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD55" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF55" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG55" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -11233,22 +11233,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G56" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H56" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="I56" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="J56" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K56" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
         <v>1.3</v>
@@ -11263,28 +11263,28 @@
         <v>1.2</v>
       </c>
       <c r="P56" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R56" t="n">
         <v>1.61</v>
       </c>
       <c r="S56" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T56" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U56" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V56" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="W56" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X56" t="n">
         <v>26</v>
@@ -11293,22 +11293,22 @@
         <v>13</v>
       </c>
       <c r="Z56" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB56" t="n">
         <v>29</v>
       </c>
       <c r="AC56" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD56" t="n">
         <v>10.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF56" t="n">
         <v>980</v>
@@ -11326,7 +11326,7 @@
         <v>170</v>
       </c>
       <c r="AK56" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AL56" t="n">
         <v>1000</v>
@@ -11335,37 +11335,37 @@
         <v>85</v>
       </c>
       <c r="AN56" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO56" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AP56" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ56" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU56" t="n">
         <v>10</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AV56" t="n">
         <v>9</v>
       </c>
       <c r="AW56" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX56" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="AY56" t="n">
         <v>20</v>
@@ -11374,29 +11374,29 @@
         <v>16.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB56" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE56" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC56" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>7</v>
-      </c>
       <c r="BF56" t="n">
-        <v>48</v>
+        <v>7.2</v>
       </c>
       <c r="BG56" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-03.xlsx
@@ -757,43 +757,43 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q2" t="n">
         <v>2.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>4.2</v>
@@ -802,16 +802,16 @@
         <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
         <v>11.5</v>
@@ -820,37 +820,37 @@
         <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
@@ -859,22 +859,22 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP2" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR2" t="n">
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -886,41 +886,41 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="BB2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BD2" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -951,79 +951,79 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.05</v>
       </c>
-      <c r="G3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
         <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AA3" t="n">
         <v>980</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
@@ -1035,16 +1035,16 @@
         <v>28</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1059,19 +1059,19 @@
         <v>980</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR3" t="n">
         <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
@@ -1080,41 +1080,41 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AX3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BE3" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1145,82 +1145,82 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G4" t="n">
         <v>1.52</v>
       </c>
       <c r="H4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
         <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
         <v>2.92</v>
       </c>
       <c r="X4" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="AB4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AE4" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AF4" t="n">
         <v>8.800000000000001</v>
@@ -1229,86 +1229,86 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI4" t="n">
         <v>520</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>980</v>
+        <v>170</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
         <v>8.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AP4" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS4" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
         <v>6.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV4" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="AX4" t="n">
         <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF4" t="n">
         <v>7</v>
       </c>
       <c r="BG4" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H5" t="n">
         <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
@@ -1366,7 +1366,7 @@
         <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
         <v>1.73</v>
@@ -1375,28 +1375,28 @@
         <v>2.22</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
         <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X5" t="n">
         <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
         <v>980</v>
@@ -1405,7 +1405,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
         <v>13.5</v>
@@ -1417,22 +1417,22 @@
         <v>980</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AH5" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL5" t="n">
         <v>980</v>
@@ -1441,34 +1441,34 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
         <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AX5" t="n">
         <v>7.6</v>
@@ -1477,32 +1477,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE5" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6</v>
       </c>
       <c r="BF5" t="n">
         <v>6.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -1548,73 +1548,73 @@
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V6" t="n">
         <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
         <v>12</v>
       </c>
       <c r="Y6" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z6" t="n">
         <v>500</v>
       </c>
-      <c r="Z6" t="n">
-        <v>120</v>
-      </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
         <v>60</v>
@@ -1623,13 +1623,13 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
         <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1647,7 +1647,7 @@
         <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>8.6</v>
       </c>
       <c r="AS6" t="n">
         <v>8.800000000000001</v>
@@ -1656,28 +1656,28 @@
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC6" t="n">
         <v>10.5</v>
@@ -1686,17 +1686,17 @@
         <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BG6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
         <v>3.6</v>
@@ -1745,79 +1745,79 @@
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="M7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N7" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="P7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
         <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>980</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>8</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AE7" t="n">
         <v>980</v>
       </c>
       <c r="AF7" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AH7" t="n">
-        <v>980</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AK7" t="n">
         <v>500</v>
@@ -1835,62 +1835,62 @@
         <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AW7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>28</v>
-      </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
         <v>8</v>
       </c>
       <c r="BG7" t="n">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
         <v>3.1</v>
@@ -1933,7 +1933,7 @@
         <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>3.25</v>
@@ -1957,61 +1957,61 @@
         <v>2.52</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.48</v>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>320</v>
       </c>
       <c r="AB8" t="n">
-        <v>19</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>980</v>
+        <v>200</v>
       </c>
       <c r="AF8" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AH8" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AI8" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>210</v>
       </c>
       <c r="AK8" t="n">
         <v>210</v>
@@ -2026,65 +2026,65 @@
         <v>980</v>
       </c>
       <c r="AO8" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>8.6</v>
       </c>
-      <c r="AX8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AY8" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE8" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.5</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="G9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H9" t="n">
         <v>2.78</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.66</v>
-      </c>
       <c r="I9" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2145,58 +2145,58 @@
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
         <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
         <v>290</v>
       </c>
       <c r="AB9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
         <v>14.5</v>
@@ -2205,52 +2205,52 @@
         <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL9" t="n">
         <v>32</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
       </c>
       <c r="AM9" t="n">
         <v>200</v>
       </c>
       <c r="AN9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP9" t="n">
         <v>20</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AQ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR9" t="n">
         <v>19.5</v>
       </c>
-      <c r="AP9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>18</v>
-      </c>
       <c r="AS9" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>12.5</v>
@@ -2259,26 +2259,26 @@
         <v>16</v>
       </c>
       <c r="BB9" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
         <v>14.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="BF9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I10" t="n">
         <v>3.05</v>
@@ -2339,52 +2339,52 @@
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R10" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
         <v>1.55</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V10" t="n">
         <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AB10" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
         <v>19</v>
@@ -2399,7 +2399,7 @@
         <v>34</v>
       </c>
       <c r="AJ10" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
         <v>23</v>
@@ -2408,31 +2408,31 @@
         <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
         <v>13.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP10" t="n">
         <v>20</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
         <v>11.5</v>
@@ -2456,7 +2456,7 @@
         <v>16.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD10" t="n">
         <v>15</v>
@@ -2465,14 +2465,14 @@
         <v>23</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G11" t="n">
         <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I11" t="n">
         <v>2.98</v>
@@ -2518,7 +2518,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.52</v>
@@ -2530,7 +2530,7 @@
         <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
         <v>1.67</v>
@@ -2548,13 +2548,13 @@
         <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
         <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
         <v>9.800000000000001</v>
@@ -2572,7 +2572,7 @@
         <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -2581,7 +2581,7 @@
         <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -2608,22 +2608,22 @@
         <v>42</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>9</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
@@ -2632,28 +2632,28 @@
         <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BC11" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE11" t="n">
         <v>130</v>
@@ -2662,11 +2662,11 @@
         <v>36</v>
       </c>
       <c r="BG11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>1.92</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
         <v>5.2</v>
@@ -2712,22 +2712,22 @@
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
@@ -2739,10 +2739,10 @@
         <v>3.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
         <v>1.25</v>
@@ -2751,31 +2751,31 @@
         <v>2.08</v>
       </c>
       <c r="X12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y12" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="Z12" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
@@ -2793,16 +2793,16 @@
         <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
         <v>7.6</v>
@@ -2811,56 +2811,56 @@
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AU12" t="n">
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>17.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G13" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
         <v>4.9</v>
@@ -2915,7 +2915,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.26</v>
@@ -2924,16 +2924,16 @@
         <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
         <v>2.14</v>
@@ -2942,7 +2942,7 @@
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
         <v>19</v>
@@ -2957,13 +2957,13 @@
         <v>700</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE13" t="n">
         <v>60</v>
@@ -2984,58 +2984,58 @@
         <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL13" t="n">
         <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="AN13" t="n">
         <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ13" t="n">
         <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
         <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC13" t="n">
         <v>15.5</v>
@@ -3047,14 +3047,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3085,82 +3085,82 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.48</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.44</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="U14" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC14" t="n">
         <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
         <v>14</v>
@@ -3169,10 +3169,10 @@
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
         <v>20</v>
@@ -3184,25 +3184,25 @@
         <v>28</v>
       </c>
       <c r="AM14" t="n">
-        <v>200</v>
+        <v>330</v>
       </c>
       <c r="AN14" t="n">
         <v>8</v>
       </c>
       <c r="AO14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ14" t="n">
         <v>21</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -3214,7 +3214,7 @@
         <v>16.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
@@ -3223,10 +3223,10 @@
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3238,17 +3238,17 @@
         <v>15</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
         <v>26</v>
       </c>
       <c r="Z15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
         <v>11.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL15" t="n">
         <v>32</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA15" t="n">
         <v>8</v>
       </c>
-      <c r="AO15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="BB15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF15" t="n">
         <v>5.7</v>
       </c>
-      <c r="AR15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G16" t="n">
         <v>1.2</v>
       </c>
       <c r="H16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I16" t="n">
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -3500,31 +3500,31 @@
         <v>2.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="n">
         <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="S16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="T16" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3575,13 +3575,13 @@
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>4.2</v>
@@ -3593,10 +3593,10 @@
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="AV16" t="n">
         <v>4.2</v>
@@ -3605,38 +3605,38 @@
         <v>4.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="BA16" t="n">
         <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.23</v>
@@ -3694,52 +3694,52 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="R17" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S17" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="T17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X17" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y17" t="n">
         <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AB17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
         <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>36</v>
@@ -3748,34 +3748,34 @@
         <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
         <v>14</v>
       </c>
       <c r="AI17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ17" t="n">
         <v>25</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL17" t="n">
         <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AN17" t="n">
         <v>6.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ17" t="n">
         <v>27</v>
@@ -3784,53 +3784,53 @@
         <v>34</v>
       </c>
       <c r="AS17" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="AT17" t="n">
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX17" t="n">
         <v>16.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
         <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
         <v>18.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K18" t="n">
         <v>5.8</v>
@@ -3885,67 +3885,67 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
         <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z18" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AA18" t="n">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>12.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AE18" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AF18" t="n">
         <v>8.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
         <v>520</v>
@@ -3957,13 +3957,13 @@
         <v>15.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
         <v>430</v>
       </c>
       <c r="AN18" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3972,13 +3972,13 @@
         <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR18" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>13.5</v>
+        <v>65</v>
       </c>
       <c r="AT18" t="n">
         <v>7.8</v>
@@ -3987,44 +3987,44 @@
         <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AW18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
         <v>23</v>
       </c>
       <c r="BA18" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD18" t="n">
         <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG18" t="n">
         <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H19" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="I19" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K19" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L19" t="n">
         <v>1.6</v>
@@ -4079,49 +4079,49 @@
         <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X19" t="n">
         <v>8</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC19" t="n">
         <v>6.8</v>
@@ -4130,7 +4130,7 @@
         <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
@@ -4145,25 +4145,25 @@
         <v>70</v>
       </c>
       <c r="AJ19" t="n">
-        <v>65</v>
+        <v>430</v>
       </c>
       <c r="AK19" t="n">
         <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="n">
         <v>70</v>
       </c>
       <c r="AO19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.4</v>
@@ -4172,25 +4172,25 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX19" t="n">
         <v>18.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
         <v>20</v>
@@ -4199,26 +4199,26 @@
         <v>55</v>
       </c>
       <c r="BB19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC19" t="n">
         <v>46</v>
       </c>
       <c r="BD19" t="n">
-        <v>65</v>
+        <v>19.5</v>
       </c>
       <c r="BE19" t="n">
         <v>180</v>
       </c>
       <c r="BF19" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="BG19" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4249,64 +4249,64 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G20" t="n">
         <v>4.1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I20" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J20" t="n">
         <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
         <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z20" t="n">
         <v>12.5</v>
@@ -4315,10 +4315,10 @@
         <v>29</v>
       </c>
       <c r="AB20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
         <v>11.5</v>
@@ -4333,10 +4333,10 @@
         <v>16.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ20" t="n">
         <v>85</v>
@@ -4348,16 +4348,16 @@
         <v>75</v>
       </c>
       <c r="AM20" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.6</v>
@@ -4366,22 +4366,22 @@
         <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>15</v>
@@ -4390,29 +4390,29 @@
         <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB20" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BD20" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BF20" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="BG20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H21" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
         <v>1.46</v>
@@ -4470,7 +4470,7 @@
         <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
         <v>1.81</v>
@@ -4479,7 +4479,7 @@
         <v>2.18</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -4491,10 +4491,10 @@
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
         <v>11.5</v>
@@ -4506,19 +4506,19 @@
         <v>13.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AB21" t="n">
         <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
         <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
@@ -4527,10 +4527,10 @@
         <v>15.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
         <v>190</v>
@@ -4539,13 +4539,13 @@
         <v>48</v>
       </c>
       <c r="AL21" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
         <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AO21" t="n">
         <v>21</v>
@@ -4554,10 +4554,10 @@
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS21" t="n">
         <v>26</v>
@@ -4572,41 +4572,41 @@
         <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
         <v>23</v>
       </c>
       <c r="AY21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ21" t="n">
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BB21" t="n">
         <v>38</v>
       </c>
       <c r="BC21" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BD21" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE21" t="n">
         <v>32</v>
       </c>
       <c r="BF21" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="BG21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
         <v>3.15</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.46</v>
@@ -4667,10 +4667,10 @@
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
@@ -4682,19 +4682,19 @@
         <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
         <v>23</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4709,22 +4709,22 @@
         <v>14</v>
       </c>
       <c r="AD22" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG22" t="n">
         <v>23</v>
       </c>
       <c r="AH22" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI22" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>900</v>
@@ -4751,56 +4751,56 @@
         <v>7.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT22" t="n">
         <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX22" t="n">
         <v>6.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>3.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4831,64 +4831,64 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G23" t="n">
         <v>5.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="J23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K23" t="n">
         <v>4.3</v>
       </c>
-      <c r="K23" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P23" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="T23" t="n">
         <v>1.71</v>
       </c>
       <c r="U23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V23" t="n">
         <v>2.3</v>
       </c>
-      <c r="V23" t="n">
-        <v>2.32</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
         <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z23" t="n">
         <v>11.5</v>
@@ -4897,28 +4897,28 @@
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="n">
         <v>42</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ23" t="n">
         <v>120</v>
@@ -4927,19 +4927,19 @@
         <v>60</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO23" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>10</v>
@@ -4948,53 +4948,53 @@
         <v>10.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AY23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB23" t="n">
         <v>42</v>
       </c>
       <c r="BC23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD23" t="n">
         <v>48</v>
       </c>
-      <c r="BD23" t="n">
-        <v>28</v>
-      </c>
       <c r="BE23" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BF23" t="n">
         <v>44</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5025,52 +5025,52 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G24" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H24" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I24" t="n">
         <v>2.98</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="U24" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V24" t="n">
         <v>1.5</v>
@@ -5088,13 +5088,13 @@
         <v>980</v>
       </c>
       <c r="AA24" t="n">
-        <v>210</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AC24" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
         <v>980</v>
@@ -5106,10 +5106,10 @@
         <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AH24" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -5139,7 +5139,7 @@
         <v>7</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS24" t="n">
         <v>14.5</v>
@@ -5148,47 +5148,47 @@
         <v>7.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
         <v>7.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX24" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AY24" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.55</v>
+        <v>16.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H25" t="n">
         <v>3.35</v>
@@ -5231,7 +5231,7 @@
         <v>3.85</v>
       </c>
       <c r="J25" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K25" t="n">
         <v>3.15</v>
@@ -5243,7 +5243,7 @@
         <v>1.13</v>
       </c>
       <c r="N25" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O25" t="n">
         <v>1.57</v>
@@ -5261,19 +5261,19 @@
         <v>5.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="V25" t="n">
         <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X25" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y25" t="n">
         <v>9.800000000000001</v>
@@ -5288,13 +5288,13 @@
         <v>7.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD25" t="n">
         <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF25" t="n">
         <v>15.5</v>
@@ -5303,7 +5303,7 @@
         <v>13.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5315,13 +5315,13 @@
         <v>140</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
@@ -5336,7 +5336,7 @@
         <v>19.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT25" t="n">
         <v>6.4</v>
@@ -5345,10 +5345,10 @@
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX25" t="n">
         <v>12.5</v>
@@ -5360,29 +5360,29 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
         <v>3.45</v>
@@ -5422,10 +5422,10 @@
         <v>2.54</v>
       </c>
       <c r="I26" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K26" t="n">
         <v>3.3</v>
@@ -5440,25 +5440,25 @@
         <v>2.92</v>
       </c>
       <c r="O26" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U26" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
         <v>1.56</v>
@@ -5470,10 +5470,10 @@
         <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA26" t="n">
         <v>150</v>
@@ -5485,22 +5485,22 @@
         <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG26" t="n">
         <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
         <v>160</v>
@@ -5518,7 +5518,7 @@
         <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AP26" t="n">
         <v>8.800000000000001</v>
@@ -5530,7 +5530,7 @@
         <v>13.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="AT26" t="n">
         <v>8.800000000000001</v>
@@ -5551,32 +5551,32 @@
         <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BC26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG26" t="n">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G27" t="n">
         <v>2.24</v>
       </c>
       <c r="H27" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
         <v>3.25</v>
@@ -5631,7 +5631,7 @@
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
         <v>1.4</v>
@@ -5649,7 +5649,7 @@
         <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U27" t="n">
         <v>1.9</v>
@@ -5667,13 +5667,13 @@
         <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA27" t="n">
         <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC27" t="n">
         <v>8</v>
@@ -5685,7 +5685,7 @@
         <v>160</v>
       </c>
       <c r="AF27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
@@ -5694,25 +5694,25 @@
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AJ27" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK27" t="n">
         <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AP27" t="n">
         <v>9.800000000000001</v>
@@ -5721,10 +5721,10 @@
         <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5751,26 +5751,26 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>22</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BE27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BF27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="G28" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="H28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.95</v>
       </c>
-      <c r="I28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U28" t="n">
         <v>1.95</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Z28" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH28" t="n">
         <v>21</v>
       </c>
       <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO28" t="n">
         <v>700</v>
       </c>
-      <c r="AJ28" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU28" t="n">
         <v>7</v>
       </c>
-      <c r="AU28" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV28" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG28" t="n">
         <v>9.4</v>
       </c>
-      <c r="AY28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G29" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H29" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="I29" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>3.75</v>
@@ -6016,10 +6016,10 @@
         <v>1.33</v>
       </c>
       <c r="M29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
         <v>1.21</v>
@@ -6034,7 +6034,7 @@
         <v>1.59</v>
       </c>
       <c r="S29" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T29" t="n">
         <v>1.57</v>
@@ -6043,13 +6043,13 @@
         <v>2.7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W29" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y29" t="n">
         <v>16</v>
@@ -6058,19 +6058,19 @@
         <v>21</v>
       </c>
       <c r="AA29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB29" t="n">
         <v>15</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD29" t="n">
         <v>12.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF29" t="n">
         <v>19</v>
@@ -6085,7 +6085,7 @@
         <v>32</v>
       </c>
       <c r="AJ29" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
@@ -6103,7 +6103,7 @@
         <v>17</v>
       </c>
       <c r="AP29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ29" t="n">
         <v>15</v>
@@ -6112,19 +6112,19 @@
         <v>20</v>
       </c>
       <c r="AS29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT29" t="n">
         <v>14.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV29" t="n">
         <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX29" t="n">
         <v>18.5</v>
@@ -6139,13 +6139,13 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
       </c>
       <c r="BD29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE29" t="n">
         <v>48</v>
@@ -6154,11 +6154,11 @@
         <v>14.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G30" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H30" t="n">
         <v>6.8</v>
@@ -6201,13 +6201,13 @@
         <v>7</v>
       </c>
       <c r="J30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.2</v>
       </c>
-      <c r="K30" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -6219,7 +6219,7 @@
         <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q30" t="n">
         <v>2.02</v>
@@ -6228,19 +6228,19 @@
         <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T30" t="n">
         <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V30" t="n">
         <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="X30" t="n">
         <v>14</v>
@@ -6255,19 +6255,19 @@
         <v>210</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC30" t="n">
         <v>9</v>
       </c>
       <c r="AD30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE30" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
@@ -6276,7 +6276,7 @@
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ30" t="n">
         <v>14.5</v>
@@ -6291,7 +6291,7 @@
         <v>150</v>
       </c>
       <c r="AN30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO30" t="n">
         <v>140</v>
@@ -6309,7 +6309,7 @@
         <v>190</v>
       </c>
       <c r="AT30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU30" t="n">
         <v>8.800000000000001</v>
@@ -6321,16 +6321,16 @@
         <v>90</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB30" t="n">
         <v>13.5</v>
@@ -6339,20 +6339,20 @@
         <v>16.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE30" t="n">
         <v>120</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG30" t="n">
         <v>130</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G31" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H31" t="n">
         <v>4.7</v>
@@ -6395,46 +6395,46 @@
         <v>4.8</v>
       </c>
       <c r="J31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.6</v>
       </c>
-      <c r="K31" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L31" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.98</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
       </c>
       <c r="V31" t="n">
         <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X31" t="n">
         <v>11.5</v>
@@ -6446,7 +6446,7 @@
         <v>32</v>
       </c>
       <c r="AA31" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB31" t="n">
         <v>7.8</v>
@@ -6461,7 +6461,7 @@
         <v>65</v>
       </c>
       <c r="AF31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG31" t="n">
         <v>10.5</v>
@@ -6473,7 +6473,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK31" t="n">
         <v>21</v>
@@ -6485,7 +6485,7 @@
         <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO31" t="n">
         <v>80</v>
@@ -6503,16 +6503,16 @@
         <v>95</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU31" t="n">
         <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX31" t="n">
         <v>10</v>
@@ -6539,14 +6539,14 @@
         <v>100</v>
       </c>
       <c r="BF31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG31" t="n">
         <v>75</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6577,91 +6577,91 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G32" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="H32" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N32" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="P32" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="S32" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="T32" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U32" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W32" t="n">
         <v>1.56</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X32" t="n">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Z32" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
         <v>980</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE32" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AG32" t="n">
         <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AI32" t="n">
         <v>980</v>
@@ -6670,10 +6670,10 @@
         <v>220</v>
       </c>
       <c r="AK32" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AL32" t="n">
-        <v>980</v>
+        <v>130</v>
       </c>
       <c r="AM32" t="n">
         <v>580</v>
@@ -6685,62 +6685,62 @@
         <v>55</v>
       </c>
       <c r="AP32" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX32" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>17.5</v>
       </c>
       <c r="AY32" t="n">
         <v>11</v>
       </c>
       <c r="AZ32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA32" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB32" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB32" t="n">
-        <v>11</v>
-      </c>
       <c r="BC32" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BD32" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BE32" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BF32" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG32" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6777,16 +6777,16 @@
         <v>4.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I33" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.54</v>
@@ -6795,16 +6795,16 @@
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O33" t="n">
         <v>1.48</v>
       </c>
       <c r="P33" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R33" t="n">
         <v>1.22</v>
@@ -6813,7 +6813,7 @@
         <v>4.9</v>
       </c>
       <c r="T33" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="U33" t="n">
         <v>1.8</v>
@@ -6828,43 +6828,43 @@
         <v>10.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z33" t="n">
         <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AB33" t="n">
         <v>12</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD33" t="n">
         <v>11.5</v>
       </c>
       <c r="AE33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF33" t="n">
         <v>75</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>90</v>
       </c>
       <c r="AG33" t="n">
         <v>18</v>
       </c>
       <c r="AH33" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AI33" t="n">
         <v>500</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL33" t="n">
         <v>1000</v>
@@ -6876,10 +6876,10 @@
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.2</v>
@@ -6888,7 +6888,7 @@
         <v>10.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
@@ -6903,13 +6903,13 @@
         <v>13.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY33" t="n">
         <v>15</v>
       </c>
       <c r="AZ33" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA33" t="n">
         <v>23</v>
@@ -6918,23 +6918,23 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD33" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>9</v>
       </c>
       <c r="BE33" t="n">
         <v>9.4</v>
       </c>
       <c r="BF33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG33" t="n">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6965,97 +6965,97 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="G34" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="H34" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>3.75</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P34" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V34" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W34" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AC34" t="n">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE34" t="n">
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AG34" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK34" t="n">
         <v>500</v>
@@ -7076,59 +7076,59 @@
         <v>7.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.66</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX34" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.74</v>
+        <v>10</v>
       </c>
       <c r="BB34" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.58</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>2.42</v>
+        <v>8.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7159,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H35" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="I35" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="J35" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K35" t="n">
         <v>4.2</v>
@@ -7189,7 +7189,7 @@
         <v>1.26</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q35" t="n">
         <v>1.81</v>
@@ -7201,16 +7201,16 @@
         <v>3.1</v>
       </c>
       <c r="T35" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U35" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V35" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X35" t="n">
         <v>16.5</v>
@@ -7219,28 +7219,28 @@
         <v>10.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB35" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF35" t="n">
         <v>36</v>
       </c>
       <c r="AG35" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH35" t="n">
         <v>18</v>
@@ -7249,40 +7249,40 @@
         <v>32</v>
       </c>
       <c r="AJ35" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AK35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL35" t="n">
         <v>60</v>
       </c>
       <c r="AM35" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN35" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO35" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ35" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR35" t="n">
         <v>10.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT35" t="n">
         <v>15.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV35" t="n">
         <v>9.199999999999999</v>
@@ -7291,38 +7291,38 @@
         <v>16.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ35" t="n">
         <v>15.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB35" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BC35" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BD35" t="n">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BE35" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BF35" t="n">
         <v>38</v>
       </c>
       <c r="BG35" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G36" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H36" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I36" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>3.25</v>
@@ -7383,7 +7383,7 @@
         <v>1.4</v>
       </c>
       <c r="P36" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q36" t="n">
         <v>2.22</v>
@@ -7395,34 +7395,34 @@
         <v>4.1</v>
       </c>
       <c r="T36" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V36" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W36" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X36" t="n">
         <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA36" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB36" t="n">
         <v>10.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD36" t="n">
         <v>14.5</v>
@@ -7431,16 +7431,16 @@
         <v>42</v>
       </c>
       <c r="AF36" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG36" t="n">
         <v>12.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI36" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AJ36" t="n">
         <v>40</v>
@@ -7449,43 +7449,43 @@
         <v>32</v>
       </c>
       <c r="AL36" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AM36" t="n">
         <v>330</v>
       </c>
       <c r="AN36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO36" t="n">
         <v>44</v>
       </c>
       <c r="AP36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ36" t="n">
         <v>10</v>
       </c>
-      <c r="AQ36" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AR36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS36" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AT36" t="n">
         <v>8.4</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW36" t="n">
         <v>32</v>
       </c>
       <c r="AX36" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY36" t="n">
         <v>10</v>
@@ -7497,10 +7497,10 @@
         <v>42</v>
       </c>
       <c r="BB36" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD36" t="n">
         <v>20</v>
@@ -7509,14 +7509,14 @@
         <v>26</v>
       </c>
       <c r="BF36" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="BG36" t="n">
-        <v>29</v>
+        <v>7.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7547,13 +7547,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G37" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H37" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
         <v>8</v>
@@ -7565,34 +7565,34 @@
         <v>4.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M37" t="n">
         <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
         <v>1.27</v>
       </c>
       <c r="P37" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R37" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.9</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.92</v>
       </c>
       <c r="V37" t="n">
         <v>1.14</v>
@@ -7607,25 +7607,25 @@
         <v>25</v>
       </c>
       <c r="Z37" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD37" t="n">
         <v>28</v>
       </c>
       <c r="AE37" t="n">
-        <v>510</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG37" t="n">
         <v>10.5</v>
@@ -7634,7 +7634,7 @@
         <v>24</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AJ37" t="n">
         <v>14.5</v>
@@ -7658,16 +7658,16 @@
         <v>15</v>
       </c>
       <c r="AQ37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR37" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS37" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU37" t="n">
         <v>8.800000000000001</v>
@@ -7676,22 +7676,22 @@
         <v>13</v>
       </c>
       <c r="AW37" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX37" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY37" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC37" t="n">
         <v>13.5</v>
@@ -7703,14 +7703,14 @@
         <v>28</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G38" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J38" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L38" t="n">
         <v>1.42</v>
@@ -7765,76 +7765,76 @@
         <v>1.07</v>
       </c>
       <c r="N38" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O38" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P38" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
         <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T38" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="U38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V38" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W38" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="X38" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD38" t="n">
         <v>980</v>
       </c>
-      <c r="Y38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>42</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE38" t="n">
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>150</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK38" t="n">
         <v>65</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>140</v>
       </c>
       <c r="AL38" t="n">
         <v>1000</v>
@@ -7846,7 +7846,7 @@
         <v>55</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP38" t="n">
         <v>9</v>
@@ -7855,13 +7855,13 @@
         <v>8.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.95</v>
+        <v>8.4</v>
       </c>
       <c r="AT38" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AU38" t="n">
         <v>6.4</v>
@@ -7870,7 +7870,7 @@
         <v>10.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AX38" t="n">
         <v>5.8</v>
@@ -7879,10 +7879,10 @@
         <v>6.2</v>
       </c>
       <c r="AZ38" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="BB38" t="n">
         <v>10.5</v>
@@ -7891,20 +7891,20 @@
         <v>10.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>9</v>
+        <v>17.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7938,10 +7938,10 @@
         <v>2.44</v>
       </c>
       <c r="G39" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H39" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I39" t="n">
         <v>3.3</v>
@@ -7950,7 +7950,7 @@
         <v>3.3</v>
       </c>
       <c r="K39" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L39" t="n">
         <v>1.46</v>
@@ -7959,52 +7959,52 @@
         <v>1.09</v>
       </c>
       <c r="N39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P39" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S39" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T39" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U39" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="V39" t="n">
         <v>1.44</v>
       </c>
       <c r="W39" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X39" t="n">
         <v>21</v>
       </c>
       <c r="Y39" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD39" t="n">
         <v>26</v>
@@ -8013,16 +8013,16 @@
         <v>980</v>
       </c>
       <c r="AF39" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AG39" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AH39" t="n">
         <v>40</v>
       </c>
       <c r="AI39" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AJ39" t="n">
         <v>1000</v>
@@ -8046,59 +8046,59 @@
         <v>7.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR39" t="n">
         <v>10.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT39" t="n">
         <v>6</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV39" t="n">
         <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX39" t="n">
         <v>7.6</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ39" t="n">
         <v>12</v>
       </c>
       <c r="BA39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB39" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BC39" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="BE39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG39" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I40" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J40" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K40" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L40" t="n">
         <v>1.48</v>
@@ -8159,140 +8159,140 @@
         <v>1.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R40" t="n">
         <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T40" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="U40" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="V40" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W40" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="X40" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG40" t="n">
         <v>23</v>
       </c>
-      <c r="Y40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>85</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>65</v>
-      </c>
       <c r="AH40" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP40" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ40" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AS40" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="AW40" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AX40" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AY40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG40" t="n">
         <v>12.5</v>
       </c>
-      <c r="BA40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8326,64 +8326,64 @@
         <v>3.4</v>
       </c>
       <c r="G41" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H41" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I41" t="n">
         <v>2.26</v>
       </c>
       <c r="J41" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L41" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M41" t="n">
         <v>1.04</v>
       </c>
       <c r="N41" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O41" t="n">
         <v>1.18</v>
       </c>
       <c r="P41" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R41" t="n">
         <v>1.64</v>
       </c>
       <c r="S41" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T41" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U41" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V41" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W41" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X41" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y41" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA41" t="n">
         <v>29</v>
@@ -8392,31 +8392,31 @@
         <v>22</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD41" t="n">
         <v>11.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG41" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AI41" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ41" t="n">
         <v>980</v>
       </c>
       <c r="AK41" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL41" t="n">
         <v>36</v>
@@ -8425,10 +8425,10 @@
         <v>55</v>
       </c>
       <c r="AN41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP41" t="n">
         <v>21</v>
@@ -8437,56 +8437,56 @@
         <v>13</v>
       </c>
       <c r="AR41" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS41" t="n">
         <v>24</v>
       </c>
       <c r="AT41" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU41" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AV41" t="n">
         <v>10</v>
       </c>
       <c r="AW41" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY41" t="n">
         <v>14</v>
       </c>
       <c r="AZ41" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA41" t="n">
         <v>22</v>
       </c>
       <c r="BB41" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC41" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="BD41" t="n">
         <v>30</v>
       </c>
       <c r="BE41" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="BF41" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG41" t="n">
         <v>9.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8520,13 +8520,13 @@
         <v>2.02</v>
       </c>
       <c r="G42" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H42" t="n">
         <v>4.1</v>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>3.5</v>
@@ -8535,19 +8535,19 @@
         <v>3.75</v>
       </c>
       <c r="L42" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M42" t="n">
         <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O42" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P42" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q42" t="n">
         <v>2.12</v>
@@ -8559,16 +8559,16 @@
         <v>3.95</v>
       </c>
       <c r="T42" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U42" t="n">
         <v>1.96</v>
       </c>
       <c r="V42" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W42" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X42" t="n">
         <v>13</v>
@@ -8577,19 +8577,19 @@
         <v>15</v>
       </c>
       <c r="Z42" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AA42" t="n">
         <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC42" t="n">
         <v>8.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE42" t="n">
         <v>200</v>
@@ -8607,10 +8607,10 @@
         <v>330</v>
       </c>
       <c r="AJ42" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AK42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL42" t="n">
         <v>130</v>
@@ -8622,7 +8622,7 @@
         <v>19</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP42" t="n">
         <v>10.5</v>
@@ -8634,53 +8634,53 @@
         <v>13</v>
       </c>
       <c r="AS42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT42" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU42" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV42" t="n">
         <v>15</v>
       </c>
       <c r="AW42" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="AX42" t="n">
         <v>10</v>
       </c>
       <c r="AY42" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BB42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC42" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF42" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G43" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H43" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="I43" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8741,10 +8741,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
         <v>2.76</v>
       </c>
       <c r="I44" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J44" t="n">
         <v>3.4</v>
@@ -8923,43 +8923,43 @@
         <v>3.7</v>
       </c>
       <c r="L44" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
         <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O44" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R44" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
         <v>3.6</v>
       </c>
       <c r="T44" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U44" t="n">
         <v>2.06</v>
       </c>
       <c r="V44" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W44" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X44" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Y44" t="n">
         <v>12</v>
@@ -8968,25 +8968,25 @@
         <v>44</v>
       </c>
       <c r="AA44" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB44" t="n">
         <v>11.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD44" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG44" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AH44" t="n">
         <v>40</v>
@@ -8998,7 +8998,7 @@
         <v>900</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL44" t="n">
         <v>1000</v>
@@ -9010,65 +9010,65 @@
         <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP44" t="n">
         <v>11</v>
       </c>
       <c r="AQ44" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR44" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AT44" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU44" t="n">
         <v>6.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AW44" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX44" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AY44" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BA44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC44" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>7</v>
-      </c>
       <c r="BD44" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BE44" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG44" t="n">
         <v>7</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="G45" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H45" t="n">
         <v>14</v>
@@ -9111,10 +9111,10 @@
         <v>16.5</v>
       </c>
       <c r="J45" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K45" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -9293,160 +9293,160 @@
         </is>
       </c>
       <c r="F46" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H46" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I46" t="n">
+        <v>12</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L46" t="n">
         <v>1.29</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="H46" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J46" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K46" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.3</v>
       </c>
       <c r="M46" t="n">
         <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O46" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P46" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="R46" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="S46" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="T46" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="U46" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="V46" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W46" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="X46" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="Y46" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="Z46" t="n">
         <v>130</v>
       </c>
       <c r="AA46" t="n">
-        <v>710</v>
+        <v>600</v>
       </c>
       <c r="AB46" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AE46" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AF46" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AG46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>11</v>
       </c>
-      <c r="AH46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI46" t="n">
+      <c r="AK46" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AO46" t="n">
         <v>210</v>
       </c>
-      <c r="AJ46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>300</v>
-      </c>
       <c r="AP46" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AQ46" t="n">
         <v>16</v>
       </c>
       <c r="AR46" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT46" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV46" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AX46" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY46" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ46" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BA46" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BB46" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC46" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BE46" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="BF46" t="n">
         <v>4.6</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -9487,58 +9487,58 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G47" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H47" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I47" t="n">
         <v>4.1</v>
       </c>
       <c r="J47" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L47" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M47" t="n">
         <v>1.06</v>
       </c>
       <c r="N47" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O47" t="n">
         <v>1.28</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T47" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="U47" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V47" t="n">
         <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X47" t="n">
         <v>17</v>
@@ -9556,13 +9556,13 @@
         <v>11</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD47" t="n">
         <v>16.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>170</v>
+        <v>980</v>
       </c>
       <c r="AF47" t="n">
         <v>14.5</v>
@@ -9589,10 +9589,10 @@
         <v>580</v>
       </c>
       <c r="AN47" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO47" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP47" t="n">
         <v>14</v>
@@ -9601,56 +9601,56 @@
         <v>13</v>
       </c>
       <c r="AR47" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT47" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU47" t="n">
         <v>7.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX47" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ47" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BB47" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC47" t="n">
         <v>18</v>
       </c>
       <c r="BD47" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF47" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G48" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H48" t="n">
         <v>3.3</v>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J48" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K48" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L48" t="n">
         <v>1.52</v>
@@ -9705,19 +9705,19 @@
         <v>1.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>1.45</v>
       </c>
       <c r="P48" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R48" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S48" t="n">
         <v>4.6</v>
@@ -9729,40 +9729,40 @@
         <v>1.72</v>
       </c>
       <c r="V48" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X48" t="n">
         <v>10.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AA48" t="n">
         <v>900</v>
       </c>
       <c r="AB48" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC48" t="n">
         <v>7.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH48" t="n">
         <v>22</v>
@@ -9774,7 +9774,7 @@
         <v>120</v>
       </c>
       <c r="AK48" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
         <v>1000</v>
@@ -9783,7 +9783,7 @@
         <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
         <v>1000</v>
@@ -9795,25 +9795,25 @@
         <v>9</v>
       </c>
       <c r="AR48" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AT48" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU48" t="n">
         <v>6.2</v>
       </c>
       <c r="AV48" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX48" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>11</v>
       </c>
       <c r="AY48" t="n">
         <v>10</v>
@@ -9822,29 +9822,29 @@
         <v>17.5</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BB48" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BC48" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="BD48" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE48" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF48" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -9878,13 +9878,13 @@
         <v>3.2</v>
       </c>
       <c r="G49" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H49" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I49" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J49" t="n">
         <v>3.4</v>
@@ -9896,19 +9896,19 @@
         <v>1.45</v>
       </c>
       <c r="M49" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N49" t="n">
         <v>3.35</v>
       </c>
       <c r="O49" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P49" t="n">
         <v>1.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R49" t="n">
         <v>1.29</v>
@@ -9917,19 +9917,19 @@
         <v>3.9</v>
       </c>
       <c r="T49" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U49" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
         <v>1.69</v>
       </c>
       <c r="W49" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X49" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="Y49" t="n">
         <v>9.800000000000001</v>
@@ -9950,10 +9950,10 @@
         <v>12</v>
       </c>
       <c r="AE49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG49" t="n">
         <v>15</v>
@@ -9962,13 +9962,13 @@
         <v>19.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ49" t="n">
-        <v>190</v>
+        <v>980</v>
       </c>
       <c r="AK49" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AL49" t="n">
         <v>980</v>
@@ -9977,22 +9977,22 @@
         <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP49" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ49" t="n">
         <v>8</v>
       </c>
       <c r="AR49" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="AT49" t="n">
         <v>10</v>
@@ -10001,44 +10001,44 @@
         <v>6.8</v>
       </c>
       <c r="AV49" t="n">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW49" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AX49" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF49" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ49" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG49" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -10072,10 +10072,10 @@
         <v>6.8</v>
       </c>
       <c r="G50" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H50" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I50" t="n">
         <v>1.54</v>
@@ -10102,7 +10102,7 @@
         <v>2.46</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R50" t="n">
         <v>1.57</v>
@@ -10111,49 +10111,49 @@
         <v>2.7</v>
       </c>
       <c r="T50" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U50" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V50" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="W50" t="n">
         <v>1.16</v>
       </c>
       <c r="X50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z50" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>9.6</v>
       </c>
       <c r="AA50" t="n">
         <v>14</v>
       </c>
       <c r="AB50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC50" t="n">
         <v>11</v>
       </c>
       <c r="AD50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AE50" t="n">
         <v>14</v>
       </c>
       <c r="AF50" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG50" t="n">
         <v>25</v>
       </c>
       <c r="AH50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI50" t="n">
         <v>28</v>
@@ -10162,7 +10162,7 @@
         <v>190</v>
       </c>
       <c r="AK50" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AL50" t="n">
         <v>75</v>
@@ -10171,16 +10171,16 @@
         <v>95</v>
       </c>
       <c r="AN50" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AO50" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP50" t="n">
         <v>22</v>
       </c>
       <c r="AQ50" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR50" t="n">
         <v>9.4</v>
@@ -10195,16 +10195,16 @@
         <v>10.5</v>
       </c>
       <c r="AV50" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW50" t="n">
         <v>13.5</v>
       </c>
       <c r="AX50" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AY50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ50" t="n">
         <v>20</v>
@@ -10213,26 +10213,26 @@
         <v>27</v>
       </c>
       <c r="BB50" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BC50" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="BD50" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE50" t="n">
         <v>85</v>
       </c>
       <c r="BF50" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BG50" t="n">
         <v>6.2</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -10263,67 +10263,67 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G51" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H51" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K51" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L51" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M51" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N51" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O51" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R51" t="n">
         <v>1.14</v>
       </c>
       <c r="S51" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T51" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U51" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V51" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W51" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X51" t="n">
         <v>7.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA51" t="n">
         <v>500</v>
@@ -10335,7 +10335,7 @@
         <v>7.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE51" t="n">
         <v>310</v>
@@ -10344,10 +10344,10 @@
         <v>11.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI51" t="n">
         <v>500</v>
@@ -10359,7 +10359,7 @@
         <v>40</v>
       </c>
       <c r="AL51" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AM51" t="n">
         <v>500</v>
@@ -10368,40 +10368,40 @@
         <v>40</v>
       </c>
       <c r="AO51" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP51" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ51" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR51" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AS51" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AT51" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU51" t="n">
         <v>6.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AX51" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY51" t="n">
         <v>11</v>
       </c>
       <c r="AZ51" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA51" t="n">
         <v>44</v>
@@ -10413,10 +10413,10 @@
         <v>23</v>
       </c>
       <c r="BD51" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BE51" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="BF51" t="n">
         <v>23</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -10472,10 +10472,10 @@
         <v>2.84</v>
       </c>
       <c r="K52" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="L52" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="M52" t="n">
         <v>1.18</v>
@@ -10496,10 +10496,10 @@
         <v>1.12</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T52" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U52" t="n">
         <v>1.6</v>
@@ -10511,7 +10511,7 @@
         <v>1.55</v>
       </c>
       <c r="X52" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Y52" t="n">
         <v>8.4</v>
@@ -10526,16 +10526,16 @@
         <v>6.8</v>
       </c>
       <c r="AC52" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD52" t="n">
         <v>18</v>
       </c>
       <c r="AE52" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="AF52" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG52" t="n">
         <v>15</v>
@@ -10544,7 +10544,7 @@
         <v>32</v>
       </c>
       <c r="AI52" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ52" t="n">
         <v>50</v>
@@ -10553,28 +10553,28 @@
         <v>55</v>
       </c>
       <c r="AL52" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AM52" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AN52" t="n